--- a/outputs/predicted_with_all_scores.xlsx
+++ b/outputs/predicted_with_all_scores.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N145"/>
+  <dimension ref="A1:M145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,55 +446,50 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t xml:space="preserve">D </t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">D </t>
+          <t>IP</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>IP</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Xmetal</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Xmetal</t>
+          <t>rion​</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>rion​</t>
+          <t>nf</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>nf</t>
+          <t>nd</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>nd</t>
+          <t xml:space="preserve">PI </t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>PI (Y)</t>
+          <t>material</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>predicted_score</t>
         </is>
@@ -515,39 +510,36 @@
         <v>3.44</v>
       </c>
       <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2.885</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I2" t="n">
         <v>8</v>
       </c>
-      <c r="E2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2.885</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1.04</v>
-      </c>
       <c r="J2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.858465802735781</v>
-      </c>
-      <c r="M2" t="inlineStr">
+        <v>2.599144</v>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>Tb-acac</t>
         </is>
       </c>
-      <c r="N2" t="n">
-        <v>0.8045361408511522</v>
+      <c r="M2" t="n">
+        <v>2.572706875000004</v>
       </c>
     </row>
     <row r="3">
@@ -565,39 +557,36 @@
         <v>3.04</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="F3" t="n">
-        <v>2.74</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2</v>
+        <v>1.095</v>
       </c>
       <c r="I3" t="n">
-        <v>1.095</v>
+        <v>8</v>
       </c>
       <c r="J3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.771725182863114</v>
-      </c>
-      <c r="M3" t="inlineStr">
+        <v>1.843828</v>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>Tb-tpy</t>
         </is>
       </c>
-      <c r="N3" t="n">
-        <v>0.6824005584686895</v>
+      <c r="M3" t="n">
+        <v>1.833986159999998</v>
       </c>
     </row>
     <row r="4">
@@ -615,39 +604,36 @@
         <v>3.44</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>2.988</v>
       </c>
       <c r="F4" t="n">
-        <v>2.988</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>1.004</v>
       </c>
       <c r="H4" t="n">
         <v>1.004</v>
       </c>
       <c r="I4" t="n">
-        <v>1.004</v>
+        <v>11</v>
       </c>
       <c r="J4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.768200974072482</v>
-      </c>
-      <c r="M4" t="inlineStr">
+        <v>2.555821</v>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>Er-acac</t>
         </is>
       </c>
-      <c r="N4" t="n">
-        <v>0.7206386307661253</v>
+      <c r="M4" t="n">
+        <v>2.518268969999997</v>
       </c>
     </row>
     <row r="5">
@@ -665,39 +651,36 @@
         <v>3.44</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>2.586</v>
       </c>
       <c r="F5" t="n">
-        <v>2.586</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="I5" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.7508962783823731</v>
-      </c>
-      <c r="M5" t="inlineStr">
+        <v>2.556</v>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>La-acac</t>
         </is>
       </c>
-      <c r="N5" t="n">
-        <v>0.7458694354685947</v>
+      <c r="M5" t="n">
+        <v>2.499090169999995</v>
       </c>
     </row>
     <row r="6">
@@ -715,39 +698,36 @@
         <v>3.04</v>
       </c>
       <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2.885</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I6" t="n">
         <v>8</v>
       </c>
-      <c r="E6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" t="n">
-        <v>2.885</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1.04</v>
-      </c>
       <c r="J6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.7453734316388571</v>
-      </c>
-      <c r="M6" t="inlineStr">
+        <v>1.796519</v>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>Tb-bpy</t>
         </is>
       </c>
-      <c r="N6" t="n">
-        <v>0.6243374426641976</v>
+      <c r="M6" t="n">
+        <v>1.703361214750003</v>
       </c>
     </row>
     <row r="7">
@@ -765,39 +745,36 @@
         <v>3.44</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>2.921</v>
       </c>
       <c r="F7" t="n">
-        <v>2.921</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>1.027</v>
       </c>
       <c r="H7" t="n">
         <v>1.027</v>
       </c>
       <c r="I7" t="n">
-        <v>1.027</v>
+        <v>9</v>
       </c>
       <c r="J7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.731057224606581</v>
-      </c>
-      <c r="M7" t="inlineStr">
+        <v>2.573673</v>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>Dy-acac</t>
         </is>
       </c>
-      <c r="N7" t="n">
-        <v>0.7172153037300517</v>
+      <c r="M7" t="n">
+        <v>2.559356454999998</v>
       </c>
     </row>
     <row r="8">
@@ -815,39 +792,36 @@
         <v>3.44</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>2.814</v>
       </c>
       <c r="F8" t="n">
-        <v>2.814</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2</v>
+        <v>1.066</v>
       </c>
       <c r="I8" t="n">
-        <v>1.066</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.722993271656855</v>
-      </c>
-      <c r="M8" t="inlineStr">
+        <v>2.56494</v>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>Eu-acac</t>
         </is>
       </c>
-      <c r="N8" t="n">
-        <v>0.7546609400815852</v>
+      <c r="M8" t="n">
+        <v>2.535438674999996</v>
       </c>
     </row>
     <row r="9">
@@ -865,39 +839,36 @@
         <v>3.04</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>2.885</v>
       </c>
       <c r="F9" t="n">
-        <v>2.885</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="H9" t="n">
         <v>1.04</v>
       </c>
       <c r="I9" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="J9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.716285565126599</v>
-      </c>
-      <c r="M9" t="inlineStr">
+        <v>1.487598</v>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>Tb-phen</t>
         </is>
       </c>
-      <c r="N9" t="n">
-        <v>0.6394657974582915</v>
+      <c r="M9" t="n">
+        <v>1.528264721694442</v>
       </c>
     </row>
     <row r="10">
@@ -915,39 +886,36 @@
         <v>3.44</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>2.941</v>
       </c>
       <c r="F10" t="n">
-        <v>2.941</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>1.65</v>
       </c>
       <c r="H10" t="n">
-        <v>1.65</v>
+        <v>0.68</v>
       </c>
       <c r="I10" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K10" t="n">
-        <v>10</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.712904761904762</v>
-      </c>
-      <c r="M10" t="inlineStr">
+        <v>2.006054</v>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>Zn-acac</t>
         </is>
       </c>
-      <c r="N10" t="n">
-        <v>0.6971211795644153</v>
+      <c r="M10" t="n">
+        <v>2.004564945000003</v>
       </c>
     </row>
     <row r="11">
@@ -965,39 +933,36 @@
         <v>3.44</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>4.651</v>
       </c>
       <c r="F11" t="n">
-        <v>4.651</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>1.83</v>
       </c>
       <c r="H11" t="n">
-        <v>1.83</v>
+        <v>0.645</v>
       </c>
       <c r="I11" t="n">
-        <v>0.645</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>5</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.706004156275977</v>
-      </c>
-      <c r="M11" t="inlineStr">
+        <v>2.121257</v>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>Fe-acac</t>
         </is>
       </c>
-      <c r="N11" t="n">
-        <v>0.6392303984879666</v>
+      <c r="M11" t="n">
+        <v>2.060342220000004</v>
       </c>
     </row>
     <row r="12">
@@ -1015,39 +980,36 @@
         <v>3.44</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>2.685</v>
       </c>
       <c r="F12" t="n">
-        <v>2.685</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>1.88</v>
       </c>
       <c r="H12" t="n">
-        <v>1.88</v>
+        <v>0.745</v>
       </c>
       <c r="I12" t="n">
-        <v>0.745</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K12" t="n">
-        <v>7</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.681983072916667</v>
-      </c>
-      <c r="M12" t="inlineStr">
+        <v>2.17946</v>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>Co-acac</t>
         </is>
       </c>
-      <c r="N12" t="n">
-        <v>0.6702102159124891</v>
+      <c r="M12" t="n">
+        <v>2.171825580000004</v>
       </c>
     </row>
     <row r="13">
@@ -1065,39 +1027,36 @@
         <v>3.44</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>1.818</v>
       </c>
       <c r="F13" t="n">
-        <v>1.818</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="H13" t="n">
         <v>1.1</v>
       </c>
       <c r="I13" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K13" t="n">
-        <v>10</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.678385159010601</v>
-      </c>
-      <c r="M13" t="inlineStr">
+        <v>2.70281</v>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>Cd-acac</t>
         </is>
       </c>
-      <c r="N13" t="n">
-        <v>0.7448791552588919</v>
+      <c r="M13" t="n">
+        <v>2.244602229999997</v>
       </c>
     </row>
     <row r="14">
@@ -1115,39 +1074,36 @@
         <v>3.44</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>3.509</v>
       </c>
       <c r="F14" t="n">
-        <v>3.509</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>1.9</v>
+        <v>0.57</v>
       </c>
       <c r="I14" t="n">
-        <v>0.57</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K14" t="n">
-        <v>9</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.67705421170012</v>
-      </c>
-      <c r="M14" t="inlineStr">
+        <v>1.706986</v>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>Cu-acac</t>
         </is>
       </c>
-      <c r="N14" t="n">
-        <v>0.66729011733773</v>
+      <c r="M14" t="n">
+        <v>1.686779487333331</v>
       </c>
     </row>
     <row r="15">
@@ -1165,39 +1121,36 @@
         <v>3.44</v>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>3.333</v>
       </c>
       <c r="F15" t="n">
-        <v>3.333</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="H15" t="n">
         <v>0.6</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K15" t="n">
-        <v>8</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.676983645983646</v>
-      </c>
-      <c r="M15" t="inlineStr">
+        <v>1.602375</v>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>Pt-acac</t>
         </is>
       </c>
-      <c r="N15" t="n">
-        <v>0.6741027876396519</v>
+      <c r="M15" t="n">
+        <v>1.682518849749998</v>
       </c>
     </row>
     <row r="16">
@@ -1215,39 +1168,36 @@
         <v>3.04</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>2.41</v>
       </c>
       <c r="F16" t="n">
-        <v>2.41</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="H16" t="n">
         <v>0.83</v>
       </c>
       <c r="I16" t="n">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K16" t="n">
-        <v>5</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.676076774862902</v>
-      </c>
-      <c r="M16" t="inlineStr">
+        <v>1.169628</v>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>Mn-phen</t>
         </is>
       </c>
-      <c r="N16" t="n">
-        <v>0.6342108052826548</v>
+      <c r="M16" t="n">
+        <v>1.238984808666664</v>
       </c>
     </row>
     <row r="17">
@@ -1265,39 +1215,36 @@
         <v>3.04</v>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>6.612</v>
       </c>
       <c r="F17" t="n">
-        <v>6.612</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>1.54</v>
       </c>
       <c r="H17" t="n">
-        <v>1.54</v>
+        <v>0.67</v>
       </c>
       <c r="I17" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.671348201011002</v>
-      </c>
-      <c r="M17" t="inlineStr">
+        <v>1.027571</v>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>Ti-phen</t>
         </is>
       </c>
-      <c r="N17" t="n">
-        <v>0.6106146820343197</v>
+      <c r="M17" t="n">
+        <v>1.093146494583332</v>
       </c>
     </row>
     <row r="18">
@@ -1315,39 +1262,36 @@
         <v>3.44</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>2.899</v>
       </c>
       <c r="F18" t="n">
-        <v>2.899</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>1.91</v>
       </c>
       <c r="H18" t="n">
-        <v>1.91</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K18" t="n">
-        <v>8</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.6567333333333329</v>
-      </c>
-      <c r="M18" t="inlineStr">
+        <v>2.131648</v>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>Ni-acac</t>
         </is>
       </c>
-      <c r="N18" t="n">
-        <v>0.6639730714790046</v>
+      <c r="M18" t="n">
+        <v>2.093686274999999</v>
       </c>
     </row>
     <row r="19">
@@ -1365,39 +1309,36 @@
         <v>3.04</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>2.703</v>
       </c>
       <c r="F19" t="n">
-        <v>2.703</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="H19" t="n">
         <v>0.74</v>
       </c>
       <c r="I19" t="n">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K19" t="n">
-        <v>10</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.6545588678109</v>
-      </c>
-      <c r="M19" t="inlineStr">
+        <v>1.118473</v>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>Zn-phen</t>
         </is>
       </c>
-      <c r="N19" t="n">
-        <v>0.6065714073706688</v>
+      <c r="M19" t="n">
+        <v>1.324663261666665</v>
       </c>
     </row>
     <row r="20">
@@ -1415,39 +1356,36 @@
         <v>3.44</v>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>3.046</v>
       </c>
       <c r="F20" t="n">
-        <v>3.046</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>0.985</v>
       </c>
       <c r="H20" t="n">
         <v>0.985</v>
       </c>
       <c r="I20" t="n">
-        <v>0.985</v>
+        <v>13</v>
       </c>
       <c r="J20" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0.64537899147522</v>
-      </c>
-      <c r="M20" t="inlineStr">
+        <v>2.556934</v>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>Yb-acac</t>
         </is>
       </c>
-      <c r="N20" t="n">
-        <v>0.6620860866500188</v>
+      <c r="M20" t="n">
+        <v>2.494475214999994</v>
       </c>
     </row>
     <row r="21">
@@ -1465,39 +1403,36 @@
         <v>3.44</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>2.41</v>
       </c>
       <c r="F21" t="n">
-        <v>2.41</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>1.55</v>
       </c>
       <c r="H21" t="n">
-        <v>1.55</v>
+        <v>0.83</v>
       </c>
       <c r="I21" t="n">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.642156855462705</v>
-      </c>
-      <c r="M21" t="inlineStr">
+        <v>2.156795</v>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>Mn-acac</t>
         </is>
       </c>
-      <c r="N21" t="n">
-        <v>0.648062857622019</v>
+      <c r="M21" t="n">
+        <v>2.111948335000003</v>
       </c>
     </row>
     <row r="22">
@@ -1515,39 +1450,36 @@
         <v>3.44</v>
       </c>
       <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4.412</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
         <v>6</v>
       </c>
-      <c r="E22" t="n">
-        <v>2</v>
-      </c>
-      <c r="F22" t="n">
-        <v>4.412</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
       <c r="K22" t="n">
-        <v>6</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0.641056378600823</v>
-      </c>
-      <c r="M22" t="inlineStr">
+        <v>2.136792</v>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>Ir-acac</t>
         </is>
       </c>
-      <c r="N22" t="n">
-        <v>0.646034175008964</v>
+      <c r="M22" t="n">
+        <v>2.073819760000005</v>
       </c>
     </row>
     <row r="23">
@@ -1565,39 +1497,36 @@
         <v>3.04</v>
       </c>
       <c r="D23" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>2.941</v>
       </c>
       <c r="F23" t="n">
-        <v>2.941</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="H23" t="n">
         <v>0.68</v>
       </c>
       <c r="I23" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K23" t="n">
-        <v>6</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0.6408996364785839</v>
-      </c>
-      <c r="M23" t="inlineStr">
+        <v>1.489393</v>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t>Ru-bpy</t>
         </is>
       </c>
-      <c r="N23" t="n">
-        <v>0.5575625776892523</v>
+      <c r="M23" t="n">
+        <v>1.34519161990476</v>
       </c>
     </row>
     <row r="24">
@@ -1615,39 +1544,36 @@
         <v>3.44</v>
       </c>
       <c r="D24" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>3.071</v>
       </c>
       <c r="F24" t="n">
-        <v>3.071</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0.977</v>
       </c>
       <c r="H24" t="n">
         <v>0.977</v>
       </c>
       <c r="I24" t="n">
-        <v>0.977</v>
+        <v>14</v>
       </c>
       <c r="J24" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0.63876898270302</v>
-      </c>
-      <c r="M24" t="inlineStr">
+        <v>2.580205</v>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>Lu-acac</t>
         </is>
       </c>
-      <c r="N24" t="n">
-        <v>0.6620860866500188</v>
+      <c r="M24" t="n">
+        <v>2.487813434999994</v>
       </c>
     </row>
     <row r="25">
@@ -1665,39 +1591,36 @@
         <v>3.44</v>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>2.778</v>
       </c>
       <c r="F25" t="n">
-        <v>2.778</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>1.31</v>
       </c>
       <c r="H25" t="n">
-        <v>1.31</v>
+        <v>0.72</v>
       </c>
       <c r="I25" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0.636899705014749</v>
-      </c>
-      <c r="M25" t="inlineStr">
+        <v>2.168522</v>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>Mg-acac</t>
         </is>
       </c>
-      <c r="N25" t="n">
-        <v>0.6425847196123533</v>
+      <c r="M25" t="n">
+        <v>2.157215669999999</v>
       </c>
     </row>
     <row r="26">
@@ -1715,13 +1638,13 @@
         <v>3.44</v>
       </c>
       <c r="D26" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
         <v>2</v>
       </c>
       <c r="F26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
@@ -1730,24 +1653,21 @@
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0.636039596832253</v>
-      </c>
-      <c r="M26" t="inlineStr">
+        <v>2.163146</v>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>Ca-acac</t>
         </is>
       </c>
-      <c r="N26" t="n">
-        <v>0.6589901448962939</v>
+      <c r="M26" t="n">
+        <v>2.257774734999997</v>
       </c>
     </row>
     <row r="27">
@@ -1765,39 +1685,36 @@
         <v>3.44</v>
       </c>
       <c r="D27" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>4.878</v>
       </c>
       <c r="F27" t="n">
-        <v>4.878</v>
+        <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>1.66</v>
       </c>
       <c r="H27" t="n">
-        <v>1.66</v>
+        <v>0.615</v>
       </c>
       <c r="I27" t="n">
-        <v>0.615</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K27" t="n">
-        <v>3</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0.634438363171355</v>
-      </c>
-      <c r="M27" t="inlineStr">
+        <v>2.142304</v>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>Cr-acac</t>
         </is>
       </c>
-      <c r="N27" t="n">
-        <v>0.6322682990404656</v>
+      <c r="M27" t="n">
+        <v>2.05164653166667</v>
       </c>
     </row>
     <row r="28">
@@ -1815,39 +1732,36 @@
         <v>3.44</v>
       </c>
       <c r="D28" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>2.625</v>
       </c>
       <c r="F28" t="n">
-        <v>2.625</v>
+        <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="H28" t="n">
-        <v>1.12</v>
+        <v>0.97</v>
       </c>
       <c r="I28" t="n">
-        <v>0.97</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0.631431592576608</v>
-      </c>
-      <c r="M28" t="inlineStr">
+        <v>2.534345</v>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t>Ce-acac</t>
         </is>
       </c>
-      <c r="N28" t="n">
-        <v>0.6523985802263057</v>
+      <c r="M28" t="n">
+        <v>2.429245519999998</v>
       </c>
     </row>
     <row r="29">
@@ -1865,39 +1779,36 @@
         <v>3.44</v>
       </c>
       <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>4.412</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
         <v>6</v>
       </c>
-      <c r="E29" t="n">
-        <v>2</v>
-      </c>
-      <c r="F29" t="n">
-        <v>4.412</v>
-      </c>
-      <c r="G29" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
       <c r="K29" t="n">
-        <v>6</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0.63141768172888</v>
-      </c>
-      <c r="M29" t="inlineStr">
+        <v>2.125508</v>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t>Ru-acac</t>
         </is>
       </c>
-      <c r="N29" t="n">
-        <v>0.646034175008964</v>
+      <c r="M29" t="n">
+        <v>2.073819760000005</v>
       </c>
     </row>
     <row r="30">
@@ -1915,39 +1826,36 @@
         <v>3.44</v>
       </c>
       <c r="D30" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>6.757</v>
       </c>
       <c r="F30" t="n">
-        <v>6.757</v>
+        <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="H30" t="n">
         <v>0.74</v>
       </c>
       <c r="I30" t="n">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0.631159565980533</v>
-      </c>
-      <c r="M30" t="inlineStr">
+        <v>2.532645</v>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t>Nb-acac</t>
         </is>
       </c>
-      <c r="N30" t="n">
-        <v>0.6373242669165448</v>
+      <c r="M30" t="n">
+        <v>2.330184813750001</v>
       </c>
     </row>
     <row r="31">
@@ -1965,39 +1873,36 @@
         <v>3.44</v>
       </c>
       <c r="D31" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>2.956</v>
       </c>
       <c r="F31" t="n">
-        <v>2.956</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>1.015</v>
       </c>
       <c r="H31" t="n">
         <v>1.015</v>
       </c>
       <c r="I31" t="n">
-        <v>1.015</v>
+        <v>10</v>
       </c>
       <c r="J31" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0.630859115243731</v>
-      </c>
-      <c r="M31" t="inlineStr">
+        <v>2.530767</v>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t>Ho-acac</t>
         </is>
       </c>
-      <c r="N31" t="n">
-        <v>0.6706065580462303</v>
+      <c r="M31" t="n">
+        <v>2.533624240000006</v>
       </c>
     </row>
     <row r="32">
@@ -2015,39 +1920,36 @@
         <v>3.04</v>
       </c>
       <c r="D32" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E32" t="n">
-        <v>3</v>
+        <v>2.679</v>
       </c>
       <c r="F32" t="n">
-        <v>2.679</v>
+        <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="H32" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="I32" t="n">
-        <v>1.12</v>
+        <v>6</v>
       </c>
       <c r="J32" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0.627956956576782</v>
-      </c>
-      <c r="M32" t="inlineStr">
+        <v>1.799442</v>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t>Eu-tpy</t>
         </is>
       </c>
-      <c r="N32" t="n">
-        <v>0.5918691972062565</v>
+      <c r="M32" t="n">
+        <v>1.817770502500001</v>
       </c>
     </row>
     <row r="33">
@@ -2065,39 +1967,36 @@
         <v>3.44</v>
       </c>
       <c r="D33" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>6.612</v>
       </c>
       <c r="F33" t="n">
-        <v>6.612</v>
+        <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>1.54</v>
       </c>
       <c r="H33" t="n">
-        <v>1.54</v>
+        <v>0.605</v>
       </c>
       <c r="I33" t="n">
-        <v>0.605</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0.6209140211640209</v>
-      </c>
-      <c r="M33" t="inlineStr">
+        <v>2.068608</v>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t>Ti-acac</t>
         </is>
       </c>
-      <c r="N33" t="n">
-        <v>0.6234722347020699</v>
+      <c r="M33" t="n">
+        <v>2.004730914999999</v>
       </c>
     </row>
     <row r="34">
@@ -2115,39 +2014,36 @@
         <v>3.44</v>
       </c>
       <c r="D34" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>2</v>
+        <v>5.66</v>
       </c>
       <c r="F34" t="n">
-        <v>5.66</v>
+        <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>1.63</v>
       </c>
       <c r="H34" t="n">
-        <v>1.63</v>
+        <v>0.53</v>
       </c>
       <c r="I34" t="n">
-        <v>0.53</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>1</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0.62074561049445</v>
-      </c>
-      <c r="M34" t="inlineStr">
+        <v>1.82443</v>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t>V-acac</t>
         </is>
       </c>
-      <c r="N34" t="n">
-        <v>0.6255440502057072</v>
+      <c r="M34" t="n">
+        <v>1.804944639000003</v>
       </c>
     </row>
     <row r="35">
@@ -2165,39 +2061,36 @@
         <v>3.04</v>
       </c>
       <c r="D35" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E35" t="n">
-        <v>3</v>
+        <v>5.556</v>
       </c>
       <c r="F35" t="n">
-        <v>5.556</v>
+        <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="H35" t="n">
-        <v>1.33</v>
+        <v>0.72</v>
       </c>
       <c r="I35" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0.619316717237393</v>
-      </c>
-      <c r="M35" t="inlineStr">
+        <v>1.126688</v>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t>Zr-tpy</t>
         </is>
       </c>
-      <c r="N35" t="n">
-        <v>0.5706068037823029</v>
+      <c r="M35" t="n">
+        <v>1.088459400416668</v>
       </c>
     </row>
     <row r="36">
@@ -2215,39 +2108,36 @@
         <v>3.04</v>
       </c>
       <c r="D36" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2</v>
+        <v>2.814</v>
       </c>
       <c r="F36" t="n">
-        <v>2.814</v>
+        <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>1.066</v>
       </c>
       <c r="H36" t="n">
         <v>1.066</v>
       </c>
       <c r="I36" t="n">
-        <v>1.066</v>
+        <v>6</v>
       </c>
       <c r="J36" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0.616603970741902</v>
-      </c>
-      <c r="M36" t="inlineStr">
+        <v>1.510422</v>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t>Eu-phen</t>
         </is>
       </c>
-      <c r="N36" t="n">
-        <v>0.5906476988179326</v>
+      <c r="M36" t="n">
+        <v>1.544629370333336</v>
       </c>
     </row>
     <row r="37">
@@ -2265,39 +2155,36 @@
         <v>3.44</v>
       </c>
       <c r="D37" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>2</v>
+        <v>5.556</v>
       </c>
       <c r="F37" t="n">
-        <v>5.556</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="H37" t="n">
         <v>0.72</v>
       </c>
       <c r="I37" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0.615964757709251</v>
-      </c>
-      <c r="M37" t="inlineStr">
+        <v>0.835874</v>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t>Zr-cooh</t>
         </is>
       </c>
-      <c r="N37" t="n">
-        <v>0.5750869748584927</v>
+      <c r="M37" t="n">
+        <v>1.087248401999998</v>
       </c>
     </row>
     <row r="38">
@@ -2315,39 +2202,36 @@
         <v>3.44</v>
       </c>
       <c r="D38" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>2</v>
+        <v>2.74</v>
       </c>
       <c r="F38" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="H38" t="n">
-        <v>1.2</v>
+        <v>1.095</v>
       </c>
       <c r="I38" t="n">
-        <v>1.095</v>
+        <v>8</v>
       </c>
       <c r="J38" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0.600494728304947</v>
-      </c>
-      <c r="M38" t="inlineStr">
+        <v>2.00169</v>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t>Tb-cooh</t>
         </is>
       </c>
-      <c r="N38" t="n">
-        <v>0.5843801102859909</v>
+      <c r="M38" t="n">
+        <v>2.039399342999998</v>
       </c>
     </row>
     <row r="39">
@@ -2365,39 +2249,36 @@
         <v>3.04</v>
       </c>
       <c r="D39" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2</v>
+        <v>5.556</v>
       </c>
       <c r="F39" t="n">
-        <v>5.556</v>
+        <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>0.72</v>
       </c>
       <c r="H39" t="n">
         <v>0.72</v>
       </c>
       <c r="I39" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0.598068595927117</v>
-      </c>
-      <c r="M39" t="inlineStr">
+        <v>1.200858</v>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t>Zr-bpy</t>
         </is>
       </c>
-      <c r="N39" t="n">
-        <v>0.5074703547007139</v>
+      <c r="M39" t="n">
+        <v>0.9823297272500018</v>
       </c>
     </row>
     <row r="40">
@@ -2415,39 +2296,36 @@
         <v>3.44</v>
       </c>
       <c r="D40" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E40" t="n">
-        <v>2</v>
+        <v>2.74</v>
       </c>
       <c r="F40" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="H40" t="n">
-        <v>1.2</v>
+        <v>1.095</v>
       </c>
       <c r="I40" t="n">
-        <v>1.095</v>
+        <v>8</v>
       </c>
       <c r="J40" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0.596475177304965</v>
-      </c>
-      <c r="M40" t="inlineStr">
+        <v>2.103654</v>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t>Tb-cooh</t>
         </is>
       </c>
-      <c r="N40" t="n">
-        <v>0.5843801102859909</v>
+      <c r="M40" t="n">
+        <v>2.039399342999998</v>
       </c>
     </row>
     <row r="41">
@@ -2465,39 +2343,36 @@
         <v>3.04</v>
       </c>
       <c r="D41" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E41" t="n">
-        <v>2</v>
+        <v>4.412</v>
       </c>
       <c r="F41" t="n">
-        <v>4.412</v>
+        <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="H41" t="n">
         <v>0.68</v>
       </c>
       <c r="I41" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K41" t="n">
-        <v>6</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0.585327218641547</v>
-      </c>
-      <c r="M41" t="inlineStr">
+        <v>1.585818</v>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t>Ir-bpy</t>
         </is>
       </c>
-      <c r="N41" t="n">
-        <v>0.5286205539255839</v>
+      <c r="M41" t="n">
+        <v>1.335918219999998</v>
       </c>
     </row>
     <row r="42">
@@ -2515,39 +2390,36 @@
         <v>3.04</v>
       </c>
       <c r="D42" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2</v>
+        <v>2.105</v>
       </c>
       <c r="F42" t="n">
-        <v>2.105</v>
+        <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H42" t="n">
         <v>0.95</v>
       </c>
       <c r="I42" t="n">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K42" t="n">
-        <v>10</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0.575463347763348</v>
-      </c>
-      <c r="M42" t="inlineStr">
+        <v>1.54896</v>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t>Cd-bpy</t>
         </is>
       </c>
-      <c r="N42" t="n">
-        <v>0.5567211596467514</v>
+      <c r="M42" t="n">
+        <v>1.460513719761905</v>
       </c>
     </row>
     <row r="43">
@@ -2565,39 +2437,36 @@
         <v>3.04</v>
       </c>
       <c r="D43" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E43" t="n">
-        <v>2</v>
+        <v>2.703</v>
       </c>
       <c r="F43" t="n">
-        <v>2.703</v>
+        <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="H43" t="n">
         <v>0.74</v>
       </c>
       <c r="I43" t="n">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K43" t="n">
-        <v>10</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0.5702829967120711</v>
-      </c>
-      <c r="M43" t="inlineStr">
+        <v>1.528249</v>
+      </c>
+      <c r="L43" t="inlineStr">
         <is>
           <t>Zn-bpy</t>
         </is>
       </c>
-      <c r="N43" t="n">
-        <v>0.6065714073706688</v>
+      <c r="M43" t="n">
+        <v>1.324663261666665</v>
       </c>
     </row>
     <row r="44">
@@ -2615,39 +2484,36 @@
         <v>3.04</v>
       </c>
       <c r="D44" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>2</v>
+        <v>2.814</v>
       </c>
       <c r="F44" t="n">
-        <v>2.814</v>
+        <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="H44" t="n">
-        <v>1.2</v>
+        <v>1.066</v>
       </c>
       <c r="I44" t="n">
-        <v>1.066</v>
+        <v>6</v>
       </c>
       <c r="J44" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0.55619877675841</v>
-      </c>
-      <c r="M44" t="inlineStr">
+        <v>1.787093</v>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t>Eu-bpy</t>
         </is>
       </c>
-      <c r="N44" t="n">
-        <v>0.564719685772969</v>
+      <c r="M44" t="n">
+        <v>1.729923306666671</v>
       </c>
     </row>
     <row r="45">
@@ -2665,39 +2531,36 @@
         <v>3.04</v>
       </c>
       <c r="D45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2</v>
+        <v>3.333</v>
       </c>
       <c r="F45" t="n">
-        <v>3.333</v>
+        <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="H45" t="n">
         <v>0.6</v>
       </c>
       <c r="I45" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K45" t="n">
-        <v>8</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0.553275132275132</v>
-      </c>
-      <c r="M45" t="inlineStr">
+        <v>1.104241</v>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t>Pt-bpy</t>
         </is>
       </c>
-      <c r="N45" t="n">
-        <v>0.5084224796098412</v>
+      <c r="M45" t="n">
+        <v>0.8950157507857142</v>
       </c>
     </row>
     <row r="46">
@@ -2715,39 +2578,36 @@
         <v>3.04</v>
       </c>
       <c r="D46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E46" t="n">
+        <v>3.279</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
         <v>6</v>
       </c>
-      <c r="E46" t="n">
-        <v>2</v>
-      </c>
-      <c r="F46" t="n">
-        <v>3.279</v>
-      </c>
-      <c r="G46" t="n">
-        <v>1</v>
-      </c>
-      <c r="H46" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
       <c r="K46" t="n">
-        <v>6</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0.5402997626314</v>
-      </c>
-      <c r="M46" t="inlineStr">
+        <v>1.56898</v>
+      </c>
+      <c r="L46" t="inlineStr">
         <is>
           <t>Fe-bpy</t>
         </is>
       </c>
-      <c r="N46" t="n">
-        <v>0.5182473606288405</v>
+      <c r="M46" t="n">
+        <v>1.396729021333336</v>
       </c>
     </row>
     <row r="47">
@@ -2765,39 +2625,36 @@
         <v>3.04</v>
       </c>
       <c r="D47" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E47" t="n">
-        <v>2</v>
+        <v>2.899</v>
       </c>
       <c r="F47" t="n">
-        <v>2.899</v>
+        <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>1.91</v>
       </c>
       <c r="H47" t="n">
-        <v>1.91</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I47" t="n">
-        <v>0.6899999999999999</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K47" t="n">
-        <v>8</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0.537283864921635</v>
-      </c>
-      <c r="M47" t="inlineStr">
+        <v>1.54663</v>
+      </c>
+      <c r="L47" t="inlineStr">
         <is>
           <t>Ni-bpy</t>
         </is>
       </c>
-      <c r="N47" t="n">
-        <v>0.4924281806592474</v>
+      <c r="M47" t="n">
+        <v>1.232314421571427</v>
       </c>
     </row>
     <row r="48">
@@ -2815,39 +2672,36 @@
         <v>3.04</v>
       </c>
       <c r="D48" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2</v>
+        <v>4.878</v>
       </c>
       <c r="F48" t="n">
-        <v>4.878</v>
+        <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>1.66</v>
       </c>
       <c r="H48" t="n">
-        <v>1.66</v>
+        <v>0.615</v>
       </c>
       <c r="I48" t="n">
-        <v>0.615</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K48" t="n">
-        <v>3</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0.531573148606301</v>
-      </c>
-      <c r="M48" t="inlineStr">
+        <v>1.514437</v>
+      </c>
+      <c r="L48" t="inlineStr">
         <is>
           <t>Cr-bpy</t>
         </is>
       </c>
-      <c r="N48" t="n">
-        <v>0.4933603810452006</v>
+      <c r="M48" t="n">
+        <v>1.27054676972619</v>
       </c>
     </row>
     <row r="49">
@@ -2865,39 +2719,36 @@
         <v>3.04</v>
       </c>
       <c r="D49" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>3.046</v>
       </c>
       <c r="F49" t="n">
-        <v>3.046</v>
+        <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>0.985</v>
       </c>
       <c r="H49" t="n">
         <v>0.985</v>
       </c>
       <c r="I49" t="n">
-        <v>0.985</v>
+        <v>13</v>
       </c>
       <c r="J49" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0.528772277227723</v>
-      </c>
-      <c r="M49" t="inlineStr">
+        <v>1.792761</v>
+      </c>
+      <c r="L49" t="inlineStr">
         <is>
           <t>Yb-bpy</t>
         </is>
       </c>
-      <c r="N49" t="n">
-        <v>0.5111216815422869</v>
+      <c r="M49" t="n">
+        <v>1.716601411333334</v>
       </c>
     </row>
     <row r="50">
@@ -2915,39 +2766,36 @@
         <v>3.04</v>
       </c>
       <c r="D50" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E50" t="n">
-        <v>2</v>
+        <v>4.511</v>
       </c>
       <c r="F50" t="n">
-        <v>4.511</v>
+        <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>0.665</v>
       </c>
       <c r="H50" t="n">
         <v>0.665</v>
       </c>
       <c r="I50" t="n">
-        <v>0.665</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K50" t="n">
-        <v>6</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0.528337164750958</v>
-      </c>
-      <c r="M50" t="inlineStr">
+        <v>1.410876</v>
+      </c>
+      <c r="L50" t="inlineStr">
         <is>
           <t>Rh-bpy</t>
         </is>
       </c>
-      <c r="N50" t="n">
-        <v>0.500229959023833</v>
+      <c r="M50" t="n">
+        <v>1.219000210416667</v>
       </c>
     </row>
     <row r="51">
@@ -2965,39 +2813,36 @@
         <v>3.04</v>
       </c>
       <c r="D51" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2</v>
+        <v>2.105</v>
       </c>
       <c r="F51" t="n">
-        <v>2.105</v>
+        <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H51" t="n">
         <v>0.95</v>
       </c>
       <c r="I51" t="n">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K51" t="n">
-        <v>10</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0.528135206869633</v>
-      </c>
-      <c r="M51" t="inlineStr">
+        <v>1.4</v>
+      </c>
+      <c r="L51" t="inlineStr">
         <is>
           <t>Cd-phen</t>
         </is>
       </c>
-      <c r="N51" t="n">
-        <v>0.5567211596467514</v>
+      <c r="M51" t="n">
+        <v>1.460513719761905</v>
       </c>
     </row>
     <row r="52">
@@ -3015,39 +2860,36 @@
         <v>3.04</v>
       </c>
       <c r="D52" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E52" t="n">
-        <v>2</v>
+        <v>2.532</v>
       </c>
       <c r="F52" t="n">
-        <v>2.532</v>
+        <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>1</v>
+        <v>1.63</v>
       </c>
       <c r="H52" t="n">
-        <v>1.63</v>
+        <v>0.79</v>
       </c>
       <c r="I52" t="n">
-        <v>0.79</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K52" t="n">
-        <v>3</v>
-      </c>
-      <c r="L52" t="n">
-        <v>0.5277809867629361</v>
-      </c>
-      <c r="M52" t="inlineStr">
+        <v>1.490735</v>
+      </c>
+      <c r="L52" t="inlineStr">
         <is>
           <t>V-bpy</t>
         </is>
       </c>
-      <c r="N52" t="n">
-        <v>0.4964307818269875</v>
+      <c r="M52" t="n">
+        <v>1.270439217809523</v>
       </c>
     </row>
     <row r="53">
@@ -3065,39 +2907,36 @@
         <v>3.04</v>
       </c>
       <c r="D53" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E53" t="n">
-        <v>2</v>
+        <v>3.75</v>
       </c>
       <c r="F53" t="n">
-        <v>3.75</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="H53" t="n">
         <v>0.8</v>
       </c>
       <c r="I53" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K53" t="n">
-        <v>10</v>
-      </c>
-      <c r="L53" t="n">
-        <v>0.52730252729176</v>
-      </c>
-      <c r="M53" t="inlineStr">
+        <v>1.487745</v>
+      </c>
+      <c r="L53" t="inlineStr">
         <is>
           <t>In-bpy</t>
         </is>
       </c>
-      <c r="N53" t="n">
-        <v>0.5421789375286786</v>
+      <c r="M53" t="n">
+        <v>1.227699638333333</v>
       </c>
     </row>
     <row r="54">
@@ -3115,39 +2954,36 @@
         <v>3.04</v>
       </c>
       <c r="D54" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2</v>
+        <v>1.786</v>
       </c>
       <c r="F54" t="n">
-        <v>1.786</v>
+        <v>1</v>
       </c>
       <c r="G54" t="n">
         <v>1</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="I54" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="n">
-        <v>0.5254021101992969</v>
-      </c>
-      <c r="M54" t="inlineStr">
+        <v>1.875867</v>
+      </c>
+      <c r="L54" t="inlineStr">
         <is>
           <t>Ca-bpy</t>
         </is>
       </c>
-      <c r="N54" t="n">
-        <v>0.5299540311367741</v>
+      <c r="M54" t="n">
+        <v>1.776833026428576</v>
       </c>
     </row>
     <row r="55">
@@ -3165,39 +3001,36 @@
         <v>3.44</v>
       </c>
       <c r="D55" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E55" t="n">
-        <v>2</v>
+        <v>2.58</v>
       </c>
       <c r="F55" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>1.163</v>
       </c>
       <c r="H55" t="n">
         <v>1.163</v>
       </c>
       <c r="I55" t="n">
-        <v>1.163</v>
+        <v>3</v>
       </c>
       <c r="J55" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="n">
-        <v>0.523848238482385</v>
-      </c>
-      <c r="M55" t="inlineStr">
+        <v>2.064318</v>
+      </c>
+      <c r="L55" t="inlineStr">
         <is>
           <t>Nd-cooh</t>
         </is>
       </c>
-      <c r="N55" t="n">
-        <v>0.5193895739791092</v>
+      <c r="M55" t="n">
+        <v>2.032157120000007</v>
       </c>
     </row>
     <row r="56">
@@ -3215,39 +3048,36 @@
         <v>3.44</v>
       </c>
       <c r="D56" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E56" t="n">
         <v>2</v>
       </c>
       <c r="F56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56" t="n">
         <v>1</v>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" t="n">
-        <v>0.523686190066035</v>
-      </c>
-      <c r="M56" t="inlineStr">
+        <v>1.444555</v>
+      </c>
+      <c r="L56" t="inlineStr">
         <is>
           <t>Ca-cooh</t>
         </is>
       </c>
-      <c r="N56" t="n">
-        <v>0.5166760655294695</v>
+      <c r="M56" t="n">
+        <v>1.608147959999999</v>
       </c>
     </row>
     <row r="57">
@@ -3265,39 +3095,36 @@
         <v>3.04</v>
       </c>
       <c r="D57" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2</v>
+        <v>3.077</v>
       </c>
       <c r="F57" t="n">
-        <v>3.077</v>
+        <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>1</v>
+        <v>1.88</v>
       </c>
       <c r="H57" t="n">
-        <v>1.88</v>
+        <v>0.65</v>
       </c>
       <c r="I57" t="n">
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K57" t="n">
-        <v>7</v>
-      </c>
-      <c r="L57" t="n">
-        <v>0.523298449612403</v>
-      </c>
-      <c r="M57" t="inlineStr">
+        <v>1.420009</v>
+      </c>
+      <c r="L57" t="inlineStr">
         <is>
           <t>Co-bpy</t>
         </is>
       </c>
-      <c r="N57" t="n">
-        <v>0.4851403060520275</v>
+      <c r="M57" t="n">
+        <v>1.177943363916665</v>
       </c>
     </row>
     <row r="58">
@@ -3315,39 +3142,36 @@
         <v>3.44</v>
       </c>
       <c r="D58" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E58" t="n">
-        <v>2</v>
+        <v>2.778</v>
       </c>
       <c r="F58" t="n">
-        <v>2.778</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="H58" t="n">
-        <v>1.31</v>
+        <v>0.72</v>
       </c>
       <c r="I58" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="n">
-        <v>0.52152886405959</v>
-      </c>
-      <c r="M58" t="inlineStr">
+        <v>1.431071</v>
+      </c>
+      <c r="L58" t="inlineStr">
         <is>
           <t>Mg-cooh</t>
         </is>
       </c>
-      <c r="N58" t="n">
-        <v>0.5132330493650481</v>
+      <c r="M58" t="n">
+        <v>1.392345855</v>
       </c>
     </row>
     <row r="59">
@@ -3365,39 +3189,36 @@
         <v>3.44</v>
       </c>
       <c r="D59" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E59" t="n">
-        <v>2</v>
+        <v>3.333</v>
       </c>
       <c r="F59" t="n">
-        <v>3.333</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="H59" t="n">
-        <v>1.65</v>
+        <v>0.6</v>
       </c>
       <c r="I59" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K59" t="n">
-        <v>10</v>
-      </c>
-      <c r="L59" t="n">
-        <v>0.520119132350449</v>
-      </c>
-      <c r="M59" t="inlineStr">
+        <v>1.001426</v>
+      </c>
+      <c r="L59" t="inlineStr">
         <is>
           <t>Zn-cooh</t>
         </is>
       </c>
-      <c r="N59" t="n">
-        <v>0.5158422844137636</v>
+      <c r="M59" t="n">
+        <v>1.036477192500002</v>
       </c>
     </row>
     <row r="60">
@@ -3415,39 +3236,36 @@
         <v>3.44</v>
       </c>
       <c r="D60" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2</v>
+        <v>2.685</v>
       </c>
       <c r="F60" t="n">
-        <v>2.685</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="H60" t="n">
-        <v>1.88</v>
+        <v>0.745</v>
       </c>
       <c r="I60" t="n">
-        <v>0.745</v>
+        <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K60" t="n">
-        <v>7</v>
-      </c>
-      <c r="L60" t="n">
-        <v>0.520066795366795</v>
-      </c>
-      <c r="M60" t="inlineStr">
+        <v>1.442559</v>
+      </c>
+      <c r="L60" t="inlineStr">
         <is>
           <t>Co-cooh</t>
         </is>
       </c>
-      <c r="N60" t="n">
-        <v>0.5179155586069684</v>
+      <c r="M60" t="n">
+        <v>1.420292749999998</v>
       </c>
     </row>
     <row r="61">
@@ -3465,39 +3283,36 @@
         <v>3.04</v>
       </c>
       <c r="D61" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E61" t="n">
-        <v>2</v>
+        <v>2.625</v>
       </c>
       <c r="F61" t="n">
-        <v>2.625</v>
+        <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>1</v>
+        <v>1.143</v>
       </c>
       <c r="H61" t="n">
         <v>1.143</v>
       </c>
       <c r="I61" t="n">
-        <v>1.143</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" t="n">
-        <v>0.519119219561637</v>
-      </c>
-      <c r="M61" t="inlineStr">
+        <v>1.836598</v>
+      </c>
+      <c r="L61" t="inlineStr">
         <is>
           <t>Ce-bpy</t>
         </is>
       </c>
-      <c r="N61" t="n">
-        <v>0.4917150286691034</v>
+      <c r="M61" t="n">
+        <v>1.642977390345236</v>
       </c>
     </row>
     <row r="62">
@@ -3515,39 +3330,36 @@
         <v>3.44</v>
       </c>
       <c r="D62" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E62" t="n">
-        <v>2</v>
+        <v>2.907</v>
       </c>
       <c r="F62" t="n">
-        <v>2.907</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="H62" t="n">
-        <v>1.27</v>
+        <v>1.032</v>
       </c>
       <c r="I62" t="n">
-        <v>1.032</v>
+        <v>14</v>
       </c>
       <c r="J62" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="n">
-        <v>0.518162515829464</v>
-      </c>
-      <c r="M62" t="inlineStr">
+        <v>2.030865</v>
+      </c>
+      <c r="L62" t="inlineStr">
         <is>
           <t>Lu-cooh</t>
         </is>
       </c>
-      <c r="N62" t="n">
-        <v>0.5165517512014305</v>
+      <c r="M62" t="n">
+        <v>2.02437581</v>
       </c>
     </row>
     <row r="63">
@@ -3565,39 +3377,36 @@
         <v>3.44</v>
       </c>
       <c r="D63" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2</v>
+        <v>2.65</v>
       </c>
       <c r="F63" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="H63" t="n">
-        <v>1.17</v>
+        <v>1.132</v>
       </c>
       <c r="I63" t="n">
-        <v>1.132</v>
+        <v>5</v>
       </c>
       <c r="J63" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" t="n">
-        <v>0.5171961414791</v>
-      </c>
-      <c r="M63" t="inlineStr">
+        <v>2.014408</v>
+      </c>
+      <c r="L63" t="inlineStr">
         <is>
           <t>Sm-cooh</t>
         </is>
       </c>
-      <c r="N63" t="n">
-        <v>0.5179497407584318</v>
+      <c r="M63" t="n">
+        <v>2.012005377000002</v>
       </c>
     </row>
     <row r="64">
@@ -3615,39 +3424,36 @@
         <v>3.44</v>
       </c>
       <c r="D64" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E64" t="n">
-        <v>2</v>
+        <v>2.899</v>
       </c>
       <c r="F64" t="n">
-        <v>2.899</v>
+        <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="H64" t="n">
-        <v>1.91</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I64" t="n">
-        <v>0.6899999999999999</v>
+        <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K64" t="n">
-        <v>8</v>
-      </c>
-      <c r="L64" t="n">
-        <v>0.516693784756297</v>
-      </c>
-      <c r="M64" t="inlineStr">
+        <v>1.421477</v>
+      </c>
+      <c r="L64" t="inlineStr">
         <is>
           <t>Ni-cooh</t>
         </is>
       </c>
-      <c r="N64" t="n">
-        <v>0.5150750210870919</v>
+      <c r="M64" t="n">
+        <v>1.398795245000001</v>
       </c>
     </row>
     <row r="65">
@@ -3665,39 +3471,36 @@
         <v>3.04</v>
       </c>
       <c r="D65" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E65" t="n">
-        <v>2</v>
+        <v>2.586</v>
       </c>
       <c r="F65" t="n">
-        <v>2.586</v>
+        <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>1</v>
+        <v>1.16</v>
       </c>
       <c r="H65" t="n">
         <v>1.16</v>
       </c>
       <c r="I65" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" t="n">
-        <v>0.516547021356313</v>
-      </c>
-      <c r="M65" t="inlineStr">
+        <v>1.820521</v>
+      </c>
+      <c r="L65" t="inlineStr">
         <is>
           <t>La-bpy</t>
         </is>
       </c>
-      <c r="N65" t="n">
-        <v>0.4969534807220833</v>
+      <c r="M65" t="n">
+        <v>1.678677425559523</v>
       </c>
     </row>
     <row r="66">
@@ -3715,39 +3518,36 @@
         <v>3.44</v>
       </c>
       <c r="D66" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2</v>
+        <v>2.508</v>
       </c>
       <c r="F66" t="n">
-        <v>2.508</v>
+        <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="H66" t="n">
-        <v>1.12</v>
+        <v>1.196</v>
       </c>
       <c r="I66" t="n">
-        <v>1.196</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" t="n">
-        <v>0.516177083333333</v>
-      </c>
-      <c r="M66" t="inlineStr">
+        <v>2.008039</v>
+      </c>
+      <c r="L66" t="inlineStr">
         <is>
           <t>Ce-cooh</t>
         </is>
       </c>
-      <c r="N66" t="n">
-        <v>0.511618231438342</v>
+      <c r="M66" t="n">
+        <v>1.871279280000001</v>
       </c>
     </row>
     <row r="67">
@@ -3765,39 +3565,36 @@
         <v>3.04</v>
       </c>
       <c r="D67" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E67" t="n">
-        <v>2</v>
+        <v>2.988</v>
       </c>
       <c r="F67" t="n">
-        <v>2.988</v>
+        <v>1</v>
       </c>
       <c r="G67" t="n">
-        <v>1</v>
+        <v>1.004</v>
       </c>
       <c r="H67" t="n">
         <v>1.004</v>
       </c>
       <c r="I67" t="n">
-        <v>1.004</v>
+        <v>11</v>
       </c>
       <c r="J67" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" t="n">
-        <v>0.515907223326706</v>
-      </c>
-      <c r="M67" t="inlineStr">
+        <v>1.816522</v>
+      </c>
+      <c r="L67" t="inlineStr">
         <is>
           <t>Er-bpy</t>
         </is>
       </c>
-      <c r="N67" t="n">
-        <v>0.4716890769333375</v>
+      <c r="M67" t="n">
+        <v>1.553205430666668</v>
       </c>
     </row>
     <row r="68">
@@ -3815,39 +3612,36 @@
         <v>3.44</v>
       </c>
       <c r="D68" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E68" t="n">
-        <v>2</v>
+        <v>2.467</v>
       </c>
       <c r="F68" t="n">
-        <v>2.467</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="H68" t="n">
-        <v>1.1</v>
+        <v>1.216</v>
       </c>
       <c r="I68" t="n">
-        <v>1.216</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" t="n">
-        <v>0.515814526588846</v>
-      </c>
-      <c r="M68" t="inlineStr">
+        <v>2.01619</v>
+      </c>
+      <c r="L68" t="inlineStr">
         <is>
           <t>La-cooh</t>
         </is>
       </c>
-      <c r="N68" t="n">
-        <v>0.5112231305215486</v>
+      <c r="M68" t="n">
+        <v>1.856169095</v>
       </c>
     </row>
     <row r="69">
@@ -3865,39 +3659,36 @@
         <v>3.04</v>
       </c>
       <c r="D69" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E69" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="F69" t="n">
-        <v>2.65</v>
+        <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="H69" t="n">
-        <v>1.17</v>
+        <v>1.132</v>
       </c>
       <c r="I69" t="n">
-        <v>1.132</v>
+        <v>5</v>
       </c>
       <c r="J69" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" t="n">
-        <v>0.515556193472277</v>
-      </c>
-      <c r="M69" t="inlineStr">
+        <v>1.881522</v>
+      </c>
+      <c r="L69" t="inlineStr">
         <is>
           <t>Sm-tpy</t>
         </is>
       </c>
-      <c r="N69" t="n">
-        <v>0.5162486795852929</v>
+      <c r="M69" t="n">
+        <v>1.846954179000003</v>
       </c>
     </row>
     <row r="70">
@@ -3915,39 +3706,36 @@
         <v>3.44</v>
       </c>
       <c r="D70" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E70" t="n">
-        <v>2</v>
+        <v>4.651</v>
       </c>
       <c r="F70" t="n">
-        <v>4.651</v>
+        <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="H70" t="n">
-        <v>1.83</v>
+        <v>0.645</v>
       </c>
       <c r="I70" t="n">
-        <v>0.645</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K70" t="n">
-        <v>5</v>
-      </c>
-      <c r="L70" t="n">
-        <v>0.515533333333333</v>
-      </c>
-      <c r="M70" t="inlineStr">
+        <v>1.414224</v>
+      </c>
+      <c r="L70" t="inlineStr">
         <is>
           <t>Fe-cooh</t>
         </is>
       </c>
-      <c r="N70" t="n">
-        <v>0.5144914034805076</v>
+      <c r="M70" t="n">
+        <v>1.389300384999996</v>
       </c>
     </row>
     <row r="71">
@@ -3965,39 +3753,36 @@
         <v>3.04</v>
       </c>
       <c r="D71" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E71" t="n">
-        <v>2</v>
+        <v>2.985</v>
       </c>
       <c r="F71" t="n">
-        <v>2.985</v>
+        <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>1</v>
+        <v>1.55</v>
       </c>
       <c r="H71" t="n">
-        <v>1.55</v>
+        <v>0.67</v>
       </c>
       <c r="I71" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K71" t="n">
-        <v>5</v>
-      </c>
-      <c r="L71" t="n">
-        <v>0.515374411933448</v>
-      </c>
-      <c r="M71" t="inlineStr">
+        <v>1.284855</v>
+      </c>
+      <c r="L71" t="inlineStr">
         <is>
           <t>Mn-bpy</t>
         </is>
       </c>
-      <c r="N71" t="n">
-        <v>0.5158929263212834</v>
+      <c r="M71" t="n">
+        <v>1.295118798297618</v>
       </c>
     </row>
     <row r="72">
@@ -4015,39 +3800,36 @@
         <v>3.44</v>
       </c>
       <c r="D72" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2</v>
+        <v>2.825</v>
       </c>
       <c r="F72" t="n">
-        <v>2.825</v>
+        <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="H72" t="n">
-        <v>1.24</v>
+        <v>1.062</v>
       </c>
       <c r="I72" t="n">
-        <v>1.062</v>
+        <v>11</v>
       </c>
       <c r="J72" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" t="n">
-        <v>0.514333745025388</v>
-      </c>
-      <c r="M72" t="inlineStr">
+        <v>2.004851</v>
+      </c>
+      <c r="L72" t="inlineStr">
         <is>
           <t>Er-cooh</t>
         </is>
       </c>
-      <c r="N72" t="n">
-        <v>0.5129544613874899</v>
+      <c r="M72" t="n">
+        <v>1.990233909999992</v>
       </c>
     </row>
     <row r="73">
@@ -4065,39 +3847,36 @@
         <v>3.04</v>
       </c>
       <c r="D73" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>2.78</v>
       </c>
       <c r="F73" t="n">
-        <v>2.78</v>
+        <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>1</v>
+        <v>1.079</v>
       </c>
       <c r="H73" t="n">
         <v>1.079</v>
       </c>
       <c r="I73" t="n">
-        <v>1.079</v>
+        <v>5</v>
       </c>
       <c r="J73" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" t="n">
-        <v>0.513126088602802</v>
-      </c>
-      <c r="M73" t="inlineStr">
+        <v>1.778306</v>
+      </c>
+      <c r="L73" t="inlineStr">
         <is>
           <t>Sm-bpy</t>
         </is>
       </c>
-      <c r="N73" t="n">
-        <v>0.5011646300270653</v>
+      <c r="M73" t="n">
+        <v>1.598126964416666</v>
       </c>
     </row>
     <row r="74">
@@ -4115,39 +3894,36 @@
         <v>3.04</v>
       </c>
       <c r="D74" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E74" t="n">
-        <v>2</v>
+        <v>2.921</v>
       </c>
       <c r="F74" t="n">
-        <v>2.921</v>
+        <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>1</v>
+        <v>1.027</v>
       </c>
       <c r="H74" t="n">
         <v>1.027</v>
       </c>
       <c r="I74" t="n">
-        <v>1.027</v>
+        <v>9</v>
       </c>
       <c r="J74" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" t="n">
-        <v>0.5129169879208429</v>
-      </c>
-      <c r="M74" t="inlineStr">
+        <v>1.772832</v>
+      </c>
+      <c r="L74" t="inlineStr">
         <is>
           <t>Dy-bpy</t>
         </is>
       </c>
-      <c r="N74" t="n">
-        <v>0.4993896504163902</v>
+      <c r="M74" t="n">
+        <v>1.629279361361112</v>
       </c>
     </row>
     <row r="75">
@@ -4165,39 +3941,36 @@
         <v>3.44</v>
       </c>
       <c r="D75" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2</v>
+        <v>4.412</v>
       </c>
       <c r="F75" t="n">
-        <v>4.412</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="H75" t="n">
         <v>0.68</v>
       </c>
       <c r="I75" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K75" t="n">
-        <v>6</v>
-      </c>
-      <c r="L75" t="n">
-        <v>0.5127523717639491</v>
-      </c>
-      <c r="M75" t="inlineStr">
+        <v>1.376217</v>
+      </c>
+      <c r="L75" t="inlineStr">
         <is>
           <t>Ir-cooh</t>
         </is>
       </c>
-      <c r="N75" t="n">
-        <v>0.5334081781146718</v>
+      <c r="M75" t="n">
+        <v>1.250144101666665</v>
       </c>
     </row>
     <row r="76">
@@ -4215,39 +3988,36 @@
         <v>3.04</v>
       </c>
       <c r="D76" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3</v>
+        <v>2.703</v>
       </c>
       <c r="F76" t="n">
-        <v>2.703</v>
+        <v>1</v>
       </c>
       <c r="G76" t="n">
-        <v>1</v>
+        <v>1.65</v>
       </c>
       <c r="H76" t="n">
-        <v>1.65</v>
+        <v>0.74</v>
       </c>
       <c r="I76" t="n">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K76" t="n">
-        <v>10</v>
-      </c>
-      <c r="L76" t="n">
-        <v>0.512725768321513</v>
-      </c>
-      <c r="M76" t="inlineStr">
+        <v>1.189663</v>
+      </c>
+      <c r="L76" t="inlineStr">
         <is>
           <t>Zn-tpy</t>
         </is>
       </c>
-      <c r="N76" t="n">
-        <v>0.5195111226453772</v>
+      <c r="M76" t="n">
+        <v>1.230448270142856</v>
       </c>
     </row>
     <row r="77">
@@ -4265,39 +4035,36 @@
         <v>3.44</v>
       </c>
       <c r="D77" t="n">
+        <v>2</v>
+      </c>
+      <c r="E77" t="n">
+        <v>4.412</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
         <v>6</v>
       </c>
-      <c r="E77" t="n">
-        <v>2</v>
-      </c>
-      <c r="F77" t="n">
-        <v>4.412</v>
-      </c>
-      <c r="G77" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="I77" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="J77" t="n">
-        <v>0</v>
-      </c>
       <c r="K77" t="n">
-        <v>6</v>
-      </c>
-      <c r="L77" t="n">
-        <v>0.511971830985916</v>
-      </c>
-      <c r="M77" t="inlineStr">
+        <v>1.390089</v>
+      </c>
+      <c r="L77" t="inlineStr">
         <is>
           <t>Ru-cooh</t>
         </is>
       </c>
-      <c r="N77" t="n">
-        <v>0.5109875256136545</v>
+      <c r="M77" t="n">
+        <v>1.390908029999997</v>
       </c>
     </row>
     <row r="78">
@@ -4315,39 +4082,36 @@
         <v>3.04</v>
       </c>
       <c r="D78" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2</v>
+        <v>3.071</v>
       </c>
       <c r="F78" t="n">
-        <v>3.071</v>
+        <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>1</v>
+        <v>0.977</v>
       </c>
       <c r="H78" t="n">
         <v>0.977</v>
       </c>
       <c r="I78" t="n">
-        <v>0.977</v>
+        <v>14</v>
       </c>
       <c r="J78" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" t="n">
-        <v>0.511687830687831</v>
-      </c>
-      <c r="M78" t="inlineStr">
+        <v>1.79015</v>
+      </c>
+      <c r="L78" t="inlineStr">
         <is>
           <t>Lu-bpy</t>
         </is>
       </c>
-      <c r="N78" t="n">
-        <v>0.4886319434913194</v>
+      <c r="M78" t="n">
+        <v>1.635016916833334</v>
       </c>
     </row>
     <row r="79">
@@ -4365,39 +4129,36 @@
         <v>3.44</v>
       </c>
       <c r="D79" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E79" t="n">
-        <v>2</v>
+        <v>4.688</v>
       </c>
       <c r="F79" t="n">
-        <v>4.688</v>
+        <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="H79" t="n">
-        <v>1.63</v>
+        <v>0.64</v>
       </c>
       <c r="I79" t="n">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K79" t="n">
-        <v>2</v>
-      </c>
-      <c r="L79" t="n">
-        <v>0.510605349794239</v>
-      </c>
-      <c r="M79" t="inlineStr">
+        <v>1.383423</v>
+      </c>
+      <c r="L79" t="inlineStr">
         <is>
           <t>V-cooh</t>
         </is>
       </c>
-      <c r="N79" t="n">
-        <v>0.5124645356903745</v>
+      <c r="M79" t="n">
+        <v>1.351876809999997</v>
       </c>
     </row>
     <row r="80">
@@ -4415,39 +4176,36 @@
         <v>3.44</v>
       </c>
       <c r="D80" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E80" t="n">
-        <v>2</v>
+        <v>4.878</v>
       </c>
       <c r="F80" t="n">
-        <v>4.878</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="H80" t="n">
-        <v>1.66</v>
+        <v>0.615</v>
       </c>
       <c r="I80" t="n">
-        <v>0.615</v>
+        <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K80" t="n">
-        <v>3</v>
-      </c>
-      <c r="L80" t="n">
-        <v>0.510016625103907</v>
-      </c>
-      <c r="M80" t="inlineStr">
+        <v>1.377868</v>
+      </c>
+      <c r="L80" t="inlineStr">
         <is>
           <t>Cr-cooh</t>
         </is>
       </c>
-      <c r="N80" t="n">
-        <v>0.5123710347190219</v>
+      <c r="M80" t="n">
+        <v>1.243943651666666</v>
       </c>
     </row>
     <row r="81">
@@ -4465,39 +4223,36 @@
         <v>3.04</v>
       </c>
       <c r="D81" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2</v>
+        <v>2.956</v>
       </c>
       <c r="F81" t="n">
-        <v>2.956</v>
+        <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>1</v>
+        <v>1.015</v>
       </c>
       <c r="H81" t="n">
         <v>1.015</v>
       </c>
       <c r="I81" t="n">
-        <v>1.015</v>
+        <v>10</v>
       </c>
       <c r="J81" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" t="n">
-        <v>0.509970721596062</v>
-      </c>
-      <c r="M81" t="inlineStr">
+        <v>1.779418</v>
+      </c>
+      <c r="L81" t="inlineStr">
         <is>
           <t>Ho-bpy</t>
         </is>
       </c>
-      <c r="N81" t="n">
-        <v>0.4846784489619198</v>
+      <c r="M81" t="n">
+        <v>1.600347259896824</v>
       </c>
     </row>
     <row r="82">
@@ -4515,39 +4270,36 @@
         <v>3.44</v>
       </c>
       <c r="D82" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>2.799</v>
       </c>
       <c r="F82" t="n">
-        <v>2.799</v>
+        <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="H82" t="n">
-        <v>1.23</v>
+        <v>1.072</v>
       </c>
       <c r="I82" t="n">
-        <v>1.072</v>
+        <v>10</v>
       </c>
       <c r="J82" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" t="n">
-        <v>0.509660468876314</v>
-      </c>
-      <c r="M82" t="inlineStr">
+        <v>1.975642</v>
+      </c>
+      <c r="L82" t="inlineStr">
         <is>
           <t>Ho-cooh</t>
         </is>
       </c>
-      <c r="N82" t="n">
-        <v>0.5104613428066304</v>
+      <c r="M82" t="n">
+        <v>1.956245244999995</v>
       </c>
     </row>
     <row r="83">
@@ -4565,39 +4317,36 @@
         <v>3.44</v>
       </c>
       <c r="D83" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E83" t="n">
-        <v>2</v>
+        <v>2.71</v>
       </c>
       <c r="F83" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="H83" t="n">
-        <v>1.2</v>
+        <v>1.107</v>
       </c>
       <c r="I83" t="n">
-        <v>1.107</v>
+        <v>7</v>
       </c>
       <c r="J83" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" t="n">
-        <v>0.5092948207171319</v>
-      </c>
-      <c r="M83" t="inlineStr">
+        <v>1.97544</v>
+      </c>
+      <c r="L83" t="inlineStr">
         <is>
           <t>Gd-cooh</t>
         </is>
       </c>
-      <c r="N83" t="n">
-        <v>0.534794466305297</v>
+      <c r="M83" t="n">
+        <v>1.994572470999996</v>
       </c>
     </row>
     <row r="84">
@@ -4615,39 +4364,36 @@
         <v>3.44</v>
       </c>
       <c r="D84" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2</v>
+        <v>2.679</v>
       </c>
       <c r="F84" t="n">
-        <v>2.679</v>
+        <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="H84" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="I84" t="n">
-        <v>1.12</v>
+        <v>6</v>
       </c>
       <c r="J84" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" t="n">
-        <v>0.509222222222222</v>
-      </c>
-      <c r="M84" t="inlineStr">
+        <v>1.741647</v>
+      </c>
+      <c r="L84" t="inlineStr">
         <is>
           <t>Eu-cooh</t>
         </is>
       </c>
-      <c r="N84" t="n">
-        <v>0.5244751523648906</v>
+      <c r="M84" t="n">
+        <v>2.004016215999999</v>
       </c>
     </row>
     <row r="85">
@@ -4665,39 +4411,36 @@
         <v>3.04</v>
       </c>
       <c r="D85" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3</v>
+        <v>1.695</v>
       </c>
       <c r="F85" t="n">
-        <v>1.695</v>
+        <v>1</v>
       </c>
       <c r="G85" t="n">
         <v>1</v>
       </c>
       <c r="H85" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="I85" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" t="n">
-        <v>0.509201383551114</v>
-      </c>
-      <c r="M85" t="inlineStr">
+        <v>1.871805</v>
+      </c>
+      <c r="L85" t="inlineStr">
         <is>
           <t>Ca-tpy</t>
         </is>
       </c>
-      <c r="N85" t="n">
-        <v>0.5170623733311569</v>
+      <c r="M85" t="n">
+        <v>1.825684365499999</v>
       </c>
     </row>
     <row r="86">
@@ -4715,39 +4458,36 @@
         <v>3.04</v>
       </c>
       <c r="D86" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E86" t="n">
-        <v>2</v>
+        <v>2.705</v>
       </c>
       <c r="F86" t="n">
-        <v>2.705</v>
+        <v>1</v>
       </c>
       <c r="G86" t="n">
-        <v>1</v>
+        <v>1.109</v>
       </c>
       <c r="H86" t="n">
         <v>1.109</v>
       </c>
       <c r="I86" t="n">
-        <v>1.109</v>
+        <v>3</v>
       </c>
       <c r="J86" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" t="n">
-        <v>0.509122421078797</v>
-      </c>
-      <c r="M86" t="inlineStr">
+        <v>1.770991</v>
+      </c>
+      <c r="L86" t="inlineStr">
         <is>
           <t>Nd-bpy</t>
         </is>
       </c>
-      <c r="N86" t="n">
-        <v>0.4888381912439083</v>
+      <c r="M86" t="n">
+        <v>1.631257657488096</v>
       </c>
     </row>
     <row r="87">
@@ -4765,39 +4505,36 @@
         <v>3.44</v>
       </c>
       <c r="D87" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2</v>
+        <v>2.852</v>
       </c>
       <c r="F87" t="n">
-        <v>2.852</v>
+        <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="H87" t="n">
-        <v>1.25</v>
+        <v>1.052</v>
       </c>
       <c r="I87" t="n">
-        <v>1.052</v>
+        <v>12</v>
       </c>
       <c r="J87" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" t="n">
-        <v>0.508939948488546</v>
-      </c>
-      <c r="M87" t="inlineStr">
+        <v>1.971139</v>
+      </c>
+      <c r="L87" t="inlineStr">
         <is>
           <t>Tm-cooh</t>
         </is>
       </c>
-      <c r="N87" t="n">
-        <v>0.5111668520589538</v>
+      <c r="M87" t="n">
+        <v>1.985195639999994</v>
       </c>
     </row>
     <row r="88">
@@ -4815,39 +4552,36 @@
         <v>3.04</v>
       </c>
       <c r="D88" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E88" t="n">
-        <v>2</v>
+        <v>4.348</v>
       </c>
       <c r="F88" t="n">
-        <v>4.348</v>
+        <v>1</v>
       </c>
       <c r="G88" t="n">
-        <v>1</v>
+        <v>2.16</v>
       </c>
       <c r="H88" t="n">
-        <v>2.16</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I88" t="n">
-        <v>0.6899999999999999</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K88" t="n">
-        <v>3</v>
-      </c>
-      <c r="L88" t="n">
-        <v>0.508845890919899</v>
-      </c>
-      <c r="M88" t="inlineStr">
+        <v>1.372387</v>
+      </c>
+      <c r="L88" t="inlineStr">
         <is>
           <t>Mo-bpy</t>
         </is>
       </c>
-      <c r="N88" t="n">
-        <v>0.4803005734329527</v>
+      <c r="M88" t="n">
+        <v>1.184956584750003</v>
       </c>
     </row>
     <row r="89">
@@ -4865,39 +4599,36 @@
         <v>3.44</v>
       </c>
       <c r="D89" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E89" t="n">
-        <v>2</v>
+        <v>2.545</v>
       </c>
       <c r="F89" t="n">
-        <v>2.545</v>
+        <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="H89" t="n">
-        <v>1.13</v>
+        <v>1.179</v>
       </c>
       <c r="I89" t="n">
-        <v>1.179</v>
+        <v>2</v>
       </c>
       <c r="J89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" t="n">
-        <v>0.50731488598514</v>
-      </c>
-      <c r="M89" t="inlineStr">
+        <v>1.960982</v>
+      </c>
+      <c r="L89" t="inlineStr">
         <is>
           <t>Pr-cooh</t>
         </is>
       </c>
-      <c r="N89" t="n">
-        <v>0.511675658394048</v>
+      <c r="M89" t="n">
+        <v>1.984475540000002</v>
       </c>
     </row>
     <row r="90">
@@ -4915,39 +4646,36 @@
         <v>3.04</v>
       </c>
       <c r="D90" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E90" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="F90" t="n">
-        <v>3.75</v>
+        <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>1</v>
+        <v>1.78</v>
       </c>
       <c r="H90" t="n">
-        <v>1.78</v>
+        <v>0.8</v>
       </c>
       <c r="I90" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K90" t="n">
-        <v>10</v>
-      </c>
-      <c r="L90" t="n">
-        <v>0.506411101216978</v>
-      </c>
-      <c r="M90" t="inlineStr">
+        <v>1.254365</v>
+      </c>
+      <c r="L90" t="inlineStr">
         <is>
           <t>In-tpy</t>
         </is>
       </c>
-      <c r="N90" t="n">
-        <v>0.5062725780126338</v>
+      <c r="M90" t="n">
+        <v>1.209998230833336</v>
       </c>
     </row>
     <row r="91">
@@ -4965,39 +4693,36 @@
         <v>3.44</v>
       </c>
       <c r="D91" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E91" t="n">
-        <v>2</v>
+        <v>3.509</v>
       </c>
       <c r="F91" t="n">
-        <v>3.509</v>
+        <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="H91" t="n">
-        <v>1.9</v>
+        <v>0.57</v>
       </c>
       <c r="I91" t="n">
-        <v>0.57</v>
+        <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K91" t="n">
-        <v>9</v>
-      </c>
-      <c r="L91" t="n">
-        <v>0.505939488731921</v>
-      </c>
-      <c r="M91" t="inlineStr">
+        <v>0.954261</v>
+      </c>
+      <c r="L91" t="inlineStr">
         <is>
           <t>Cu-cooh</t>
         </is>
       </c>
-      <c r="N91" t="n">
-        <v>0.5096281977310684</v>
+      <c r="M91" t="n">
+        <v>1.047909992666668</v>
       </c>
     </row>
     <row r="92">
@@ -5015,39 +4740,36 @@
         <v>3.44</v>
       </c>
       <c r="D92" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E92" t="n">
-        <v>2</v>
+        <v>4.348</v>
       </c>
       <c r="F92" t="n">
-        <v>4.348</v>
+        <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="H92" t="n">
-        <v>2.16</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I92" t="n">
-        <v>0.6899999999999999</v>
+        <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K92" t="n">
-        <v>3</v>
-      </c>
-      <c r="L92" t="n">
-        <v>0.50530303030303</v>
-      </c>
-      <c r="M92" t="inlineStr">
+        <v>1.348408</v>
+      </c>
+      <c r="L92" t="inlineStr">
         <is>
           <t>Mo-cooh</t>
         </is>
       </c>
-      <c r="N92" t="n">
-        <v>0.5077291311975447</v>
+      <c r="M92" t="n">
+        <v>1.356347395000002</v>
       </c>
     </row>
     <row r="93">
@@ -5065,39 +4787,36 @@
         <v>3.04</v>
       </c>
       <c r="D93" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E93" t="n">
-        <v>2</v>
+        <v>4.478</v>
       </c>
       <c r="F93" t="n">
-        <v>4.478</v>
+        <v>1</v>
       </c>
       <c r="G93" t="n">
-        <v>1</v>
+        <v>1.54</v>
       </c>
       <c r="H93" t="n">
-        <v>1.54</v>
+        <v>0.67</v>
       </c>
       <c r="I93" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K93" t="n">
-        <v>1</v>
-      </c>
-      <c r="L93" t="n">
-        <v>0.505169632265718</v>
-      </c>
-      <c r="M93" t="inlineStr">
+        <v>1.34941</v>
+      </c>
+      <c r="L93" t="inlineStr">
         <is>
           <t>Ti-bpy</t>
         </is>
       </c>
-      <c r="N93" t="n">
-        <v>0.5129972071312739</v>
+      <c r="M93" t="n">
+        <v>1.243724666333336</v>
       </c>
     </row>
     <row r="94">
@@ -5115,39 +4834,36 @@
         <v>3.04</v>
       </c>
       <c r="D94" t="n">
+        <v>3</v>
+      </c>
+      <c r="E94" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="F94" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="H94" t="n">
+        <v>1.083</v>
+      </c>
+      <c r="I94" t="n">
         <v>9</v>
       </c>
-      <c r="E94" t="n">
-        <v>3</v>
-      </c>
-      <c r="F94" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="G94" t="n">
-        <v>1</v>
-      </c>
-      <c r="H94" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="I94" t="n">
-        <v>1.083</v>
-      </c>
       <c r="J94" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>0</v>
-      </c>
-      <c r="L94" t="n">
-        <v>0.505121666009723</v>
-      </c>
-      <c r="M94" t="inlineStr">
+        <v>1.846306</v>
+      </c>
+      <c r="L94" t="inlineStr">
         <is>
           <t>Dy-tpy</t>
         </is>
       </c>
-      <c r="N94" t="n">
-        <v>0.526492131191328</v>
+      <c r="M94" t="n">
+        <v>1.844667060000006</v>
       </c>
     </row>
     <row r="95">
@@ -5165,39 +4881,36 @@
         <v>3.44</v>
       </c>
       <c r="D95" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E95" t="n">
-        <v>2</v>
+        <v>2.41</v>
       </c>
       <c r="F95" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="H95" t="n">
-        <v>1.55</v>
+        <v>0.83</v>
       </c>
       <c r="I95" t="n">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K95" t="n">
-        <v>5</v>
-      </c>
-      <c r="L95" t="n">
-        <v>0.5035918907007489</v>
-      </c>
-      <c r="M95" t="inlineStr">
+        <v>1.337713</v>
+      </c>
+      <c r="L95" t="inlineStr">
         <is>
           <t>Mn-cooh</t>
         </is>
       </c>
-      <c r="N95" t="n">
-        <v>0.508081958805827</v>
+      <c r="M95" t="n">
+        <v>1.346781465000001</v>
       </c>
     </row>
     <row r="96">
@@ -5215,39 +4928,36 @@
         <v>3.04</v>
       </c>
       <c r="D96" t="n">
+        <v>3</v>
+      </c>
+      <c r="E96" t="n">
+        <v>3.279</v>
+      </c>
+      <c r="F96" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
         <v>6</v>
       </c>
-      <c r="E96" t="n">
-        <v>3</v>
-      </c>
-      <c r="F96" t="n">
-        <v>3.279</v>
-      </c>
-      <c r="G96" t="n">
-        <v>1</v>
-      </c>
-      <c r="H96" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="I96" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="J96" t="n">
-        <v>0</v>
-      </c>
       <c r="K96" t="n">
-        <v>6</v>
-      </c>
-      <c r="L96" t="n">
-        <v>0.502115591397849</v>
-      </c>
-      <c r="M96" t="inlineStr">
+        <v>1.331687</v>
+      </c>
+      <c r="L96" t="inlineStr">
         <is>
           <t>Fe-tpy</t>
         </is>
       </c>
-      <c r="N96" t="n">
-        <v>0.5135046727778124</v>
+      <c r="M96" t="n">
+        <v>1.343213250833334</v>
       </c>
     </row>
     <row r="97">
@@ -5265,39 +4975,36 @@
         <v>3.04</v>
       </c>
       <c r="D97" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E97" t="n">
-        <v>3</v>
+        <v>3.125</v>
       </c>
       <c r="F97" t="n">
-        <v>3.125</v>
+        <v>1</v>
       </c>
       <c r="G97" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="H97" t="n">
-        <v>2.2</v>
+        <v>0.64</v>
       </c>
       <c r="I97" t="n">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K97" t="n">
-        <v>8</v>
-      </c>
-      <c r="L97" t="n">
-        <v>0.500687427912341</v>
-      </c>
-      <c r="M97" t="inlineStr">
+        <v>0.920677</v>
+      </c>
+      <c r="L97" t="inlineStr">
         <is>
           <t>Pd-tpy</t>
         </is>
       </c>
-      <c r="N97" t="n">
-        <v>0.4953326399995456</v>
+      <c r="M97" t="n">
+        <v>1.007584361250002</v>
       </c>
     </row>
     <row r="98">
@@ -5315,39 +5022,36 @@
         <v>3.04</v>
       </c>
       <c r="D98" t="n">
+        <v>3</v>
+      </c>
+      <c r="E98" t="n">
+        <v>2.941</v>
+      </c>
+      <c r="F98" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="n">
         <v>6</v>
       </c>
-      <c r="E98" t="n">
-        <v>3</v>
-      </c>
-      <c r="F98" t="n">
-        <v>2.941</v>
-      </c>
-      <c r="G98" t="n">
-        <v>1</v>
-      </c>
-      <c r="H98" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="I98" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="J98" t="n">
-        <v>0</v>
-      </c>
       <c r="K98" t="n">
-        <v>6</v>
-      </c>
-      <c r="L98" t="n">
-        <v>0.498772412683084</v>
-      </c>
-      <c r="M98" t="inlineStr">
+        <v>1.310791</v>
+      </c>
+      <c r="L98" t="inlineStr">
         <is>
           <t>Ru-tpy</t>
         </is>
       </c>
-      <c r="N98" t="n">
-        <v>0.5022708333623561</v>
+      <c r="M98" t="n">
+        <v>1.263667820499998</v>
       </c>
     </row>
     <row r="99">
@@ -5365,39 +5069,36 @@
         <v>3.04</v>
       </c>
       <c r="D99" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E99" t="n">
-        <v>3</v>
+        <v>2.508</v>
       </c>
       <c r="F99" t="n">
-        <v>2.508</v>
+        <v>1</v>
       </c>
       <c r="G99" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="H99" t="n">
-        <v>1.12</v>
+        <v>1.196</v>
       </c>
       <c r="I99" t="n">
-        <v>1.196</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" t="n">
-        <v>0.498353535353535</v>
-      </c>
-      <c r="M99" t="inlineStr">
+        <v>1.854005</v>
+      </c>
+      <c r="L99" t="inlineStr">
         <is>
           <t>Ce-tpy</t>
         </is>
       </c>
-      <c r="N99" t="n">
-        <v>0.4916479431069506</v>
+      <c r="M99" t="n">
+        <v>1.800545228416669</v>
       </c>
     </row>
     <row r="100">
@@ -5415,39 +5116,36 @@
         <v>3.04</v>
       </c>
       <c r="D100" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E100" t="n">
-        <v>2</v>
+        <v>3.509</v>
       </c>
       <c r="F100" t="n">
-        <v>3.509</v>
+        <v>1</v>
       </c>
       <c r="G100" t="n">
-        <v>1</v>
+        <v>0.57</v>
       </c>
       <c r="H100" t="n">
         <v>0.57</v>
       </c>
       <c r="I100" t="n">
-        <v>0.57</v>
+        <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K100" t="n">
-        <v>9</v>
-      </c>
-      <c r="L100" t="n">
-        <v>0.495517345399698</v>
-      </c>
-      <c r="M100" t="inlineStr">
+        <v>0.889082</v>
+      </c>
+      <c r="L100" t="inlineStr">
         <is>
           <t>Cu-bpy</t>
         </is>
       </c>
-      <c r="N100" t="n">
-        <v>0.4884743182141376</v>
+      <c r="M100" t="n">
+        <v>0.8326255677738095</v>
       </c>
     </row>
     <row r="101">
@@ -5465,39 +5163,36 @@
         <v>3.44</v>
       </c>
       <c r="D101" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E101" t="n">
-        <v>2</v>
+        <v>2.105</v>
       </c>
       <c r="F101" t="n">
-        <v>2.105</v>
+        <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="H101" t="n">
         <v>0.95</v>
       </c>
       <c r="I101" t="n">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K101" t="n">
-        <v>10</v>
-      </c>
-      <c r="L101" t="n">
-        <v>0.494868365180467</v>
-      </c>
-      <c r="M101" t="inlineStr">
+        <v>1.243605</v>
+      </c>
+      <c r="L101" t="inlineStr">
         <is>
           <t>Cd-cooh</t>
         </is>
       </c>
-      <c r="N101" t="n">
-        <v>0.5055142962678248</v>
+      <c r="M101" t="n">
+        <v>1.259128460000001</v>
       </c>
     </row>
     <row r="102">
@@ -5515,39 +5210,36 @@
         <v>3.44</v>
       </c>
       <c r="D102" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E102" t="n">
-        <v>2</v>
+        <v>3.125</v>
       </c>
       <c r="F102" t="n">
-        <v>3.125</v>
+        <v>0</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="H102" t="n">
-        <v>2.2</v>
+        <v>0.64</v>
       </c>
       <c r="I102" t="n">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K102" t="n">
-        <v>8</v>
-      </c>
-      <c r="L102" t="n">
-        <v>0.493728103044497</v>
-      </c>
-      <c r="M102" t="inlineStr">
+        <v>0.877937</v>
+      </c>
+      <c r="L102" t="inlineStr">
         <is>
           <t>Pd-cooh</t>
         </is>
       </c>
-      <c r="N102" t="n">
-        <v>0.5138962986591448</v>
+      <c r="M102" t="n">
+        <v>1.358545954999999</v>
       </c>
     </row>
     <row r="103">
@@ -5565,39 +5257,36 @@
         <v>3.04</v>
       </c>
       <c r="D103" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E103" t="n">
-        <v>3</v>
+        <v>2.899</v>
       </c>
       <c r="F103" t="n">
-        <v>2.899</v>
+        <v>1</v>
       </c>
       <c r="G103" t="n">
-        <v>1</v>
+        <v>1.91</v>
       </c>
       <c r="H103" t="n">
-        <v>1.91</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I103" t="n">
-        <v>0.6899999999999999</v>
+        <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K103" t="n">
-        <v>8</v>
-      </c>
-      <c r="L103" t="n">
-        <v>0.493516154452325</v>
-      </c>
-      <c r="M103" t="inlineStr">
+        <v>1.275855</v>
+      </c>
+      <c r="L103" t="inlineStr">
         <is>
           <t>Ni-tpy</t>
         </is>
       </c>
-      <c r="N103" t="n">
-        <v>0.4953113101748612</v>
+      <c r="M103" t="n">
+        <v>1.242102811250002</v>
       </c>
     </row>
     <row r="104">
@@ -5615,39 +5304,36 @@
         <v>3.04</v>
       </c>
       <c r="D104" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E104" t="n">
+        <v>4.878</v>
+      </c>
+      <c r="F104" t="n">
+        <v>1</v>
+      </c>
+      <c r="G104" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="n">
         <v>3</v>
       </c>
-      <c r="F104" t="n">
-        <v>4.878</v>
-      </c>
-      <c r="G104" t="n">
-        <v>1</v>
-      </c>
-      <c r="H104" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="I104" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="J104" t="n">
-        <v>0</v>
-      </c>
       <c r="K104" t="n">
-        <v>3</v>
-      </c>
-      <c r="L104" t="n">
-        <v>0.491597606339964</v>
-      </c>
-      <c r="M104" t="inlineStr">
+        <v>1.25553</v>
+      </c>
+      <c r="L104" t="inlineStr">
         <is>
           <t>Cr-tpy</t>
         </is>
       </c>
-      <c r="N104" t="n">
-        <v>0.4943416467974673</v>
+      <c r="M104" t="n">
+        <v>1.266746432142854</v>
       </c>
     </row>
     <row r="105">
@@ -5665,39 +5351,36 @@
         <v>3.04</v>
       </c>
       <c r="D105" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E105" t="n">
-        <v>3</v>
+        <v>2.825</v>
       </c>
       <c r="F105" t="n">
-        <v>2.825</v>
+        <v>1</v>
       </c>
       <c r="G105" t="n">
-        <v>1</v>
+        <v>1.24</v>
       </c>
       <c r="H105" t="n">
-        <v>1.24</v>
+        <v>1.062</v>
       </c>
       <c r="I105" t="n">
-        <v>1.062</v>
+        <v>11</v>
       </c>
       <c r="J105" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K105" t="n">
-        <v>0</v>
-      </c>
-      <c r="L105" t="n">
-        <v>0.491194045720362</v>
-      </c>
-      <c r="M105" t="inlineStr">
+        <v>1.853008</v>
+      </c>
+      <c r="L105" t="inlineStr">
         <is>
           <t>Er-tpy</t>
         </is>
       </c>
-      <c r="N105" t="n">
-        <v>0.4994303964426625</v>
+      <c r="M105" t="n">
+        <v>1.841456169999998</v>
       </c>
     </row>
     <row r="106">
@@ -5715,39 +5398,36 @@
         <v>3.04</v>
       </c>
       <c r="D106" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E106" t="n">
-        <v>3</v>
+        <v>2.532</v>
       </c>
       <c r="F106" t="n">
-        <v>2.532</v>
+        <v>1</v>
       </c>
       <c r="G106" t="n">
-        <v>1</v>
+        <v>1.63</v>
       </c>
       <c r="H106" t="n">
-        <v>1.63</v>
+        <v>0.64</v>
       </c>
       <c r="I106" t="n">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="J106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K106" t="n">
-        <v>2</v>
-      </c>
-      <c r="L106" t="n">
-        <v>0.491043408617652</v>
-      </c>
-      <c r="M106" t="inlineStr">
+        <v>1.2604</v>
+      </c>
+      <c r="L106" t="inlineStr">
         <is>
           <t>V-tpy</t>
         </is>
       </c>
-      <c r="N106" t="n">
-        <v>0.4958771607356545</v>
+      <c r="M106" t="n">
+        <v>1.267812216666668</v>
       </c>
     </row>
     <row r="107">
@@ -5765,39 +5445,36 @@
         <v>3.04</v>
       </c>
       <c r="D107" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E107" t="n">
-        <v>2</v>
+        <v>2.941</v>
       </c>
       <c r="F107" t="n">
-        <v>2.941</v>
+        <v>1</v>
       </c>
       <c r="G107" t="n">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="H107" t="n">
         <v>0.68</v>
       </c>
       <c r="I107" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K107" t="n">
-        <v>6</v>
-      </c>
-      <c r="L107" t="n">
-        <v>0.490273901808786</v>
-      </c>
-      <c r="M107" t="inlineStr">
+        <v>1.208362</v>
+      </c>
+      <c r="L107" t="inlineStr">
         <is>
           <t>Ru-phen</t>
         </is>
       </c>
-      <c r="N107" t="n">
-        <v>0.5575625776892523</v>
+      <c r="M107" t="n">
+        <v>1.34519161990476</v>
       </c>
     </row>
     <row r="108">
@@ -5815,39 +5492,36 @@
         <v>3.04</v>
       </c>
       <c r="D108" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E108" t="n">
-        <v>3</v>
+        <v>2.799</v>
       </c>
       <c r="F108" t="n">
-        <v>2.799</v>
+        <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>1</v>
+        <v>1.23</v>
       </c>
       <c r="H108" t="n">
-        <v>1.23</v>
+        <v>1.072</v>
       </c>
       <c r="I108" t="n">
-        <v>1.072</v>
+        <v>10</v>
       </c>
       <c r="J108" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>0</v>
-      </c>
-      <c r="L108" t="n">
-        <v>0.489596837944664</v>
-      </c>
-      <c r="M108" t="inlineStr">
+        <v>1.843025</v>
+      </c>
+      <c r="L108" t="inlineStr">
         <is>
           <t>Ho-tpy</t>
         </is>
       </c>
-      <c r="N108" t="n">
-        <v>0.502327677870589</v>
+      <c r="M108" t="n">
+        <v>1.842453145000005</v>
       </c>
     </row>
     <row r="109">
@@ -5865,39 +5539,36 @@
         <v>3.44</v>
       </c>
       <c r="D109" t="n">
+        <v>2</v>
+      </c>
+      <c r="E109" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="H109" t="n">
+        <v>1.083</v>
+      </c>
+      <c r="I109" t="n">
         <v>9</v>
       </c>
-      <c r="E109" t="n">
-        <v>2</v>
-      </c>
-      <c r="F109" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="G109" t="n">
-        <v>0</v>
-      </c>
-      <c r="H109" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="I109" t="n">
-        <v>1.083</v>
-      </c>
       <c r="J109" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>0</v>
-      </c>
-      <c r="L109" t="n">
-        <v>0.489039128829826</v>
-      </c>
-      <c r="M109" t="inlineStr">
+        <v>1.807171</v>
+      </c>
+      <c r="L109" t="inlineStr">
         <is>
           <t>Dy-cooh</t>
         </is>
       </c>
-      <c r="N109" t="n">
-        <v>0.5069646534213536</v>
+      <c r="M109" t="n">
+        <v>1.877855126999997</v>
       </c>
     </row>
     <row r="110">
@@ -5915,39 +5586,36 @@
         <v>3.04</v>
       </c>
       <c r="D110" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E110" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="F110" t="n">
+        <v>1</v>
+      </c>
+      <c r="G110" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="H110" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="I110" t="n">
         <v>3</v>
       </c>
-      <c r="F110" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="G110" t="n">
-        <v>1</v>
-      </c>
-      <c r="H110" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="I110" t="n">
-        <v>1.163</v>
-      </c>
       <c r="J110" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>0</v>
-      </c>
-      <c r="L110" t="n">
-        <v>0.488825783530009</v>
-      </c>
-      <c r="M110" t="inlineStr">
+        <v>1.838206</v>
+      </c>
+      <c r="L110" t="inlineStr">
         <is>
           <t>Nd-tpy</t>
         </is>
       </c>
-      <c r="N110" t="n">
-        <v>0.491046908062412</v>
+      <c r="M110" t="n">
+        <v>1.814155202166673</v>
       </c>
     </row>
     <row r="111">
@@ -5965,39 +5633,36 @@
         <v>3.04</v>
       </c>
       <c r="D111" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E111" t="n">
-        <v>2</v>
+        <v>3.125</v>
       </c>
       <c r="F111" t="n">
-        <v>3.125</v>
+        <v>1</v>
       </c>
       <c r="G111" t="n">
-        <v>1</v>
+        <v>0.64</v>
       </c>
       <c r="H111" t="n">
         <v>0.64</v>
       </c>
       <c r="I111" t="n">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K111" t="n">
-        <v>8</v>
-      </c>
-      <c r="L111" t="n">
-        <v>0.488258706467662</v>
-      </c>
-      <c r="M111" t="inlineStr">
+        <v>0.8249339999999999</v>
+      </c>
+      <c r="L111" t="inlineStr">
         <is>
           <t>Pd-phen</t>
         </is>
       </c>
-      <c r="N111" t="n">
-        <v>0.498266171819329</v>
+      <c r="M111" t="n">
+        <v>0.9554049913333365</v>
       </c>
     </row>
     <row r="112">
@@ -6015,39 +5680,36 @@
         <v>3.04</v>
       </c>
       <c r="D112" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E112" t="n">
-        <v>3</v>
+        <v>2.907</v>
       </c>
       <c r="F112" t="n">
-        <v>2.907</v>
+        <v>1</v>
       </c>
       <c r="G112" t="n">
-        <v>1</v>
+        <v>1.27</v>
       </c>
       <c r="H112" t="n">
-        <v>1.27</v>
+        <v>1.032</v>
       </c>
       <c r="I112" t="n">
-        <v>1.032</v>
+        <v>14</v>
       </c>
       <c r="J112" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>0</v>
-      </c>
-      <c r="L112" t="n">
-        <v>0.488202572347267</v>
-      </c>
-      <c r="M112" t="inlineStr">
+        <v>1.844728</v>
+      </c>
+      <c r="L112" t="inlineStr">
         <is>
           <t>Lu-tpy</t>
         </is>
       </c>
-      <c r="N112" t="n">
-        <v>0.494479844665192</v>
+      <c r="M112" t="n">
+        <v>1.806607386250004</v>
       </c>
     </row>
     <row r="113">
@@ -6065,39 +5727,36 @@
         <v>3.04</v>
       </c>
       <c r="D113" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E113" t="n">
-        <v>3</v>
+        <v>2.852</v>
       </c>
       <c r="F113" t="n">
-        <v>2.852</v>
+        <v>1</v>
       </c>
       <c r="G113" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="H113" t="n">
-        <v>1.25</v>
+        <v>1.052</v>
       </c>
       <c r="I113" t="n">
-        <v>1.052</v>
+        <v>12</v>
       </c>
       <c r="J113" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>0</v>
-      </c>
-      <c r="L113" t="n">
-        <v>0.488011630980703</v>
-      </c>
-      <c r="M113" t="inlineStr">
+        <v>1.833118</v>
+      </c>
+      <c r="L113" t="inlineStr">
         <is>
           <t>Tm-tpy</t>
         </is>
       </c>
-      <c r="N113" t="n">
-        <v>0.4960412823737652</v>
+      <c r="M113" t="n">
+        <v>1.826600075000005</v>
       </c>
     </row>
     <row r="114">
@@ -6115,39 +5774,36 @@
         <v>3.04</v>
       </c>
       <c r="D114" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E114" t="n">
-        <v>3</v>
+        <v>3.077</v>
       </c>
       <c r="F114" t="n">
-        <v>3.077</v>
+        <v>1</v>
       </c>
       <c r="G114" t="n">
-        <v>1</v>
+        <v>1.88</v>
       </c>
       <c r="H114" t="n">
-        <v>1.88</v>
+        <v>0.65</v>
       </c>
       <c r="I114" t="n">
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="J114" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K114" t="n">
-        <v>7</v>
-      </c>
-      <c r="L114" t="n">
-        <v>0.485025207452638</v>
-      </c>
-      <c r="M114" t="inlineStr">
+        <v>1.222785</v>
+      </c>
+      <c r="L114" t="inlineStr">
         <is>
           <t>Co-tpy</t>
         </is>
       </c>
-      <c r="N114" t="n">
-        <v>0.4862726679680586</v>
+      <c r="M114" t="n">
+        <v>1.183588054999997</v>
       </c>
     </row>
     <row r="115">
@@ -6165,39 +5821,36 @@
         <v>3.04</v>
       </c>
       <c r="D115" t="n">
+        <v>2</v>
+      </c>
+      <c r="E115" t="n">
+        <v>3.279</v>
+      </c>
+      <c r="F115" t="n">
+        <v>1</v>
+      </c>
+      <c r="G115" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" t="n">
         <v>6</v>
       </c>
-      <c r="E115" t="n">
-        <v>2</v>
-      </c>
-      <c r="F115" t="n">
-        <v>3.279</v>
-      </c>
-      <c r="G115" t="n">
-        <v>1</v>
-      </c>
-      <c r="H115" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="I115" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="J115" t="n">
-        <v>0</v>
-      </c>
       <c r="K115" t="n">
-        <v>6</v>
-      </c>
-      <c r="L115" t="n">
-        <v>0.484782258064516</v>
-      </c>
-      <c r="M115" t="inlineStr">
+        <v>1.221956</v>
+      </c>
+      <c r="L115" t="inlineStr">
         <is>
           <t>Fe-phen</t>
         </is>
       </c>
-      <c r="N115" t="n">
-        <v>0.5182473606288405</v>
+      <c r="M115" t="n">
+        <v>1.396729021333336</v>
       </c>
     </row>
     <row r="116">
@@ -6215,39 +5868,36 @@
         <v>3.04</v>
       </c>
       <c r="D116" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E116" t="n">
-        <v>2</v>
+        <v>2.899</v>
       </c>
       <c r="F116" t="n">
-        <v>2.899</v>
+        <v>1</v>
       </c>
       <c r="G116" t="n">
-        <v>1</v>
+        <v>1.91</v>
       </c>
       <c r="H116" t="n">
-        <v>1.91</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I116" t="n">
-        <v>0.6899999999999999</v>
+        <v>0</v>
       </c>
       <c r="J116" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K116" t="n">
-        <v>8</v>
-      </c>
-      <c r="L116" t="n">
-        <v>0.483552758954501</v>
-      </c>
-      <c r="M116" t="inlineStr">
+        <v>1.216355</v>
+      </c>
+      <c r="L116" t="inlineStr">
         <is>
           <t>Ni-phen</t>
         </is>
       </c>
-      <c r="N116" t="n">
-        <v>0.4924281806592474</v>
+      <c r="M116" t="n">
+        <v>1.232314421571427</v>
       </c>
     </row>
     <row r="117">
@@ -6265,39 +5915,36 @@
         <v>3.04</v>
       </c>
       <c r="D117" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E117" t="n">
-        <v>3</v>
+        <v>2.545</v>
       </c>
       <c r="F117" t="n">
-        <v>2.545</v>
+        <v>1</v>
       </c>
       <c r="G117" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="H117" t="n">
-        <v>1.13</v>
+        <v>1.179</v>
       </c>
       <c r="I117" t="n">
-        <v>1.179</v>
+        <v>2</v>
       </c>
       <c r="J117" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K117" t="n">
-        <v>0</v>
-      </c>
-      <c r="L117" t="n">
-        <v>0.483256944444444</v>
-      </c>
-      <c r="M117" t="inlineStr">
+        <v>1.8034</v>
+      </c>
+      <c r="L117" t="inlineStr">
         <is>
           <t>Pr-tpy</t>
         </is>
       </c>
-      <c r="N117" t="n">
-        <v>0.4895049387168147</v>
+      <c r="M117" t="n">
+        <v>1.804143268416672</v>
       </c>
     </row>
     <row r="118">
@@ -6315,39 +5962,36 @@
         <v>3.04</v>
       </c>
       <c r="D118" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E118" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="F118" t="n">
-        <v>2.71</v>
+        <v>1</v>
       </c>
       <c r="G118" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="H118" t="n">
-        <v>1.2</v>
+        <v>1.107</v>
       </c>
       <c r="I118" t="n">
-        <v>1.107</v>
+        <v>7</v>
       </c>
       <c r="J118" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K118" t="n">
-        <v>0</v>
-      </c>
-      <c r="L118" t="n">
-        <v>0.482678178562292</v>
-      </c>
-      <c r="M118" t="inlineStr">
+        <v>1.810199</v>
+      </c>
+      <c r="L118" t="inlineStr">
         <is>
           <t>Gd-tpy</t>
         </is>
       </c>
-      <c r="N118" t="n">
-        <v>0.5413436139950268</v>
+      <c r="M118" t="n">
+        <v>1.815719915000004</v>
       </c>
     </row>
     <row r="119">
@@ -6365,39 +6009,36 @@
         <v>3.04</v>
       </c>
       <c r="D119" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E119" t="n">
-        <v>2</v>
+        <v>1.786</v>
       </c>
       <c r="F119" t="n">
-        <v>1.786</v>
+        <v>1</v>
       </c>
       <c r="G119" t="n">
         <v>1</v>
       </c>
       <c r="H119" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="I119" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
       </c>
       <c r="K119" t="n">
-        <v>0</v>
-      </c>
-      <c r="L119" t="n">
-        <v>0.482205226258763</v>
-      </c>
-      <c r="M119" t="inlineStr">
+        <v>1.503763</v>
+      </c>
+      <c r="L119" t="inlineStr">
         <is>
           <t>Ca-phen</t>
         </is>
       </c>
-      <c r="N119" t="n">
-        <v>0.5299540311367741</v>
+      <c r="M119" t="n">
+        <v>1.776833026428576</v>
       </c>
     </row>
     <row r="120">
@@ -6415,39 +6056,36 @@
         <v>3.04</v>
       </c>
       <c r="D120" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E120" t="n">
+        <v>4.348</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1</v>
+      </c>
+      <c r="G120" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" t="n">
         <v>3</v>
       </c>
-      <c r="F120" t="n">
-        <v>4.348</v>
-      </c>
-      <c r="G120" t="n">
-        <v>1</v>
-      </c>
-      <c r="H120" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="I120" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="J120" t="n">
-        <v>0</v>
-      </c>
       <c r="K120" t="n">
-        <v>3</v>
-      </c>
-      <c r="L120" t="n">
-        <v>0.479833030852995</v>
-      </c>
-      <c r="M120" t="inlineStr">
+        <v>1.190333</v>
+      </c>
+      <c r="L120" t="inlineStr">
         <is>
           <t>Mo-tpy</t>
         </is>
       </c>
-      <c r="N120" t="n">
-        <v>0.4832306261667768</v>
+      <c r="M120" t="n">
+        <v>1.183468462083336</v>
       </c>
     </row>
     <row r="121">
@@ -6465,39 +6103,36 @@
         <v>3.04</v>
       </c>
       <c r="D121" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E121" t="n">
-        <v>3</v>
+        <v>2.467</v>
       </c>
       <c r="F121" t="n">
-        <v>2.467</v>
+        <v>1</v>
       </c>
       <c r="G121" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="H121" t="n">
-        <v>1.1</v>
+        <v>1.216</v>
       </c>
       <c r="I121" t="n">
-        <v>1.216</v>
+        <v>0</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
       </c>
       <c r="K121" t="n">
-        <v>0</v>
-      </c>
-      <c r="L121" t="n">
-        <v>0.479287795992714</v>
-      </c>
-      <c r="M121" t="inlineStr">
+        <v>1.789009</v>
+      </c>
+      <c r="L121" t="inlineStr">
         <is>
           <t>La-tpy</t>
         </is>
       </c>
-      <c r="N121" t="n">
-        <v>0.5106740694371809</v>
+      <c r="M121" t="n">
+        <v>1.786860770250002</v>
       </c>
     </row>
     <row r="122">
@@ -6515,39 +6150,36 @@
         <v>3.04</v>
       </c>
       <c r="D122" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E122" t="n">
-        <v>3</v>
+        <v>6.612</v>
       </c>
       <c r="F122" t="n">
-        <v>6.612</v>
+        <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>1</v>
+        <v>1.54</v>
       </c>
       <c r="H122" t="n">
-        <v>1.54</v>
+        <v>0.605</v>
       </c>
       <c r="I122" t="n">
-        <v>0.605</v>
+        <v>0</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
       </c>
       <c r="K122" t="n">
-        <v>0</v>
-      </c>
-      <c r="L122" t="n">
-        <v>0.476920099875156</v>
-      </c>
-      <c r="M122" t="inlineStr">
+        <v>1.172127</v>
+      </c>
+      <c r="L122" t="inlineStr">
         <is>
           <t>Ti-tpy</t>
         </is>
       </c>
-      <c r="N122" t="n">
-        <v>0.5199210287921037</v>
+      <c r="M122" t="n">
+        <v>1.071022150833332</v>
       </c>
     </row>
     <row r="123">
@@ -6565,39 +6197,36 @@
         <v>3.04</v>
       </c>
       <c r="D123" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E123" t="n">
-        <v>2</v>
+        <v>3.509</v>
       </c>
       <c r="F123" t="n">
-        <v>3.509</v>
+        <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>1</v>
+        <v>0.57</v>
       </c>
       <c r="H123" t="n">
         <v>0.57</v>
       </c>
       <c r="I123" t="n">
-        <v>0.57</v>
+        <v>0</v>
       </c>
       <c r="J123" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K123" t="n">
-        <v>9</v>
-      </c>
-      <c r="L123" t="n">
-        <v>0.476552058432935</v>
-      </c>
-      <c r="M123" t="inlineStr">
+        <v>0.754474</v>
+      </c>
+      <c r="L123" t="inlineStr">
         <is>
           <t>Cu-phen</t>
         </is>
       </c>
-      <c r="N123" t="n">
-        <v>0.4884743182141376</v>
+      <c r="M123" t="n">
+        <v>0.8326255677738095</v>
       </c>
     </row>
     <row r="124">
@@ -6615,39 +6244,36 @@
         <v>3.04</v>
       </c>
       <c r="D124" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E124" t="n">
-        <v>2</v>
+        <v>3.077</v>
       </c>
       <c r="F124" t="n">
-        <v>3.077</v>
+        <v>1</v>
       </c>
       <c r="G124" t="n">
-        <v>1</v>
+        <v>1.88</v>
       </c>
       <c r="H124" t="n">
-        <v>1.88</v>
+        <v>0.745</v>
       </c>
       <c r="I124" t="n">
-        <v>0.745</v>
+        <v>0</v>
       </c>
       <c r="J124" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K124" t="n">
-        <v>7</v>
-      </c>
-      <c r="L124" t="n">
-        <v>0.475532503457815</v>
-      </c>
-      <c r="M124" t="inlineStr">
+        <v>1.166227</v>
+      </c>
+      <c r="L124" t="inlineStr">
         <is>
           <t>Co-phen</t>
         </is>
       </c>
-      <c r="N124" t="n">
-        <v>0.4792578365415072</v>
+      <c r="M124" t="n">
+        <v>1.185689053749998</v>
       </c>
     </row>
     <row r="125">
@@ -6665,39 +6291,36 @@
         <v>3.04</v>
       </c>
       <c r="D125" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E125" t="n">
-        <v>2</v>
+        <v>2.586</v>
       </c>
       <c r="F125" t="n">
-        <v>2.586</v>
+        <v>1</v>
       </c>
       <c r="G125" t="n">
-        <v>1</v>
+        <v>1.16</v>
       </c>
       <c r="H125" t="n">
         <v>1.16</v>
       </c>
       <c r="I125" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
       </c>
       <c r="K125" t="n">
-        <v>0</v>
-      </c>
-      <c r="L125" t="n">
-        <v>0.475358173378497</v>
-      </c>
-      <c r="M125" t="inlineStr">
+        <v>1.502635</v>
+      </c>
+      <c r="L125" t="inlineStr">
         <is>
           <t>La-phen</t>
         </is>
       </c>
-      <c r="N125" t="n">
-        <v>0.4969534807220833</v>
+      <c r="M125" t="n">
+        <v>1.678677425559523</v>
       </c>
     </row>
     <row r="126">
@@ -6715,39 +6338,36 @@
         <v>3.04</v>
       </c>
       <c r="D126" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E126" t="n">
-        <v>2</v>
+        <v>3.333</v>
       </c>
       <c r="F126" t="n">
-        <v>3.333</v>
+        <v>1</v>
       </c>
       <c r="G126" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="H126" t="n">
         <v>0.6</v>
       </c>
       <c r="I126" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="J126" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K126" t="n">
-        <v>8</v>
-      </c>
-      <c r="L126" t="n">
-        <v>0.472354256508545</v>
-      </c>
-      <c r="M126" t="inlineStr">
+        <v>0.704694</v>
+      </c>
+      <c r="L126" t="inlineStr">
         <is>
           <t>Pt-phen</t>
         </is>
       </c>
-      <c r="N126" t="n">
-        <v>0.5084224796098412</v>
+      <c r="M126" t="n">
+        <v>0.8950157507857142</v>
       </c>
     </row>
     <row r="127">
@@ -6765,39 +6385,36 @@
         <v>3.04</v>
       </c>
       <c r="D127" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E127" t="n">
-        <v>3</v>
+        <v>2.985</v>
       </c>
       <c r="F127" t="n">
-        <v>2.985</v>
+        <v>1</v>
       </c>
       <c r="G127" t="n">
-        <v>1</v>
+        <v>1.55</v>
       </c>
       <c r="H127" t="n">
-        <v>1.55</v>
+        <v>0.67</v>
       </c>
       <c r="I127" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="J127" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K127" t="n">
-        <v>5</v>
-      </c>
-      <c r="L127" t="n">
-        <v>0.471207014415218</v>
-      </c>
-      <c r="M127" t="inlineStr">
+        <v>1.136419</v>
+      </c>
+      <c r="L127" t="inlineStr">
         <is>
           <t>Mn-tpy</t>
         </is>
       </c>
-      <c r="N127" t="n">
-        <v>0.5134217372265141</v>
+      <c r="M127" t="n">
+        <v>1.281615376392857</v>
       </c>
     </row>
     <row r="128">
@@ -6815,39 +6432,36 @@
         <v>3.04</v>
       </c>
       <c r="D128" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E128" t="n">
-        <v>2</v>
+        <v>4.412</v>
       </c>
       <c r="F128" t="n">
-        <v>4.412</v>
+        <v>1</v>
       </c>
       <c r="G128" t="n">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="H128" t="n">
         <v>0.68</v>
       </c>
       <c r="I128" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="J128" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K128" t="n">
-        <v>6</v>
-      </c>
-      <c r="L128" t="n">
-        <v>0.470604001861331</v>
-      </c>
-      <c r="M128" t="inlineStr">
+        <v>1.122922</v>
+      </c>
+      <c r="L128" t="inlineStr">
         <is>
           <t>Ir-phen</t>
         </is>
       </c>
-      <c r="N128" t="n">
-        <v>0.5286205539255839</v>
+      <c r="M128" t="n">
+        <v>1.335918219999998</v>
       </c>
     </row>
     <row r="129">
@@ -6865,39 +6479,36 @@
         <v>3.04</v>
       </c>
       <c r="D129" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E129" t="n">
-        <v>3</v>
+        <v>3.077</v>
       </c>
       <c r="F129" t="n">
-        <v>3.077</v>
+        <v>1</v>
       </c>
       <c r="G129" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="H129" t="n">
-        <v>1.9</v>
+        <v>0.65</v>
       </c>
       <c r="I129" t="n">
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="J129" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K129" t="n">
-        <v>9</v>
-      </c>
-      <c r="L129" t="n">
-        <v>0.468654761904762</v>
-      </c>
-      <c r="M129" t="inlineStr">
+        <v>0.920467</v>
+      </c>
+      <c r="L129" t="inlineStr">
         <is>
           <t>Cu-tpy</t>
         </is>
       </c>
-      <c r="N129" t="n">
-        <v>0.4776876908334756</v>
+      <c r="M129" t="n">
+        <v>1.014834800000001</v>
       </c>
     </row>
     <row r="130">
@@ -6915,39 +6526,36 @@
         <v>3.04</v>
       </c>
       <c r="D130" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E130" t="n">
-        <v>2</v>
+        <v>2.625</v>
       </c>
       <c r="F130" t="n">
-        <v>2.625</v>
+        <v>1</v>
       </c>
       <c r="G130" t="n">
-        <v>1</v>
+        <v>1.143</v>
       </c>
       <c r="H130" t="n">
         <v>1.143</v>
       </c>
       <c r="I130" t="n">
-        <v>1.143</v>
+        <v>1</v>
       </c>
       <c r="J130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K130" t="n">
-        <v>0</v>
-      </c>
-      <c r="L130" t="n">
-        <v>0.468058882235529</v>
-      </c>
-      <c r="M130" t="inlineStr">
+        <v>1.477847</v>
+      </c>
+      <c r="L130" t="inlineStr">
         <is>
           <t>Ce-phen</t>
         </is>
       </c>
-      <c r="N130" t="n">
-        <v>0.4917150286691034</v>
+      <c r="M130" t="n">
+        <v>1.642977390345236</v>
       </c>
     </row>
     <row r="131">
@@ -6965,39 +6573,36 @@
         <v>3.04</v>
       </c>
       <c r="D131" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E131" t="n">
-        <v>2</v>
+        <v>2.921</v>
       </c>
       <c r="F131" t="n">
-        <v>2.921</v>
+        <v>1</v>
       </c>
       <c r="G131" t="n">
-        <v>1</v>
+        <v>1.027</v>
       </c>
       <c r="H131" t="n">
         <v>1.027</v>
       </c>
       <c r="I131" t="n">
-        <v>1.027</v>
+        <v>9</v>
       </c>
       <c r="J131" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>0</v>
-      </c>
-      <c r="L131" t="n">
-        <v>0.467538522323192</v>
-      </c>
-      <c r="M131" t="inlineStr">
+        <v>1.495429</v>
+      </c>
+      <c r="L131" t="inlineStr">
         <is>
           <t>Dy-phen</t>
         </is>
       </c>
-      <c r="N131" t="n">
-        <v>0.4993896504163902</v>
+      <c r="M131" t="n">
+        <v>1.629279361361112</v>
       </c>
     </row>
     <row r="132">
@@ -7015,39 +6620,36 @@
         <v>3.04</v>
       </c>
       <c r="D132" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E132" t="n">
-        <v>2</v>
+        <v>2.988</v>
       </c>
       <c r="F132" t="n">
-        <v>2.988</v>
+        <v>1</v>
       </c>
       <c r="G132" t="n">
-        <v>1</v>
+        <v>1.004</v>
       </c>
       <c r="H132" t="n">
         <v>1.004</v>
       </c>
       <c r="I132" t="n">
-        <v>1.004</v>
+        <v>11</v>
       </c>
       <c r="J132" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K132" t="n">
-        <v>0</v>
-      </c>
-      <c r="L132" t="n">
-        <v>0.4675250501002</v>
-      </c>
-      <c r="M132" t="inlineStr">
+        <v>1.505762</v>
+      </c>
+      <c r="L132" t="inlineStr">
         <is>
           <t>Er-phen</t>
         </is>
       </c>
-      <c r="N132" t="n">
-        <v>0.4716890769333375</v>
+      <c r="M132" t="n">
+        <v>1.553205430666668</v>
       </c>
     </row>
     <row r="133">
@@ -7065,39 +6667,36 @@
         <v>3.04</v>
       </c>
       <c r="D133" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E133" t="n">
-        <v>2</v>
+        <v>4.511</v>
       </c>
       <c r="F133" t="n">
-        <v>4.511</v>
+        <v>1</v>
       </c>
       <c r="G133" t="n">
-        <v>1</v>
+        <v>0.665</v>
       </c>
       <c r="H133" t="n">
         <v>0.665</v>
       </c>
       <c r="I133" t="n">
-        <v>0.665</v>
+        <v>0</v>
       </c>
       <c r="J133" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K133" t="n">
-        <v>6</v>
-      </c>
-      <c r="L133" t="n">
-        <v>0.466008292610692</v>
-      </c>
-      <c r="M133" t="inlineStr">
+        <v>1.015029</v>
+      </c>
+      <c r="L133" t="inlineStr">
         <is>
           <t>Rh-phen</t>
         </is>
       </c>
-      <c r="N133" t="n">
-        <v>0.500229959023833</v>
+      <c r="M133" t="n">
+        <v>1.219000210416667</v>
       </c>
     </row>
     <row r="134">
@@ -7115,39 +6714,36 @@
         <v>3.04</v>
       </c>
       <c r="D134" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E134" t="n">
-        <v>2</v>
+        <v>3.046</v>
       </c>
       <c r="F134" t="n">
-        <v>3.046</v>
+        <v>1</v>
       </c>
       <c r="G134" t="n">
-        <v>1</v>
+        <v>0.985</v>
       </c>
       <c r="H134" t="n">
         <v>0.985</v>
       </c>
       <c r="I134" t="n">
-        <v>0.985</v>
+        <v>13</v>
       </c>
       <c r="J134" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K134" t="n">
-        <v>0</v>
-      </c>
-      <c r="L134" t="n">
-        <v>0.464960127591707</v>
-      </c>
-      <c r="M134" t="inlineStr">
+        <v>1.479314</v>
+      </c>
+      <c r="L134" t="inlineStr">
         <is>
           <t>Yb-phen</t>
         </is>
       </c>
-      <c r="N134" t="n">
-        <v>0.5111216815422869</v>
+      <c r="M134" t="n">
+        <v>1.716601411333334</v>
       </c>
     </row>
     <row r="135">
@@ -7165,39 +6761,36 @@
         <v>3.04</v>
       </c>
       <c r="D135" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E135" t="n">
-        <v>2</v>
+        <v>2.849</v>
       </c>
       <c r="F135" t="n">
-        <v>2.849</v>
+        <v>1</v>
       </c>
       <c r="G135" t="n">
-        <v>1</v>
+        <v>1.053</v>
       </c>
       <c r="H135" t="n">
         <v>1.053</v>
       </c>
       <c r="I135" t="n">
-        <v>1.053</v>
+        <v>7</v>
       </c>
       <c r="J135" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K135" t="n">
-        <v>0</v>
-      </c>
-      <c r="L135" t="n">
-        <v>0.464905956112853</v>
-      </c>
-      <c r="M135" t="inlineStr">
+        <v>1.499809</v>
+      </c>
+      <c r="L135" t="inlineStr">
         <is>
           <t>Gd-phen</t>
         </is>
       </c>
-      <c r="N135" t="n">
-        <v>0.5841902534259727</v>
+      <c r="M135" t="n">
+        <v>1.534397212194445</v>
       </c>
     </row>
     <row r="136">
@@ -7215,39 +6808,36 @@
         <v>3.04</v>
       </c>
       <c r="D136" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E136" t="n">
-        <v>2</v>
+        <v>2.705</v>
       </c>
       <c r="F136" t="n">
-        <v>2.705</v>
+        <v>1</v>
       </c>
       <c r="G136" t="n">
-        <v>1</v>
+        <v>1.109</v>
       </c>
       <c r="H136" t="n">
         <v>1.109</v>
       </c>
       <c r="I136" t="n">
-        <v>1.109</v>
+        <v>3</v>
       </c>
       <c r="J136" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K136" t="n">
-        <v>0</v>
-      </c>
-      <c r="L136" t="n">
-        <v>0.464059211360467</v>
-      </c>
-      <c r="M136" t="inlineStr">
+        <v>1.4841</v>
+      </c>
+      <c r="L136" t="inlineStr">
         <is>
           <t>Nd-phen</t>
         </is>
       </c>
-      <c r="N136" t="n">
-        <v>0.4888381912439083</v>
+      <c r="M136" t="n">
+        <v>1.631257657488096</v>
       </c>
     </row>
     <row r="137">
@@ -7265,39 +6855,36 @@
         <v>3.04</v>
       </c>
       <c r="D137" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E137" t="n">
-        <v>2</v>
+        <v>3.071</v>
       </c>
       <c r="F137" t="n">
-        <v>3.071</v>
+        <v>1</v>
       </c>
       <c r="G137" t="n">
-        <v>1</v>
+        <v>0.977</v>
       </c>
       <c r="H137" t="n">
         <v>0.977</v>
       </c>
       <c r="I137" t="n">
-        <v>0.977</v>
+        <v>14</v>
       </c>
       <c r="J137" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K137" t="n">
-        <v>0</v>
-      </c>
-      <c r="L137" t="n">
-        <v>0.462251169004676</v>
-      </c>
-      <c r="M137" t="inlineStr">
+        <v>1.483216</v>
+      </c>
+      <c r="L137" t="inlineStr">
         <is>
           <t>Lu-phen</t>
         </is>
       </c>
-      <c r="N137" t="n">
-        <v>0.4886319434913194</v>
+      <c r="M137" t="n">
+        <v>1.635016916833334</v>
       </c>
     </row>
     <row r="138">
@@ -7315,39 +6902,36 @@
         <v>3.04</v>
       </c>
       <c r="D138" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E138" t="n">
-        <v>2</v>
+        <v>2.532</v>
       </c>
       <c r="F138" t="n">
-        <v>2.532</v>
+        <v>1</v>
       </c>
       <c r="G138" t="n">
-        <v>1</v>
+        <v>1.63</v>
       </c>
       <c r="H138" t="n">
-        <v>1.63</v>
+        <v>0.79</v>
       </c>
       <c r="I138" t="n">
-        <v>0.79</v>
+        <v>0</v>
       </c>
       <c r="J138" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K138" t="n">
-        <v>3</v>
-      </c>
-      <c r="L138" t="n">
-        <v>0.45958064516129</v>
-      </c>
-      <c r="M138" t="inlineStr">
+        <v>1.064441</v>
+      </c>
+      <c r="L138" t="inlineStr">
         <is>
           <t>V-phen</t>
         </is>
       </c>
-      <c r="N138" t="n">
-        <v>0.4964307818269875</v>
+      <c r="M138" t="n">
+        <v>1.270439217809523</v>
       </c>
     </row>
     <row r="139">
@@ -7365,39 +6949,36 @@
         <v>3.04</v>
       </c>
       <c r="D139" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E139" t="n">
-        <v>2</v>
+        <v>2.956</v>
       </c>
       <c r="F139" t="n">
-        <v>2.956</v>
+        <v>1</v>
       </c>
       <c r="G139" t="n">
-        <v>1</v>
+        <v>1.015</v>
       </c>
       <c r="H139" t="n">
         <v>1.015</v>
       </c>
       <c r="I139" t="n">
-        <v>1.015</v>
+        <v>10</v>
       </c>
       <c r="J139" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K139" t="n">
-        <v>0</v>
-      </c>
-      <c r="L139" t="n">
-        <v>0.457235536657647</v>
-      </c>
-      <c r="M139" t="inlineStr">
+        <v>1.44145</v>
+      </c>
+      <c r="L139" t="inlineStr">
         <is>
           <t>Ho-phen</t>
         </is>
       </c>
-      <c r="N139" t="n">
-        <v>0.4846784489619198</v>
+      <c r="M139" t="n">
+        <v>1.600347259896824</v>
       </c>
     </row>
     <row r="140">
@@ -7415,39 +6996,36 @@
         <v>3.04</v>
       </c>
       <c r="D140" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E140" t="n">
-        <v>2</v>
+        <v>4.878</v>
       </c>
       <c r="F140" t="n">
-        <v>4.878</v>
+        <v>1</v>
       </c>
       <c r="G140" t="n">
-        <v>1</v>
+        <v>1.66</v>
       </c>
       <c r="H140" t="n">
-        <v>1.66</v>
+        <v>0.615</v>
       </c>
       <c r="I140" t="n">
-        <v>0.615</v>
+        <v>0</v>
       </c>
       <c r="J140" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K140" t="n">
-        <v>3</v>
-      </c>
-      <c r="L140" t="n">
-        <v>0.456987473266117</v>
-      </c>
-      <c r="M140" t="inlineStr">
+        <v>1.029483</v>
+      </c>
+      <c r="L140" t="inlineStr">
         <is>
           <t>Cr-phen</t>
         </is>
       </c>
-      <c r="N140" t="n">
-        <v>0.4933603810452006</v>
+      <c r="M140" t="n">
+        <v>1.27054676972619</v>
       </c>
     </row>
     <row r="141">
@@ -7465,39 +7043,36 @@
         <v>3.04</v>
       </c>
       <c r="D141" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E141" t="n">
-        <v>2</v>
+        <v>4.348</v>
       </c>
       <c r="F141" t="n">
-        <v>4.348</v>
+        <v>1</v>
       </c>
       <c r="G141" t="n">
-        <v>1</v>
+        <v>2.16</v>
       </c>
       <c r="H141" t="n">
-        <v>2.16</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I141" t="n">
-        <v>0.6899999999999999</v>
+        <v>0</v>
       </c>
       <c r="J141" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K141" t="n">
-        <v>3</v>
-      </c>
-      <c r="L141" t="n">
-        <v>0.455660145249741</v>
-      </c>
-      <c r="M141" t="inlineStr">
+        <v>1.039938</v>
+      </c>
+      <c r="L141" t="inlineStr">
         <is>
           <t>Mo-phen</t>
         </is>
       </c>
-      <c r="N141" t="n">
-        <v>0.4803005734329527</v>
+      <c r="M141" t="n">
+        <v>1.184956584750003</v>
       </c>
     </row>
     <row r="142">
@@ -7515,39 +7090,36 @@
         <v>3.04</v>
       </c>
       <c r="D142" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E142" t="n">
-        <v>2</v>
+        <v>2.78</v>
       </c>
       <c r="F142" t="n">
-        <v>2.78</v>
+        <v>1</v>
       </c>
       <c r="G142" t="n">
-        <v>1</v>
+        <v>1.079</v>
       </c>
       <c r="H142" t="n">
         <v>1.079</v>
       </c>
       <c r="I142" t="n">
-        <v>1.079</v>
+        <v>5</v>
       </c>
       <c r="J142" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K142" t="n">
-        <v>0</v>
-      </c>
-      <c r="L142" t="n">
-        <v>0.452485294117647</v>
-      </c>
-      <c r="M142" t="inlineStr">
+        <v>1.39301</v>
+      </c>
+      <c r="L142" t="inlineStr">
         <is>
           <t>Sm-phen</t>
         </is>
       </c>
-      <c r="N142" t="n">
-        <v>0.5011646300270653</v>
+      <c r="M142" t="n">
+        <v>1.598126964416666</v>
       </c>
     </row>
     <row r="143">
@@ -7565,39 +7137,36 @@
         <v>3.04</v>
       </c>
       <c r="D143" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E143" t="n">
-        <v>2</v>
+        <v>2.852</v>
       </c>
       <c r="F143" t="n">
-        <v>2.852</v>
+        <v>1</v>
       </c>
       <c r="G143" t="n">
-        <v>1</v>
+        <v>0.994</v>
       </c>
       <c r="H143" t="n">
         <v>0.994</v>
       </c>
       <c r="I143" t="n">
-        <v>0.994</v>
+        <v>12</v>
       </c>
       <c r="J143" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K143" t="n">
-        <v>0</v>
-      </c>
-      <c r="L143" t="n">
-        <v>0.45200976612696</v>
-      </c>
-      <c r="M143" t="inlineStr">
+        <v>1.419205</v>
+      </c>
+      <c r="L143" t="inlineStr">
         <is>
           <t>Tm-phen</t>
         </is>
       </c>
-      <c r="N143" t="n">
-        <v>0.4902792631160333</v>
+      <c r="M143" t="n">
+        <v>1.526551644833333</v>
       </c>
     </row>
     <row r="144">
@@ -7615,39 +7184,36 @@
         <v>3.04</v>
       </c>
       <c r="D144" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E144" t="n">
-        <v>2</v>
+        <v>5.556</v>
       </c>
       <c r="F144" t="n">
-        <v>5.556</v>
+        <v>1</v>
       </c>
       <c r="G144" t="n">
-        <v>1</v>
+        <v>0.72</v>
       </c>
       <c r="H144" t="n">
         <v>0.72</v>
       </c>
       <c r="I144" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
       </c>
       <c r="K144" t="n">
-        <v>0</v>
-      </c>
-      <c r="L144" t="n">
-        <v>0.414628369866465</v>
-      </c>
-      <c r="M144" t="inlineStr">
+        <v>0.764731</v>
+      </c>
+      <c r="L144" t="inlineStr">
         <is>
           <t>Zr-phen</t>
         </is>
       </c>
-      <c r="N144" t="n">
-        <v>0.5074703547007139</v>
+      <c r="M144" t="n">
+        <v>0.9823297272500018</v>
       </c>
     </row>
     <row r="145">
@@ -7665,39 +7231,36 @@
         <v>3.04</v>
       </c>
       <c r="D145" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E145" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F145" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G145" t="n">
-        <v>1</v>
+        <v>2.36</v>
       </c>
       <c r="H145" t="n">
-        <v>2.36</v>
+        <v>0.6</v>
       </c>
       <c r="I145" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
       </c>
       <c r="K145" t="n">
-        <v>0</v>
-      </c>
-      <c r="L145" t="n">
-        <v>0.370939632545932</v>
-      </c>
-      <c r="M145" t="inlineStr">
+        <v>0.509731</v>
+      </c>
+      <c r="L145" t="inlineStr">
         <is>
           <t>W-tpy</t>
         </is>
       </c>
-      <c r="N145" t="n">
-        <v>0.4190721420065808</v>
+      <c r="M145" t="n">
+        <v>0.73733078</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/predicted_with_all_scores.xlsx
+++ b/outputs/predicted_with_all_scores.xlsx
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2.499090169999995</v>
+        <v>2.499090169999996</v>
       </c>
     </row>
     <row r="6">
@@ -774,7 +774,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>2.559356454999998</v>
+        <v>2.559356454999999</v>
       </c>
     </row>
     <row r="8">
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>1.686779487333331</v>
+        <v>1.686779487333332</v>
       </c>
     </row>
     <row r="15">
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>1.682518849749998</v>
+        <v>1.682518849749997</v>
       </c>
     </row>
     <row r="16">
@@ -1291,7 +1291,7 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>2.093686274999999</v>
+        <v>2.093686275</v>
       </c>
     </row>
     <row r="19">
@@ -1714,7 +1714,7 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>2.05164653166667</v>
+        <v>2.051646531666671</v>
       </c>
     </row>
     <row r="28">
@@ -2278,7 +2278,7 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>0.9823297272500018</v>
+        <v>0.982329727250002</v>
       </c>
     </row>
     <row r="40">
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>1.729923306666671</v>
+        <v>1.729923306666672</v>
       </c>
     </row>
     <row r="45">
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="M45" t="n">
-        <v>0.8950157507857142</v>
+        <v>0.8950157507857144</v>
       </c>
     </row>
     <row r="46">
@@ -2654,7 +2654,7 @@
         </is>
       </c>
       <c r="M47" t="n">
-        <v>1.232314421571427</v>
+        <v>1.232314421571426</v>
       </c>
     </row>
     <row r="48">
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>1.270439217809523</v>
+        <v>1.270439217809524</v>
       </c>
     </row>
     <row r="53">
@@ -3077,7 +3077,7 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>1.608147959999999</v>
+        <v>1.60814796</v>
       </c>
     </row>
     <row r="57">
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>1.392345855</v>
+        <v>1.392345854999999</v>
       </c>
     </row>
     <row r="59">
@@ -3641,7 +3641,7 @@
         </is>
       </c>
       <c r="M68" t="n">
-        <v>1.856169095</v>
+        <v>1.856169095000001</v>
       </c>
     </row>
     <row r="69">
@@ -4440,7 +4440,7 @@
         </is>
       </c>
       <c r="M85" t="n">
-        <v>1.825684365499999</v>
+        <v>1.8256843655</v>
       </c>
     </row>
     <row r="86">
@@ -5145,7 +5145,7 @@
         </is>
       </c>
       <c r="M100" t="n">
-        <v>0.8326255677738095</v>
+        <v>0.8326255677738094</v>
       </c>
     </row>
     <row r="101">
@@ -5239,7 +5239,7 @@
         </is>
       </c>
       <c r="M102" t="n">
-        <v>1.358545954999999</v>
+        <v>1.358545955</v>
       </c>
     </row>
     <row r="103">
@@ -5662,7 +5662,7 @@
         </is>
       </c>
       <c r="M111" t="n">
-        <v>0.9554049913333365</v>
+        <v>0.9554049913333366</v>
       </c>
     </row>
     <row r="112">
@@ -5897,7 +5897,7 @@
         </is>
       </c>
       <c r="M116" t="n">
-        <v>1.232314421571427</v>
+        <v>1.232314421571426</v>
       </c>
     </row>
     <row r="117">
@@ -6132,7 +6132,7 @@
         </is>
       </c>
       <c r="M121" t="n">
-        <v>1.786860770250002</v>
+        <v>1.786860770250001</v>
       </c>
     </row>
     <row r="122">
@@ -6226,7 +6226,7 @@
         </is>
       </c>
       <c r="M123" t="n">
-        <v>0.8326255677738095</v>
+        <v>0.8326255677738094</v>
       </c>
     </row>
     <row r="124">
@@ -6367,7 +6367,7 @@
         </is>
       </c>
       <c r="M126" t="n">
-        <v>0.8950157507857142</v>
+        <v>0.8950157507857144</v>
       </c>
     </row>
     <row r="127">
@@ -6931,7 +6931,7 @@
         </is>
       </c>
       <c r="M138" t="n">
-        <v>1.270439217809523</v>
+        <v>1.270439217809524</v>
       </c>
     </row>
     <row r="139">
@@ -7213,7 +7213,7 @@
         </is>
       </c>
       <c r="M144" t="n">
-        <v>0.9823297272500018</v>
+        <v>0.982329727250002</v>
       </c>
     </row>
     <row r="145">
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="M145" t="n">
-        <v>0.73733078</v>
+        <v>0.7373307800000002</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/predicted_with_all_scores.xlsx
+++ b/outputs/predicted_with_all_scores.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M145"/>
+  <dimension ref="A1:M144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>2.572706875000004</v>
+        <v>2.569328395000004</v>
       </c>
     </row>
     <row r="3">
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1.833986159999998</v>
+        <v>1.833073944999998</v>
       </c>
     </row>
     <row r="4">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>2.518268969999997</v>
+        <v>2.535290779999999</v>
       </c>
     </row>
     <row r="5">
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2.499090169999996</v>
+        <v>2.507809214999993</v>
       </c>
     </row>
     <row r="6">
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>1.703361214750003</v>
+        <v>1.741904397583335</v>
       </c>
     </row>
     <row r="7">
@@ -774,7 +774,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>2.559356454999999</v>
+        <v>2.556022789999999</v>
       </c>
     </row>
     <row r="8">
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>2.535438674999996</v>
+        <v>2.546527004999995</v>
       </c>
     </row>
     <row r="9">
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>1.528264721694442</v>
+        <v>1.522577470916664</v>
       </c>
     </row>
     <row r="10">
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>2.004564945000003</v>
+        <v>1.959021177500003</v>
       </c>
     </row>
     <row r="11">
@@ -962,7 +962,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>2.060342220000004</v>
+        <v>1.900514155000002</v>
       </c>
     </row>
     <row r="12">
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>2.171825580000004</v>
+        <v>2.10215050214286</v>
       </c>
     </row>
     <row r="13">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>2.244602229999997</v>
+        <v>2.281260404999996</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Pt</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1077,86 +1077,86 @@
         <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>3.509</v>
+        <v>3.333</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="H14" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K14" t="n">
-        <v>1.706986</v>
+        <v>1.602375</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Cu-acac</t>
+          <t>Pt-acac</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>1.686779487333332</v>
+        <v>1.412167055642858</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Pt</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>acac</t>
+          <t>phen</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="D15" t="n">
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.333</v>
+        <v>2.41</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6</v>
+        <v>0.83</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6</v>
+        <v>0.83</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K15" t="n">
-        <v>1.602375</v>
+        <v>1.169628</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Pt-acac</t>
+          <t>Mn-phen</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>1.682518849749997</v>
+        <v>1.238768308333331</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Ti</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1171,180 +1171,180 @@
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>2.41</v>
+        <v>6.612</v>
       </c>
       <c r="F16" t="n">
         <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>0.83</v>
+        <v>1.54</v>
       </c>
       <c r="H16" t="n">
-        <v>0.83</v>
+        <v>0.67</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>1.169628</v>
+        <v>1.027571</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Mn-phen</t>
+          <t>Ti-phen</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>1.238984808666664</v>
+        <v>1.109990123999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ti</t>
+          <t>Ni</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>phen</t>
+          <t>acac</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3.04</v>
+        <v>3.44</v>
       </c>
       <c r="D17" t="n">
         <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>6.612</v>
+        <v>2.899</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>1.54</v>
+        <v>1.91</v>
       </c>
       <c r="H17" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K17" t="n">
-        <v>1.027571</v>
+        <v>2.131648</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Ti-phen</t>
+          <t>Ni-acac</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>1.093146494583332</v>
+        <v>2.054152114999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ni</t>
+          <t>Zn</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>acac</t>
+          <t>phen</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.899</v>
+        <v>2.703</v>
       </c>
       <c r="F18" t="n">
         <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>1.91</v>
+        <v>0.74</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.74</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K18" t="n">
-        <v>2.131648</v>
+        <v>1.118473</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Ni-acac</t>
+          <t>Zn-phen</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>2.093686275</v>
+        <v>1.321589214583332</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Zn</t>
+          <t>Yb</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>phen</t>
+          <t>acac</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3.04</v>
+        <v>3.44</v>
       </c>
       <c r="D19" t="n">
         <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>2.703</v>
+        <v>3.046</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>0.74</v>
+        <v>0.985</v>
       </c>
       <c r="H19" t="n">
-        <v>0.74</v>
+        <v>0.985</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>1.118473</v>
+        <v>2.556934</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Zn-phen</t>
+          <t>Yb-acac</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>1.324663261666665</v>
+        <v>2.542488035000003</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Yb</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1359,39 +1359,39 @@
         <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>3.046</v>
+        <v>2.41</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>0.985</v>
+        <v>1.55</v>
       </c>
       <c r="H20" t="n">
-        <v>0.985</v>
+        <v>0.83</v>
       </c>
       <c r="I20" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K20" t="n">
-        <v>2.556934</v>
+        <v>2.156795</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Yb-acac</t>
+          <t>Mn-acac</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>2.494475214999994</v>
+        <v>1.982425661833334</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Ir</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1406,60 +1406,60 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.41</v>
+        <v>4.412</v>
       </c>
       <c r="F21" t="n">
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>1.55</v>
+        <v>2.2</v>
       </c>
       <c r="H21" t="n">
-        <v>0.83</v>
+        <v>0.68</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K21" t="n">
-        <v>2.156795</v>
+        <v>2.136792</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Mn-acac</t>
+          <t>Ir-acac</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>2.111948335000003</v>
+        <v>1.808368617916667</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ir</t>
+          <t>Ru</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>acac</t>
+          <t>bpy</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="D22" t="n">
         <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>4.412</v>
+        <v>2.941</v>
       </c>
       <c r="F22" t="n">
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>2.2</v>
+        <v>0.68</v>
       </c>
       <c r="H22" t="n">
         <v>0.68</v>
@@ -1471,68 +1471,68 @@
         <v>6</v>
       </c>
       <c r="K22" t="n">
-        <v>2.136792</v>
+        <v>1.489393</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Ir-acac</t>
+          <t>Ru-bpy</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>2.073819760000005</v>
+        <v>1.365390601267857</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ru</t>
+          <t>Lu</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>bpy</t>
+          <t>acac</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3.04</v>
+        <v>3.44</v>
       </c>
       <c r="D23" t="n">
         <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>2.941</v>
+        <v>3.071</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>0.68</v>
+        <v>0.977</v>
       </c>
       <c r="H23" t="n">
-        <v>0.68</v>
+        <v>0.977</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J23" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>1.489393</v>
+        <v>2.580205</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Ru-bpy</t>
+          <t>Lu-acac</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>1.34519161990476</v>
+        <v>2.513645233749995</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>Mg</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1547,39 +1547,39 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.071</v>
+        <v>2.778</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>0.977</v>
+        <v>1.31</v>
       </c>
       <c r="H24" t="n">
-        <v>0.977</v>
+        <v>0.72</v>
       </c>
       <c r="I24" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>2.580205</v>
+        <v>2.168522</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Lu-acac</t>
+          <t>Mg-acac</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>2.487813434999994</v>
+        <v>2.060985192499997</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Mg</t>
+          <t>Ca</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1594,16 +1594,16 @@
         <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>2.778</v>
+        <v>2</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>1.31</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>0.72</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -1612,21 +1612,21 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>2.168522</v>
+        <v>2.163146</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Mg-acac</t>
+          <t>Ca-acac</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>2.157215669999999</v>
+        <v>2.280228944999996</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ca</t>
+          <t>Cr</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1641,39 +1641,39 @@
         <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>4.878</v>
       </c>
       <c r="F26" t="n">
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>1.66</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>0.615</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K26" t="n">
-        <v>2.163146</v>
+        <v>2.142304</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Ca-acac</t>
+          <t>Cr-acac</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>2.257774734999997</v>
+        <v>1.914118270000004</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cr</t>
+          <t>Ce</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1688,39 +1688,39 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>4.878</v>
+        <v>2.625</v>
       </c>
       <c r="F27" t="n">
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>1.66</v>
+        <v>1.12</v>
       </c>
       <c r="H27" t="n">
-        <v>0.615</v>
+        <v>0.97</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>2.142304</v>
+        <v>2.534345</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Cr-acac</t>
+          <t>Ce-acac</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>2.051646531666671</v>
+        <v>2.472506719999991</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ce</t>
+          <t>Ru</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1735,39 +1735,39 @@
         <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>2.625</v>
+        <v>4.412</v>
       </c>
       <c r="F28" t="n">
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>1.12</v>
+        <v>2.2</v>
       </c>
       <c r="H28" t="n">
-        <v>0.97</v>
+        <v>0.68</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K28" t="n">
-        <v>2.534345</v>
+        <v>2.125508</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Ce-acac</t>
+          <t>Ru-acac</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>2.429245519999998</v>
+        <v>1.808368617916667</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Ru</t>
+          <t>Nb</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1782,39 +1782,39 @@
         <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>4.412</v>
+        <v>6.757</v>
       </c>
       <c r="F29" t="n">
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>2.2</v>
+        <v>0.74</v>
       </c>
       <c r="H29" t="n">
-        <v>0.68</v>
+        <v>0.74</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>2.125508</v>
+        <v>2.532645</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Ru-acac</t>
+          <t>Nb-acac</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>2.073819760000005</v>
+        <v>1.659590524940475</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Nb</t>
+          <t>Ho</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1829,133 +1829,133 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>6.757</v>
+        <v>2.956</v>
       </c>
       <c r="F30" t="n">
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>0.74</v>
+        <v>1.015</v>
       </c>
       <c r="H30" t="n">
-        <v>0.74</v>
+        <v>1.015</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>2.532645</v>
+        <v>2.530767</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Nb-acac</t>
+          <t>Ho-acac</t>
         </is>
       </c>
       <c r="M30" t="n">
-        <v>2.330184813750001</v>
+        <v>2.533607095000005</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ho</t>
+          <t>Eu</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>acac</t>
+          <t>tpy</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.956</v>
+        <v>2.679</v>
       </c>
       <c r="F31" t="n">
         <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>1.015</v>
+        <v>1.2</v>
       </c>
       <c r="H31" t="n">
-        <v>1.015</v>
+        <v>1.12</v>
       </c>
       <c r="I31" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>2.530767</v>
+        <v>1.799442</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Ho-acac</t>
+          <t>Eu-tpy</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>2.533624240000006</v>
+        <v>1.806963440000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Eu</t>
+          <t>Ti</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>tpy</t>
+          <t>acac</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3.04</v>
+        <v>3.44</v>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>2.679</v>
+        <v>6.612</v>
       </c>
       <c r="F32" t="n">
         <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>1.2</v>
+        <v>1.54</v>
       </c>
       <c r="H32" t="n">
-        <v>1.12</v>
+        <v>0.605</v>
       </c>
       <c r="I32" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>1.799442</v>
+        <v>2.068608</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Eu-tpy</t>
+          <t>Ti-acac</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>1.817770502500001</v>
+        <v>1.838331877023809</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Ti</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1970,180 +1970,180 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>6.612</v>
+        <v>5.66</v>
       </c>
       <c r="F33" t="n">
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="H33" t="n">
-        <v>0.605</v>
+        <v>0.53</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>2.068608</v>
+        <v>1.82443</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Ti-acac</t>
+          <t>V-acac</t>
         </is>
       </c>
       <c r="M33" t="n">
-        <v>2.004730914999999</v>
+        <v>1.680100776500002</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>Zr</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>acac</t>
+          <t>tpy</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>5.66</v>
+        <v>5.556</v>
       </c>
       <c r="F34" t="n">
         <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="H34" t="n">
-        <v>0.53</v>
+        <v>0.72</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>1.82443</v>
+        <v>1.126688</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>V-acac</t>
+          <t>Zr-tpy</t>
         </is>
       </c>
       <c r="M34" t="n">
-        <v>1.804944639000003</v>
+        <v>1.111443524583334</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Zr</t>
+          <t>Eu</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>tpy</t>
+          <t>phen</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>3.04</v>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>5.556</v>
+        <v>2.814</v>
       </c>
       <c r="F35" t="n">
         <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>1.33</v>
+        <v>1.066</v>
       </c>
       <c r="H35" t="n">
-        <v>0.72</v>
+        <v>1.066</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>1.126688</v>
+        <v>1.510422</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Zr-tpy</t>
+          <t>Eu-phen</t>
         </is>
       </c>
       <c r="M35" t="n">
-        <v>1.088459400416668</v>
+        <v>1.555202598833335</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Eu</t>
+          <t>Zr</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>phen</t>
+          <t>cooh</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3.04</v>
+        <v>3.44</v>
       </c>
       <c r="D36" t="n">
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.814</v>
+        <v>5.556</v>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>1.066</v>
+        <v>0.72</v>
       </c>
       <c r="H36" t="n">
-        <v>1.066</v>
+        <v>0.72</v>
       </c>
       <c r="I36" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>1.510422</v>
+        <v>0.835874</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Eu-phen</t>
+          <t>Zr-cooh</t>
         </is>
       </c>
       <c r="M36" t="n">
-        <v>1.544629370333336</v>
+        <v>1.017364876833332</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Zr</t>
+          <t>Tb</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2158,180 +2158,180 @@
         <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>5.556</v>
+        <v>2.74</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.72</v>
+        <v>1.2</v>
       </c>
       <c r="H37" t="n">
-        <v>0.72</v>
+        <v>1.095</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0.835874</v>
+        <v>2.00169</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Zr-cooh</t>
+          <t>Tb-cooh</t>
         </is>
       </c>
       <c r="M37" t="n">
-        <v>1.087248401999998</v>
+        <v>2.035660143142856</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Tb</t>
+          <t>Zr</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>cooh</t>
+          <t>bpy</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="D38" t="n">
         <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>2.74</v>
+        <v>5.556</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>1.2</v>
+        <v>0.72</v>
       </c>
       <c r="H38" t="n">
-        <v>1.095</v>
+        <v>0.72</v>
       </c>
       <c r="I38" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>2.00169</v>
+        <v>1.200858</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Tb-cooh</t>
+          <t>Zr-bpy</t>
         </is>
       </c>
       <c r="M38" t="n">
-        <v>2.039399342999998</v>
+        <v>0.9721486894821445</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Zr</t>
+          <t>Tb</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>bpy</t>
+          <t>cooh</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3.04</v>
+        <v>3.44</v>
       </c>
       <c r="D39" t="n">
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>5.556</v>
+        <v>2.74</v>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.72</v>
+        <v>1.2</v>
       </c>
       <c r="H39" t="n">
-        <v>0.72</v>
+        <v>1.095</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>1.200858</v>
+        <v>2.103654</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Zr-bpy</t>
+          <t>Tb-cooh</t>
         </is>
       </c>
       <c r="M39" t="n">
-        <v>0.982329727250002</v>
+        <v>2.035660143142856</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Tb</t>
+          <t>Ir</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>cooh</t>
+          <t>bpy</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="D40" t="n">
         <v>2</v>
       </c>
       <c r="E40" t="n">
-        <v>2.74</v>
+        <v>4.412</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>1.2</v>
+        <v>0.68</v>
       </c>
       <c r="H40" t="n">
-        <v>1.095</v>
+        <v>0.68</v>
       </c>
       <c r="I40" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K40" t="n">
-        <v>2.103654</v>
+        <v>1.585818</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Tb-cooh</t>
+          <t>Ir-bpy</t>
         </is>
       </c>
       <c r="M40" t="n">
-        <v>2.039399342999998</v>
+        <v>1.481144786124999</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ir</t>
+          <t>Cd</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2346,39 +2346,39 @@
         <v>2</v>
       </c>
       <c r="E41" t="n">
-        <v>4.412</v>
+        <v>2.105</v>
       </c>
       <c r="F41" t="n">
         <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>0.68</v>
+        <v>0.95</v>
       </c>
       <c r="H41" t="n">
-        <v>0.68</v>
+        <v>0.95</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K41" t="n">
-        <v>1.585818</v>
+        <v>1.54896</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Ir-bpy</t>
+          <t>Cd-bpy</t>
         </is>
       </c>
       <c r="M41" t="n">
-        <v>1.335918219999998</v>
+        <v>1.455697885833332</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cd</t>
+          <t>Zn</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2393,16 +2393,16 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.105</v>
+        <v>2.703</v>
       </c>
       <c r="F42" t="n">
         <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>0.95</v>
+        <v>0.74</v>
       </c>
       <c r="H42" t="n">
-        <v>0.95</v>
+        <v>0.74</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -2411,21 +2411,21 @@
         <v>10</v>
       </c>
       <c r="K42" t="n">
-        <v>1.54896</v>
+        <v>1.528249</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Cd-bpy</t>
+          <t>Zn-bpy</t>
         </is>
       </c>
       <c r="M42" t="n">
-        <v>1.460513719761905</v>
+        <v>1.321589214583332</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Zn</t>
+          <t>Eu</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2440,39 +2440,39 @@
         <v>2</v>
       </c>
       <c r="E43" t="n">
-        <v>2.703</v>
+        <v>2.814</v>
       </c>
       <c r="F43" t="n">
         <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>0.74</v>
+        <v>1.2</v>
       </c>
       <c r="H43" t="n">
-        <v>0.74</v>
+        <v>1.066</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J43" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>1.528249</v>
+        <v>1.787093</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Zn-bpy</t>
+          <t>Eu-bpy</t>
         </is>
       </c>
       <c r="M43" t="n">
-        <v>1.324663261666665</v>
+        <v>1.744822492583337</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Eu</t>
+          <t>Pt</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2487,39 +2487,39 @@
         <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>2.814</v>
+        <v>3.333</v>
       </c>
       <c r="F44" t="n">
         <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="H44" t="n">
-        <v>1.066</v>
+        <v>0.6</v>
       </c>
       <c r="I44" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K44" t="n">
-        <v>1.787093</v>
+        <v>1.104241</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Eu-bpy</t>
+          <t>Pt-bpy</t>
         </is>
       </c>
       <c r="M44" t="n">
-        <v>1.729923306666672</v>
+        <v>0.9190281243928565</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Pt</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2534,39 +2534,39 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.333</v>
+        <v>3.279</v>
       </c>
       <c r="F45" t="n">
         <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>0.6</v>
+        <v>1.83</v>
       </c>
       <c r="H45" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K45" t="n">
-        <v>1.104241</v>
+        <v>1.56898</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Pt-bpy</t>
+          <t>Fe-bpy</t>
         </is>
       </c>
       <c r="M45" t="n">
-        <v>0.8950157507857144</v>
+        <v>1.387350583666668</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Ni</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2581,39 +2581,39 @@
         <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>3.279</v>
+        <v>2.899</v>
       </c>
       <c r="F46" t="n">
         <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="H46" t="n">
-        <v>0.61</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K46" t="n">
-        <v>1.56898</v>
+        <v>1.54663</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Fe-bpy</t>
+          <t>Ni-bpy</t>
         </is>
       </c>
       <c r="M46" t="n">
-        <v>1.396729021333336</v>
+        <v>1.469693507166663</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Ni</t>
+          <t>Cr</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2628,39 +2628,39 @@
         <v>2</v>
       </c>
       <c r="E47" t="n">
-        <v>2.899</v>
+        <v>4.878</v>
       </c>
       <c r="F47" t="n">
         <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>1.91</v>
+        <v>1.66</v>
       </c>
       <c r="H47" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.615</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K47" t="n">
-        <v>1.54663</v>
+        <v>1.514437</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Ni-bpy</t>
+          <t>Cr-bpy</t>
         </is>
       </c>
       <c r="M47" t="n">
-        <v>1.232314421571426</v>
+        <v>1.148117904666666</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cr</t>
+          <t>Yb</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2675,39 +2675,39 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>4.878</v>
+        <v>3.046</v>
       </c>
       <c r="F48" t="n">
         <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>1.66</v>
+        <v>0.985</v>
       </c>
       <c r="H48" t="n">
-        <v>0.615</v>
+        <v>0.985</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>1.514437</v>
+        <v>1.792761</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Cr-bpy</t>
+          <t>Yb-bpy</t>
         </is>
       </c>
       <c r="M48" t="n">
-        <v>1.27054676972619</v>
+        <v>1.701775563833334</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Yb</t>
+          <t>Rh</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2722,44 +2722,44 @@
         <v>2</v>
       </c>
       <c r="E49" t="n">
-        <v>3.046</v>
+        <v>4.511</v>
       </c>
       <c r="F49" t="n">
         <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>0.985</v>
+        <v>0.665</v>
       </c>
       <c r="H49" t="n">
-        <v>0.985</v>
+        <v>0.665</v>
       </c>
       <c r="I49" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K49" t="n">
-        <v>1.792761</v>
+        <v>1.410876</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Yb-bpy</t>
+          <t>Rh-bpy</t>
         </is>
       </c>
       <c r="M49" t="n">
-        <v>1.716601411333334</v>
+        <v>1.228062739684523</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Rh</t>
+          <t>Cd</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>bpy</t>
+          <t>phen</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -2769,44 +2769,44 @@
         <v>2</v>
       </c>
       <c r="E50" t="n">
-        <v>4.511</v>
+        <v>2.105</v>
       </c>
       <c r="F50" t="n">
         <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>0.665</v>
+        <v>0.95</v>
       </c>
       <c r="H50" t="n">
-        <v>0.665</v>
+        <v>0.95</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K50" t="n">
-        <v>1.410876</v>
+        <v>1.4</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Rh-bpy</t>
+          <t>Cd-phen</t>
         </is>
       </c>
       <c r="M50" t="n">
-        <v>1.219000210416667</v>
+        <v>1.455697885833332</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cd</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>phen</t>
+          <t>bpy</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -2816,39 +2816,39 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.105</v>
+        <v>2.532</v>
       </c>
       <c r="F51" t="n">
         <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>0.95</v>
+        <v>1.63</v>
       </c>
       <c r="H51" t="n">
-        <v>0.95</v>
+        <v>0.79</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K51" t="n">
-        <v>1.4</v>
+        <v>1.490735</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Cd-phen</t>
+          <t>V-bpy</t>
         </is>
       </c>
       <c r="M51" t="n">
-        <v>1.460513719761905</v>
+        <v>1.296561909499998</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>In</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2863,39 +2863,39 @@
         <v>2</v>
       </c>
       <c r="E52" t="n">
-        <v>2.532</v>
+        <v>3.75</v>
       </c>
       <c r="F52" t="n">
         <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>1.63</v>
+        <v>0.8</v>
       </c>
       <c r="H52" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K52" t="n">
-        <v>1.490735</v>
+        <v>1.487745</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>V-bpy</t>
+          <t>In-bpy</t>
         </is>
       </c>
       <c r="M52" t="n">
-        <v>1.270439217809524</v>
+        <v>1.393830866958332</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>In</t>
+          <t>Ca</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2910,86 +2910,86 @@
         <v>2</v>
       </c>
       <c r="E53" t="n">
-        <v>3.75</v>
+        <v>1.786</v>
       </c>
       <c r="F53" t="n">
         <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H53" t="n">
-        <v>0.8</v>
+        <v>1.12</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>1.487745</v>
+        <v>1.875867</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>In-bpy</t>
+          <t>Ca-bpy</t>
         </is>
       </c>
       <c r="M53" t="n">
-        <v>1.227699638333333</v>
+        <v>1.529093592333331</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Ca</t>
+          <t>Nd</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>bpy</t>
+          <t>cooh</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>3.04</v>
+        <v>3.44</v>
       </c>
       <c r="D54" t="n">
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>1.786</v>
+        <v>2.58</v>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>1.163</v>
       </c>
       <c r="H54" t="n">
-        <v>1.12</v>
+        <v>1.163</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>1.875867</v>
+        <v>2.064318</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Ca-bpy</t>
+          <t>Nd-cooh</t>
         </is>
       </c>
       <c r="M54" t="n">
-        <v>1.776833026428576</v>
+        <v>2.029187900000006</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Nd</t>
+          <t>Ca</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3004,133 +3004,133 @@
         <v>2</v>
       </c>
       <c r="E55" t="n">
-        <v>2.58</v>
+        <v>2</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>1.163</v>
+        <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>1.163</v>
+        <v>1</v>
       </c>
       <c r="I55" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>2.064318</v>
+        <v>1.444555</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Nd-cooh</t>
+          <t>Ca-cooh</t>
         </is>
       </c>
       <c r="M55" t="n">
-        <v>2.032157120000007</v>
+        <v>1.610020932999998</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Ca</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>cooh</t>
+          <t>bpy</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="D56" t="n">
         <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>3.077</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>1.88</v>
       </c>
       <c r="H56" t="n">
-        <v>1</v>
+        <v>0.65</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K56" t="n">
-        <v>1.444555</v>
+        <v>1.420009</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Ca-cooh</t>
+          <t>Co-bpy</t>
         </is>
       </c>
       <c r="M56" t="n">
-        <v>1.60814796</v>
+        <v>1.364748289166662</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>Mg</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>bpy</t>
+          <t>cooh</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>3.04</v>
+        <v>3.44</v>
       </c>
       <c r="D57" t="n">
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.077</v>
+        <v>2.778</v>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>1.88</v>
+        <v>1.31</v>
       </c>
       <c r="H57" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>1.420009</v>
+        <v>1.431071</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Co-bpy</t>
+          <t>Mg-cooh</t>
         </is>
       </c>
       <c r="M57" t="n">
-        <v>1.177943363916665</v>
+        <v>1.4346344025</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Mg</t>
+          <t>Zn</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3145,39 +3145,39 @@
         <v>2</v>
       </c>
       <c r="E58" t="n">
-        <v>2.778</v>
+        <v>3.333</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>1.31</v>
+        <v>1.65</v>
       </c>
       <c r="H58" t="n">
-        <v>0.72</v>
+        <v>0.6</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K58" t="n">
-        <v>1.431071</v>
+        <v>1.001426</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Mg-cooh</t>
+          <t>Zn-cooh</t>
         </is>
       </c>
       <c r="M58" t="n">
-        <v>1.392345854999999</v>
+        <v>1.188432502583335</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Zn</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3192,133 +3192,133 @@
         <v>2</v>
       </c>
       <c r="E59" t="n">
-        <v>3.333</v>
+        <v>2.685</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="H59" t="n">
-        <v>0.6</v>
+        <v>0.745</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K59" t="n">
-        <v>1.001426</v>
+        <v>1.442559</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Zn-cooh</t>
+          <t>Co-cooh</t>
         </is>
       </c>
       <c r="M59" t="n">
-        <v>1.036477192500002</v>
+        <v>1.450559354999999</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>Ce</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>cooh</t>
+          <t>bpy</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="D60" t="n">
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.685</v>
+        <v>2.625</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>1.88</v>
+        <v>1.143</v>
       </c>
       <c r="H60" t="n">
-        <v>0.745</v>
+        <v>1.143</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>1.442559</v>
+        <v>1.836598</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Co-cooh</t>
+          <t>Ce-bpy</t>
         </is>
       </c>
       <c r="M60" t="n">
-        <v>1.420292749999998</v>
+        <v>1.663242690666665</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Ce</t>
+          <t>Lu</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>bpy</t>
+          <t>cooh</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>3.04</v>
+        <v>3.44</v>
       </c>
       <c r="D61" t="n">
         <v>2</v>
       </c>
       <c r="E61" t="n">
-        <v>2.625</v>
+        <v>2.907</v>
       </c>
       <c r="F61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>1.143</v>
+        <v>1.27</v>
       </c>
       <c r="H61" t="n">
-        <v>1.143</v>
+        <v>1.032</v>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>1.836598</v>
+        <v>2.030865</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Ce-bpy</t>
+          <t>Lu-cooh</t>
         </is>
       </c>
       <c r="M61" t="n">
-        <v>1.642977390345236</v>
+        <v>2.006152105</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>Sm</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3333,39 +3333,39 @@
         <v>2</v>
       </c>
       <c r="E62" t="n">
-        <v>2.907</v>
+        <v>2.65</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="H62" t="n">
-        <v>1.032</v>
+        <v>1.132</v>
       </c>
       <c r="I62" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>2.030865</v>
+        <v>2.014408</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Lu-cooh</t>
+          <t>Sm-cooh</t>
         </is>
       </c>
       <c r="M62" t="n">
-        <v>2.02437581</v>
+        <v>1.950729275000002</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sm</t>
+          <t>Ni</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3380,345 +3380,345 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.65</v>
+        <v>2.899</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>1.17</v>
+        <v>1.91</v>
       </c>
       <c r="H63" t="n">
-        <v>1.132</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I63" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K63" t="n">
-        <v>2.014408</v>
+        <v>1.421477</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Sm-cooh</t>
+          <t>Ni-cooh</t>
         </is>
       </c>
       <c r="M63" t="n">
-        <v>2.012005377000002</v>
+        <v>1.391024605000001</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Ni</t>
+          <t>La</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>cooh</t>
+          <t>bpy</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="D64" t="n">
         <v>2</v>
       </c>
       <c r="E64" t="n">
-        <v>2.899</v>
+        <v>2.586</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G64" t="n">
-        <v>1.91</v>
+        <v>1.16</v>
       </c>
       <c r="H64" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.16</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>1.421477</v>
+        <v>1.820521</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Ni-cooh</t>
+          <t>La-bpy</t>
         </is>
       </c>
       <c r="M64" t="n">
-        <v>1.398795245000001</v>
+        <v>1.667973842333334</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>La</t>
+          <t>Ce</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>bpy</t>
+          <t>cooh</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>3.04</v>
+        <v>3.44</v>
       </c>
       <c r="D65" t="n">
         <v>2</v>
       </c>
       <c r="E65" t="n">
-        <v>2.586</v>
+        <v>2.508</v>
       </c>
       <c r="F65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="H65" t="n">
-        <v>1.16</v>
+        <v>1.196</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>1.820521</v>
+        <v>2.008039</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>La-bpy</t>
+          <t>Ce-cooh</t>
         </is>
       </c>
       <c r="M65" t="n">
-        <v>1.678677425559523</v>
+        <v>1.967235894999998</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Ce</t>
+          <t>Er</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>cooh</t>
+          <t>bpy</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="D66" t="n">
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.508</v>
+        <v>2.988</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>1.12</v>
+        <v>1.004</v>
       </c>
       <c r="H66" t="n">
-        <v>1.196</v>
+        <v>1.004</v>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>2.008039</v>
+        <v>1.816522</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Ce-cooh</t>
+          <t>Er-bpy</t>
         </is>
       </c>
       <c r="M66" t="n">
-        <v>1.871279280000001</v>
+        <v>1.501769991666667</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Er</t>
+          <t>La</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>bpy</t>
+          <t>cooh</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>3.04</v>
+        <v>3.44</v>
       </c>
       <c r="D67" t="n">
         <v>2</v>
       </c>
       <c r="E67" t="n">
-        <v>2.988</v>
+        <v>2.467</v>
       </c>
       <c r="F67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>1.004</v>
+        <v>1.1</v>
       </c>
       <c r="H67" t="n">
-        <v>1.004</v>
+        <v>1.216</v>
       </c>
       <c r="I67" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>1.816522</v>
+        <v>2.01619</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Er-bpy</t>
+          <t>La-cooh</t>
         </is>
       </c>
       <c r="M67" t="n">
-        <v>1.553205430666668</v>
+        <v>1.884624399999998</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>La</t>
+          <t>Sm</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>cooh</t>
+          <t>tpy</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="D68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E68" t="n">
-        <v>2.467</v>
+        <v>2.65</v>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="H68" t="n">
-        <v>1.216</v>
+        <v>1.132</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>2.01619</v>
+        <v>1.881522</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>La-cooh</t>
+          <t>Sm-tpy</t>
         </is>
       </c>
       <c r="M68" t="n">
-        <v>1.856169095000001</v>
+        <v>1.807713725000002</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sm</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>tpy</t>
+          <t>cooh</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>3.04</v>
+        <v>3.44</v>
       </c>
       <c r="D69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.65</v>
+        <v>4.651</v>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>1.17</v>
+        <v>1.83</v>
       </c>
       <c r="H69" t="n">
-        <v>1.132</v>
+        <v>0.645</v>
       </c>
       <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
         <v>5</v>
       </c>
-      <c r="J69" t="n">
-        <v>0</v>
-      </c>
       <c r="K69" t="n">
-        <v>1.881522</v>
+        <v>1.414224</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Sm-tpy</t>
+          <t>Fe-cooh</t>
         </is>
       </c>
       <c r="M69" t="n">
-        <v>1.846954179000003</v>
+        <v>1.389681772499997</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>cooh</t>
+          <t>bpy</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="D70" t="n">
         <v>2</v>
       </c>
       <c r="E70" t="n">
-        <v>4.651</v>
+        <v>2.985</v>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G70" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="H70" t="n">
-        <v>0.645</v>
+        <v>0.67</v>
       </c>
       <c r="I70" t="n">
         <v>0</v>
@@ -3727,115 +3727,115 @@
         <v>5</v>
       </c>
       <c r="K70" t="n">
-        <v>1.414224</v>
+        <v>1.284855</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Fe-cooh</t>
+          <t>Mn-bpy</t>
         </is>
       </c>
       <c r="M70" t="n">
-        <v>1.389300384999996</v>
+        <v>1.267908544999996</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Er</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>bpy</t>
+          <t>cooh</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>3.04</v>
+        <v>3.44</v>
       </c>
       <c r="D71" t="n">
         <v>2</v>
       </c>
       <c r="E71" t="n">
-        <v>2.985</v>
+        <v>2.825</v>
       </c>
       <c r="F71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>1.55</v>
+        <v>1.24</v>
       </c>
       <c r="H71" t="n">
-        <v>0.67</v>
+        <v>1.062</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J71" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>1.284855</v>
+        <v>2.004851</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Mn-bpy</t>
+          <t>Er-cooh</t>
         </is>
       </c>
       <c r="M71" t="n">
-        <v>1.295118798297618</v>
+        <v>1.968652959999996</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Er</t>
+          <t>Sm</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>cooh</t>
+          <t>bpy</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="D72" t="n">
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.825</v>
+        <v>2.78</v>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>1.24</v>
+        <v>1.079</v>
       </c>
       <c r="H72" t="n">
-        <v>1.062</v>
+        <v>1.079</v>
       </c>
       <c r="I72" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>2.004851</v>
+        <v>1.778306</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Er-cooh</t>
+          <t>Sm-bpy</t>
         </is>
       </c>
       <c r="M72" t="n">
-        <v>1.990233909999992</v>
+        <v>1.595577532999999</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sm</t>
+          <t>Dy</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3850,274 +3850,274 @@
         <v>2</v>
       </c>
       <c r="E73" t="n">
-        <v>2.78</v>
+        <v>2.921</v>
       </c>
       <c r="F73" t="n">
         <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>1.079</v>
+        <v>1.027</v>
       </c>
       <c r="H73" t="n">
-        <v>1.079</v>
+        <v>1.027</v>
       </c>
       <c r="I73" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>1.778306</v>
+        <v>1.772832</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Sm-bpy</t>
+          <t>Dy-bpy</t>
         </is>
       </c>
       <c r="M73" t="n">
-        <v>1.598126964416666</v>
+        <v>1.607533569666666</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Dy</t>
+          <t>Ir</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>bpy</t>
+          <t>cooh</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>3.04</v>
+        <v>3.44</v>
       </c>
       <c r="D74" t="n">
         <v>2</v>
       </c>
       <c r="E74" t="n">
-        <v>2.921</v>
+        <v>4.412</v>
       </c>
       <c r="F74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>1.027</v>
+        <v>0.68</v>
       </c>
       <c r="H74" t="n">
-        <v>1.027</v>
+        <v>0.68</v>
       </c>
       <c r="I74" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K74" t="n">
-        <v>1.772832</v>
+        <v>1.376217</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Dy-bpy</t>
+          <t>Ir-cooh</t>
         </is>
       </c>
       <c r="M74" t="n">
-        <v>1.629279361361112</v>
+        <v>1.368473057499998</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Ir</t>
+          <t>Zn</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>cooh</t>
+          <t>tpy</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="D75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E75" t="n">
-        <v>4.412</v>
+        <v>2.703</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>0.68</v>
+        <v>1.65</v>
       </c>
       <c r="H75" t="n">
-        <v>0.68</v>
+        <v>0.74</v>
       </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K75" t="n">
-        <v>1.376217</v>
+        <v>1.189663</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Ir-cooh</t>
+          <t>Zn-tpy</t>
         </is>
       </c>
       <c r="M75" t="n">
-        <v>1.250144101666665</v>
+        <v>1.331069789166667</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Zn</t>
+          <t>Ru</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>tpy</t>
+          <t>cooh</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>3.04</v>
+        <v>3.44</v>
       </c>
       <c r="D76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E76" t="n">
-        <v>2.703</v>
+        <v>4.412</v>
       </c>
       <c r="F76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="H76" t="n">
-        <v>0.74</v>
+        <v>0.68</v>
       </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K76" t="n">
-        <v>1.189663</v>
+        <v>1.390089</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Zn-tpy</t>
+          <t>Ru-cooh</t>
         </is>
       </c>
       <c r="M76" t="n">
-        <v>1.230448270142856</v>
+        <v>1.345982934999998</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Ru</t>
+          <t>Lu</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>cooh</t>
+          <t>bpy</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="D77" t="n">
         <v>2</v>
       </c>
       <c r="E77" t="n">
-        <v>4.412</v>
+        <v>3.071</v>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>2.2</v>
+        <v>0.977</v>
       </c>
       <c r="H77" t="n">
-        <v>0.68</v>
+        <v>0.977</v>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J77" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>1.390089</v>
+        <v>1.79015</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Ru-cooh</t>
+          <t>Lu-bpy</t>
         </is>
       </c>
       <c r="M77" t="n">
-        <v>1.390908029999997</v>
+        <v>1.647205103250001</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>bpy</t>
+          <t>cooh</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>3.04</v>
+        <v>3.44</v>
       </c>
       <c r="D78" t="n">
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.071</v>
+        <v>4.688</v>
       </c>
       <c r="F78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>0.977</v>
+        <v>1.63</v>
       </c>
       <c r="H78" t="n">
-        <v>0.977</v>
+        <v>0.64</v>
       </c>
       <c r="I78" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K78" t="n">
-        <v>1.79015</v>
+        <v>1.383423</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Lu-bpy</t>
+          <t>V-cooh</t>
         </is>
       </c>
       <c r="M78" t="n">
-        <v>1.635016916833334</v>
+        <v>1.359156167499998</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>Cr</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4132,80 +4132,80 @@
         <v>2</v>
       </c>
       <c r="E79" t="n">
-        <v>4.688</v>
+        <v>4.878</v>
       </c>
       <c r="F79" t="n">
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="H79" t="n">
-        <v>0.64</v>
+        <v>0.615</v>
       </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K79" t="n">
-        <v>1.383423</v>
+        <v>1.377868</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>V-cooh</t>
+          <t>Cr-cooh</t>
         </is>
       </c>
       <c r="M79" t="n">
-        <v>1.351876809999997</v>
+        <v>1.373751020000001</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Cr</t>
+          <t>Ho</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>cooh</t>
+          <t>bpy</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="D80" t="n">
         <v>2</v>
       </c>
       <c r="E80" t="n">
-        <v>4.878</v>
+        <v>2.956</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G80" t="n">
-        <v>1.66</v>
+        <v>1.015</v>
       </c>
       <c r="H80" t="n">
-        <v>0.615</v>
+        <v>1.015</v>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J80" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>1.377868</v>
+        <v>1.779418</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Cr-cooh</t>
+          <t>Ho-bpy</t>
         </is>
       </c>
       <c r="M80" t="n">
-        <v>1.243943651666666</v>
+        <v>1.485425779166665</v>
       </c>
     </row>
     <row r="81">
@@ -4216,26 +4216,26 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>bpy</t>
+          <t>cooh</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>3.04</v>
+        <v>3.44</v>
       </c>
       <c r="D81" t="n">
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.956</v>
+        <v>2.799</v>
       </c>
       <c r="F81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>1.015</v>
+        <v>1.23</v>
       </c>
       <c r="H81" t="n">
-        <v>1.015</v>
+        <v>1.072</v>
       </c>
       <c r="I81" t="n">
         <v>10</v>
@@ -4244,21 +4244,21 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>1.779418</v>
+        <v>1.975642</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Ho-bpy</t>
+          <t>Ho-cooh</t>
         </is>
       </c>
       <c r="M81" t="n">
-        <v>1.600347259896824</v>
+        <v>1.940608637999996</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Ho</t>
+          <t>Gd</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4273,39 +4273,39 @@
         <v>2</v>
       </c>
       <c r="E82" t="n">
-        <v>2.799</v>
+        <v>2.71</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="H82" t="n">
-        <v>1.072</v>
+        <v>1.107</v>
       </c>
       <c r="I82" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>1.975642</v>
+        <v>1.97544</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Ho-cooh</t>
+          <t>Gd-cooh</t>
         </is>
       </c>
       <c r="M82" t="n">
-        <v>1.956245244999995</v>
+        <v>1.974890776999997</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Gd</t>
+          <t>Eu</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4320,7 +4320,7 @@
         <v>2</v>
       </c>
       <c r="E83" t="n">
-        <v>2.71</v>
+        <v>2.679</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -4329,359 +4329,359 @@
         <v>1.2</v>
       </c>
       <c r="H83" t="n">
-        <v>1.107</v>
+        <v>1.12</v>
       </c>
       <c r="I83" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>1.97544</v>
+        <v>1.741647</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Gd-cooh</t>
+          <t>Eu-cooh</t>
         </is>
       </c>
       <c r="M83" t="n">
-        <v>1.994572470999996</v>
+        <v>1.836479515</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Eu</t>
+          <t>Ca</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>cooh</t>
+          <t>tpy</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="D84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E84" t="n">
-        <v>2.679</v>
+        <v>1.695</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G84" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="H84" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="I84" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>1.741647</v>
+        <v>1.871805</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Eu-cooh</t>
+          <t>Ca-tpy</t>
         </is>
       </c>
       <c r="M84" t="n">
-        <v>2.004016215999999</v>
+        <v>1.683333093333333</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Ca</t>
+          <t>Nd</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>tpy</t>
+          <t>bpy</t>
         </is>
       </c>
       <c r="C85" t="n">
         <v>3.04</v>
       </c>
       <c r="D85" t="n">
+        <v>2</v>
+      </c>
+      <c r="E85" t="n">
+        <v>2.705</v>
+      </c>
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" t="n">
+        <v>1.109</v>
+      </c>
+      <c r="H85" t="n">
+        <v>1.109</v>
+      </c>
+      <c r="I85" t="n">
         <v>3</v>
       </c>
-      <c r="E85" t="n">
-        <v>1.695</v>
-      </c>
-      <c r="F85" t="n">
-        <v>1</v>
-      </c>
-      <c r="G85" t="n">
-        <v>1</v>
-      </c>
-      <c r="H85" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="I85" t="n">
-        <v>0</v>
-      </c>
       <c r="J85" t="n">
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>1.871805</v>
+        <v>1.770991</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Ca-tpy</t>
+          <t>Nd-bpy</t>
         </is>
       </c>
       <c r="M85" t="n">
-        <v>1.8256843655</v>
+        <v>1.620709019083334</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Nd</t>
+          <t>Tm</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>bpy</t>
+          <t>cooh</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>3.04</v>
+        <v>3.44</v>
       </c>
       <c r="D86" t="n">
         <v>2</v>
       </c>
       <c r="E86" t="n">
-        <v>2.705</v>
+        <v>2.852</v>
       </c>
       <c r="F86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>1.109</v>
+        <v>1.25</v>
       </c>
       <c r="H86" t="n">
-        <v>1.109</v>
+        <v>1.052</v>
       </c>
       <c r="I86" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>1.770991</v>
+        <v>1.971139</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Nd-bpy</t>
+          <t>Tm-cooh</t>
         </is>
       </c>
       <c r="M86" t="n">
-        <v>1.631257657488096</v>
+        <v>1.983202659999996</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Tm</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>cooh</t>
+          <t>bpy</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="D87" t="n">
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.852</v>
+        <v>4.348</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>1.25</v>
+        <v>2.16</v>
       </c>
       <c r="H87" t="n">
-        <v>1.052</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I87" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K87" t="n">
-        <v>1.971139</v>
+        <v>1.372387</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Tm-cooh</t>
+          <t>Mo-bpy</t>
         </is>
       </c>
       <c r="M87" t="n">
-        <v>1.985195639999994</v>
+        <v>1.197547407500003</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>Pr</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>bpy</t>
+          <t>cooh</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>3.04</v>
+        <v>3.44</v>
       </c>
       <c r="D88" t="n">
         <v>2</v>
       </c>
       <c r="E88" t="n">
-        <v>4.348</v>
+        <v>2.545</v>
       </c>
       <c r="F88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>2.16</v>
+        <v>1.13</v>
       </c>
       <c r="H88" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.179</v>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J88" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>1.372387</v>
+        <v>1.960982</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Mo-bpy</t>
+          <t>Pr-cooh</t>
         </is>
       </c>
       <c r="M88" t="n">
-        <v>1.184956584750003</v>
+        <v>1.983449260000001</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Pr</t>
+          <t>In</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>cooh</t>
+          <t>tpy</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="D89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E89" t="n">
-        <v>2.545</v>
+        <v>3.75</v>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>1.13</v>
+        <v>1.78</v>
       </c>
       <c r="H89" t="n">
-        <v>1.179</v>
+        <v>0.8</v>
       </c>
       <c r="I89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K89" t="n">
-        <v>1.960982</v>
+        <v>1.254365</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Pr-cooh</t>
+          <t>In-tpy</t>
         </is>
       </c>
       <c r="M89" t="n">
-        <v>1.984475540000002</v>
+        <v>1.252168466666669</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>In</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>tpy</t>
+          <t>cooh</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>3.04</v>
+        <v>3.44</v>
       </c>
       <c r="D90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E90" t="n">
-        <v>3.75</v>
+        <v>3.509</v>
       </c>
       <c r="F90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="H90" t="n">
-        <v>0.8</v>
+        <v>0.57</v>
       </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K90" t="n">
-        <v>1.254365</v>
+        <v>0.954261</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>In-tpy</t>
+          <t>Cu-cooh</t>
         </is>
       </c>
       <c r="M90" t="n">
-        <v>1.209998230833336</v>
+        <v>1.071619273666668</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4696,227 +4696,227 @@
         <v>2</v>
       </c>
       <c r="E91" t="n">
-        <v>3.509</v>
+        <v>4.348</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>1.9</v>
+        <v>2.16</v>
       </c>
       <c r="H91" t="n">
-        <v>0.57</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K91" t="n">
-        <v>0.954261</v>
+        <v>1.348408</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Cu-cooh</t>
+          <t>Mo-cooh</t>
         </is>
       </c>
       <c r="M91" t="n">
-        <v>1.047909992666668</v>
+        <v>1.333173738750002</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>Ti</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>cooh</t>
+          <t>bpy</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="D92" t="n">
         <v>2</v>
       </c>
       <c r="E92" t="n">
-        <v>4.348</v>
+        <v>4.478</v>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G92" t="n">
-        <v>2.16</v>
+        <v>1.54</v>
       </c>
       <c r="H92" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K92" t="n">
-        <v>1.348408</v>
+        <v>1.34941</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Mo-cooh</t>
+          <t>Ti-bpy</t>
         </is>
       </c>
       <c r="M92" t="n">
-        <v>1.356347395000002</v>
+        <v>1.290852337166669</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Ti</t>
+          <t>Dy</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>bpy</t>
+          <t>tpy</t>
         </is>
       </c>
       <c r="C93" t="n">
         <v>3.04</v>
       </c>
       <c r="D93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E93" t="n">
-        <v>4.478</v>
+        <v>2.77</v>
       </c>
       <c r="F93" t="n">
         <v>1</v>
       </c>
       <c r="G93" t="n">
-        <v>1.54</v>
+        <v>1.22</v>
       </c>
       <c r="H93" t="n">
-        <v>0.67</v>
+        <v>1.083</v>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>1.34941</v>
+        <v>1.846306</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Ti-bpy</t>
+          <t>Dy-tpy</t>
         </is>
       </c>
       <c r="M93" t="n">
-        <v>1.243724666333336</v>
+        <v>1.843724195000005</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Dy</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>tpy</t>
+          <t>cooh</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>3.04</v>
+        <v>3.44</v>
       </c>
       <c r="D94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E94" t="n">
-        <v>2.77</v>
+        <v>2.41</v>
       </c>
       <c r="F94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>1.22</v>
+        <v>1.55</v>
       </c>
       <c r="H94" t="n">
-        <v>1.083</v>
+        <v>0.83</v>
       </c>
       <c r="I94" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K94" t="n">
-        <v>1.846306</v>
+        <v>1.337713</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>Dy-tpy</t>
+          <t>Mn-cooh</t>
         </is>
       </c>
       <c r="M94" t="n">
-        <v>1.844667060000006</v>
+        <v>1.366815520000001</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>cooh</t>
+          <t>tpy</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="D95" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E95" t="n">
-        <v>2.41</v>
+        <v>3.279</v>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="H95" t="n">
-        <v>0.83</v>
+        <v>0.61</v>
       </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K95" t="n">
-        <v>1.337713</v>
+        <v>1.331687</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>Mn-cooh</t>
+          <t>Fe-tpy</t>
         </is>
       </c>
       <c r="M95" t="n">
-        <v>1.346781465000001</v>
+        <v>1.330702706666663</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Pd</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4931,39 +4931,39 @@
         <v>3</v>
       </c>
       <c r="E96" t="n">
-        <v>3.279</v>
+        <v>3.125</v>
       </c>
       <c r="F96" t="n">
         <v>1</v>
       </c>
       <c r="G96" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="H96" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="I96" t="n">
         <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K96" t="n">
-        <v>1.331687</v>
+        <v>0.920677</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Fe-tpy</t>
+          <t>Pd-tpy</t>
         </is>
       </c>
       <c r="M96" t="n">
-        <v>1.343213250833334</v>
+        <v>1.079200007166666</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Pd</t>
+          <t>Ru</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4978,7 +4978,7 @@
         <v>3</v>
       </c>
       <c r="E97" t="n">
-        <v>3.125</v>
+        <v>2.941</v>
       </c>
       <c r="F97" t="n">
         <v>1</v>
@@ -4987,30 +4987,30 @@
         <v>2.2</v>
       </c>
       <c r="H97" t="n">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K97" t="n">
-        <v>0.920677</v>
+        <v>1.310791</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>Pd-tpy</t>
+          <t>Ru-tpy</t>
         </is>
       </c>
       <c r="M97" t="n">
-        <v>1.007584361250002</v>
+        <v>1.306544233166664</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Ru</t>
+          <t>Ce</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -5025,133 +5025,133 @@
         <v>3</v>
       </c>
       <c r="E98" t="n">
-        <v>2.941</v>
+        <v>2.508</v>
       </c>
       <c r="F98" t="n">
         <v>1</v>
       </c>
       <c r="G98" t="n">
-        <v>2.2</v>
+        <v>1.12</v>
       </c>
       <c r="H98" t="n">
-        <v>0.68</v>
+        <v>1.196</v>
       </c>
       <c r="I98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J98" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>1.310791</v>
+        <v>1.854005</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>Ru-tpy</t>
+          <t>Ce-tpy</t>
         </is>
       </c>
       <c r="M98" t="n">
-        <v>1.263667820499998</v>
+        <v>1.821152890749996</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Ce</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>tpy</t>
+          <t>bpy</t>
         </is>
       </c>
       <c r="C99" t="n">
         <v>3.04</v>
       </c>
       <c r="D99" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E99" t="n">
-        <v>2.508</v>
+        <v>3.509</v>
       </c>
       <c r="F99" t="n">
         <v>1</v>
       </c>
       <c r="G99" t="n">
-        <v>1.12</v>
+        <v>0.57</v>
       </c>
       <c r="H99" t="n">
-        <v>1.196</v>
+        <v>0.57</v>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K99" t="n">
-        <v>1.854005</v>
+        <v>0.889082</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>Ce-tpy</t>
+          <t>Cu-bpy</t>
         </is>
       </c>
       <c r="M99" t="n">
-        <v>1.800545228416669</v>
+        <v>0.8155785140833319</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Cd</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>bpy</t>
+          <t>cooh</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>3.04</v>
+        <v>3.44</v>
       </c>
       <c r="D100" t="n">
         <v>2</v>
       </c>
       <c r="E100" t="n">
-        <v>3.509</v>
+        <v>2.105</v>
       </c>
       <c r="F100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>0.57</v>
+        <v>0.95</v>
       </c>
       <c r="H100" t="n">
-        <v>0.57</v>
+        <v>0.95</v>
       </c>
       <c r="I100" t="n">
         <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K100" t="n">
-        <v>0.889082</v>
+        <v>1.243605</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>Cu-bpy</t>
+          <t>Cd-cooh</t>
         </is>
       </c>
       <c r="M100" t="n">
-        <v>0.8326255677738094</v>
+        <v>1.282985988333335</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Cd</t>
+          <t>Pd</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -5166,63 +5166,63 @@
         <v>2</v>
       </c>
       <c r="E101" t="n">
-        <v>2.105</v>
+        <v>3.125</v>
       </c>
       <c r="F101" t="n">
         <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>0.95</v>
+        <v>2.2</v>
       </c>
       <c r="H101" t="n">
-        <v>0.95</v>
+        <v>0.64</v>
       </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K101" t="n">
-        <v>1.243605</v>
+        <v>0.877937</v>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>Cd-cooh</t>
+          <t>Pd-cooh</t>
         </is>
       </c>
       <c r="M101" t="n">
-        <v>1.259128460000001</v>
+        <v>1.041335445000002</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Pd</t>
+          <t>Ni</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>cooh</t>
+          <t>tpy</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="D102" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E102" t="n">
-        <v>3.125</v>
+        <v>2.899</v>
       </c>
       <c r="F102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="H102" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I102" t="n">
         <v>0</v>
@@ -5231,21 +5231,21 @@
         <v>8</v>
       </c>
       <c r="K102" t="n">
-        <v>0.877937</v>
+        <v>1.275855</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>Pd-cooh</t>
+          <t>Ni-tpy</t>
         </is>
       </c>
       <c r="M102" t="n">
-        <v>1.358545955</v>
+        <v>1.387203244666664</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Ni</t>
+          <t>Cr</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -5260,39 +5260,39 @@
         <v>3</v>
       </c>
       <c r="E103" t="n">
-        <v>2.899</v>
+        <v>4.878</v>
       </c>
       <c r="F103" t="n">
         <v>1</v>
       </c>
       <c r="G103" t="n">
-        <v>1.91</v>
+        <v>1.66</v>
       </c>
       <c r="H103" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.615</v>
       </c>
       <c r="I103" t="n">
         <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K103" t="n">
-        <v>1.275855</v>
+        <v>1.25553</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>Ni-tpy</t>
+          <t>Cr-tpy</t>
         </is>
       </c>
       <c r="M103" t="n">
-        <v>1.242102811250002</v>
+        <v>1.210333019999997</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Cr</t>
+          <t>Er</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -5307,39 +5307,39 @@
         <v>3</v>
       </c>
       <c r="E104" t="n">
-        <v>4.878</v>
+        <v>2.825</v>
       </c>
       <c r="F104" t="n">
         <v>1</v>
       </c>
       <c r="G104" t="n">
-        <v>1.66</v>
+        <v>1.24</v>
       </c>
       <c r="H104" t="n">
-        <v>0.615</v>
+        <v>1.062</v>
       </c>
       <c r="I104" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J104" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>1.25553</v>
+        <v>1.853008</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>Cr-tpy</t>
+          <t>Er-tpy</t>
         </is>
       </c>
       <c r="M104" t="n">
-        <v>1.266746432142854</v>
+        <v>1.847457799999997</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Er</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -5354,321 +5354,321 @@
         <v>3</v>
       </c>
       <c r="E105" t="n">
-        <v>2.825</v>
+        <v>2.532</v>
       </c>
       <c r="F105" t="n">
         <v>1</v>
       </c>
       <c r="G105" t="n">
-        <v>1.24</v>
+        <v>1.63</v>
       </c>
       <c r="H105" t="n">
-        <v>1.062</v>
+        <v>0.64</v>
       </c>
       <c r="I105" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K105" t="n">
-        <v>1.853008</v>
+        <v>1.2604</v>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>Er-tpy</t>
+          <t>V-tpy</t>
         </is>
       </c>
       <c r="M105" t="n">
-        <v>1.841456169999998</v>
+        <v>1.277851859642858</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>Ru</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>tpy</t>
+          <t>phen</t>
         </is>
       </c>
       <c r="C106" t="n">
         <v>3.04</v>
       </c>
       <c r="D106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E106" t="n">
-        <v>2.532</v>
+        <v>2.941</v>
       </c>
       <c r="F106" t="n">
         <v>1</v>
       </c>
       <c r="G106" t="n">
-        <v>1.63</v>
+        <v>0.68</v>
       </c>
       <c r="H106" t="n">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="I106" t="n">
         <v>0</v>
       </c>
       <c r="J106" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K106" t="n">
-        <v>1.2604</v>
+        <v>1.208362</v>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>V-tpy</t>
+          <t>Ru-phen</t>
         </is>
       </c>
       <c r="M106" t="n">
-        <v>1.267812216666668</v>
+        <v>1.365390601267857</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Ru</t>
+          <t>Ho</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>phen</t>
+          <t>tpy</t>
         </is>
       </c>
       <c r="C107" t="n">
         <v>3.04</v>
       </c>
       <c r="D107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E107" t="n">
-        <v>2.941</v>
+        <v>2.799</v>
       </c>
       <c r="F107" t="n">
         <v>1</v>
       </c>
       <c r="G107" t="n">
-        <v>0.68</v>
+        <v>1.23</v>
       </c>
       <c r="H107" t="n">
-        <v>0.68</v>
+        <v>1.072</v>
       </c>
       <c r="I107" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J107" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K107" t="n">
-        <v>1.208362</v>
+        <v>1.843025</v>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>Ru-phen</t>
+          <t>Ho-tpy</t>
         </is>
       </c>
       <c r="M107" t="n">
-        <v>1.34519161990476</v>
+        <v>1.844592315000004</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Ho</t>
+          <t>Dy</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>tpy</t>
+          <t>cooh</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>3.04</v>
+        <v>3.44</v>
       </c>
       <c r="D108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E108" t="n">
-        <v>2.799</v>
+        <v>2.77</v>
       </c>
       <c r="F108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G108" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="H108" t="n">
-        <v>1.072</v>
+        <v>1.083</v>
       </c>
       <c r="I108" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>1.843025</v>
+        <v>1.807171</v>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>Ho-tpy</t>
+          <t>Dy-cooh</t>
         </is>
       </c>
       <c r="M108" t="n">
-        <v>1.842453145000005</v>
+        <v>1.875882712999997</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Dy</t>
+          <t>Nd</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>cooh</t>
+          <t>tpy</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="D109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E109" t="n">
-        <v>2.77</v>
+        <v>2.58</v>
       </c>
       <c r="F109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G109" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="H109" t="n">
-        <v>1.083</v>
+        <v>1.163</v>
       </c>
       <c r="I109" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>1.807171</v>
+        <v>1.838206</v>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>Dy-cooh</t>
+          <t>Nd-tpy</t>
         </is>
       </c>
       <c r="M109" t="n">
-        <v>1.877855126999997</v>
+        <v>1.821608852750006</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Nd</t>
+          <t>Pd</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>tpy</t>
+          <t>phen</t>
         </is>
       </c>
       <c r="C110" t="n">
         <v>3.04</v>
       </c>
       <c r="D110" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E110" t="n">
-        <v>2.58</v>
+        <v>3.125</v>
       </c>
       <c r="F110" t="n">
         <v>1</v>
       </c>
       <c r="G110" t="n">
-        <v>1.14</v>
+        <v>0.64</v>
       </c>
       <c r="H110" t="n">
-        <v>1.163</v>
+        <v>0.64</v>
       </c>
       <c r="I110" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J110" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K110" t="n">
-        <v>1.838206</v>
+        <v>0.8249339999999999</v>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>Nd-tpy</t>
+          <t>Pd-phen</t>
         </is>
       </c>
       <c r="M110" t="n">
-        <v>1.814155202166673</v>
+        <v>0.9666736129761923</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Pd</t>
+          <t>Lu</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>phen</t>
+          <t>tpy</t>
         </is>
       </c>
       <c r="C111" t="n">
         <v>3.04</v>
       </c>
       <c r="D111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E111" t="n">
-        <v>3.125</v>
+        <v>2.907</v>
       </c>
       <c r="F111" t="n">
         <v>1</v>
       </c>
       <c r="G111" t="n">
-        <v>0.64</v>
+        <v>1.27</v>
       </c>
       <c r="H111" t="n">
-        <v>0.64</v>
+        <v>1.032</v>
       </c>
       <c r="I111" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J111" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>0.8249339999999999</v>
+        <v>1.844728</v>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>Pd-phen</t>
+          <t>Lu-tpy</t>
         </is>
       </c>
       <c r="M111" t="n">
-        <v>0.9554049913333366</v>
+        <v>1.836791784999996</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>Tm</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5683,39 +5683,39 @@
         <v>3</v>
       </c>
       <c r="E112" t="n">
-        <v>2.907</v>
+        <v>2.852</v>
       </c>
       <c r="F112" t="n">
         <v>1</v>
       </c>
       <c r="G112" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="H112" t="n">
-        <v>1.032</v>
+        <v>1.052</v>
       </c>
       <c r="I112" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>1.844728</v>
+        <v>1.833118</v>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>Lu-tpy</t>
+          <t>Tm-tpy</t>
         </is>
       </c>
       <c r="M112" t="n">
-        <v>1.806607386250004</v>
+        <v>1.845243394999996</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Tm</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5730,86 +5730,86 @@
         <v>3</v>
       </c>
       <c r="E113" t="n">
-        <v>2.852</v>
+        <v>3.077</v>
       </c>
       <c r="F113" t="n">
         <v>1</v>
       </c>
       <c r="G113" t="n">
-        <v>1.25</v>
+        <v>1.88</v>
       </c>
       <c r="H113" t="n">
-        <v>1.052</v>
+        <v>0.65</v>
       </c>
       <c r="I113" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K113" t="n">
-        <v>1.833118</v>
+        <v>1.222785</v>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>Tm-tpy</t>
+          <t>Co-tpy</t>
         </is>
       </c>
       <c r="M113" t="n">
-        <v>1.826600075000005</v>
+        <v>1.260027630999995</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>tpy</t>
+          <t>phen</t>
         </is>
       </c>
       <c r="C114" t="n">
         <v>3.04</v>
       </c>
       <c r="D114" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E114" t="n">
-        <v>3.077</v>
+        <v>3.279</v>
       </c>
       <c r="F114" t="n">
         <v>1</v>
       </c>
       <c r="G114" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="H114" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="I114" t="n">
         <v>0</v>
       </c>
       <c r="J114" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K114" t="n">
-        <v>1.222785</v>
+        <v>1.221956</v>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>Co-tpy</t>
+          <t>Fe-phen</t>
         </is>
       </c>
       <c r="M114" t="n">
-        <v>1.183588054999997</v>
+        <v>1.387350583666668</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Ni</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5824,86 +5824,86 @@
         <v>2</v>
       </c>
       <c r="E115" t="n">
-        <v>3.279</v>
+        <v>2.899</v>
       </c>
       <c r="F115" t="n">
         <v>1</v>
       </c>
       <c r="G115" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="H115" t="n">
-        <v>0.61</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I115" t="n">
         <v>0</v>
       </c>
       <c r="J115" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K115" t="n">
-        <v>1.221956</v>
+        <v>1.216355</v>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>Fe-phen</t>
+          <t>Ni-phen</t>
         </is>
       </c>
       <c r="M115" t="n">
-        <v>1.396729021333336</v>
+        <v>1.469693507166663</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Ni</t>
+          <t>Pr</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>phen</t>
+          <t>tpy</t>
         </is>
       </c>
       <c r="C116" t="n">
         <v>3.04</v>
       </c>
       <c r="D116" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E116" t="n">
-        <v>2.899</v>
+        <v>2.545</v>
       </c>
       <c r="F116" t="n">
         <v>1</v>
       </c>
       <c r="G116" t="n">
-        <v>1.91</v>
+        <v>1.13</v>
       </c>
       <c r="H116" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.179</v>
       </c>
       <c r="I116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J116" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K116" t="n">
-        <v>1.216355</v>
+        <v>1.8034</v>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>Ni-phen</t>
+          <t>Pr-tpy</t>
         </is>
       </c>
       <c r="M116" t="n">
-        <v>1.232314421571426</v>
+        <v>1.807574148750004</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Pr</t>
+          <t>Gd</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5918,133 +5918,133 @@
         <v>3</v>
       </c>
       <c r="E117" t="n">
-        <v>2.545</v>
+        <v>2.71</v>
       </c>
       <c r="F117" t="n">
         <v>1</v>
       </c>
       <c r="G117" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="H117" t="n">
-        <v>1.179</v>
+        <v>1.107</v>
       </c>
       <c r="I117" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
       </c>
       <c r="K117" t="n">
-        <v>1.8034</v>
+        <v>1.810199</v>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>Pr-tpy</t>
+          <t>Gd-tpy</t>
         </is>
       </c>
       <c r="M117" t="n">
-        <v>1.804143268416672</v>
+        <v>1.815300745000003</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Gd</t>
+          <t>Ca</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>tpy</t>
+          <t>phen</t>
         </is>
       </c>
       <c r="C118" t="n">
         <v>3.04</v>
       </c>
       <c r="D118" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E118" t="n">
-        <v>2.71</v>
+        <v>1.786</v>
       </c>
       <c r="F118" t="n">
         <v>1</v>
       </c>
       <c r="G118" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="H118" t="n">
-        <v>1.107</v>
+        <v>1.12</v>
       </c>
       <c r="I118" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
       </c>
       <c r="K118" t="n">
-        <v>1.810199</v>
+        <v>1.503763</v>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>Gd-tpy</t>
+          <t>Ca-phen</t>
         </is>
       </c>
       <c r="M118" t="n">
-        <v>1.815719915000004</v>
+        <v>1.529093592333331</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Ca</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>phen</t>
+          <t>tpy</t>
         </is>
       </c>
       <c r="C119" t="n">
         <v>3.04</v>
       </c>
       <c r="D119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E119" t="n">
-        <v>1.786</v>
+        <v>4.348</v>
       </c>
       <c r="F119" t="n">
         <v>1</v>
       </c>
       <c r="G119" t="n">
-        <v>1</v>
+        <v>2.16</v>
       </c>
       <c r="H119" t="n">
-        <v>1.12</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I119" t="n">
         <v>0</v>
       </c>
       <c r="J119" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K119" t="n">
-        <v>1.503763</v>
+        <v>1.190333</v>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>Ca-phen</t>
+          <t>Mo-tpy</t>
         </is>
       </c>
       <c r="M119" t="n">
-        <v>1.776833026428576</v>
+        <v>1.184655156333335</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>La</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -6059,39 +6059,39 @@
         <v>3</v>
       </c>
       <c r="E120" t="n">
-        <v>4.348</v>
+        <v>2.467</v>
       </c>
       <c r="F120" t="n">
         <v>1</v>
       </c>
       <c r="G120" t="n">
-        <v>2.16</v>
+        <v>1.1</v>
       </c>
       <c r="H120" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.216</v>
       </c>
       <c r="I120" t="n">
         <v>0</v>
       </c>
       <c r="J120" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K120" t="n">
-        <v>1.190333</v>
+        <v>1.789009</v>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>Mo-tpy</t>
+          <t>La-tpy</t>
         </is>
       </c>
       <c r="M120" t="n">
-        <v>1.183468462083336</v>
+        <v>1.762042808750001</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>La</t>
+          <t>Ti</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -6106,16 +6106,16 @@
         <v>3</v>
       </c>
       <c r="E121" t="n">
-        <v>2.467</v>
+        <v>6.612</v>
       </c>
       <c r="F121" t="n">
         <v>1</v>
       </c>
       <c r="G121" t="n">
-        <v>1.1</v>
+        <v>1.54</v>
       </c>
       <c r="H121" t="n">
-        <v>1.216</v>
+        <v>0.605</v>
       </c>
       <c r="I121" t="n">
         <v>0</v>
@@ -6124,68 +6124,68 @@
         <v>0</v>
       </c>
       <c r="K121" t="n">
-        <v>1.789009</v>
+        <v>1.172127</v>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>La-tpy</t>
+          <t>Ti-tpy</t>
         </is>
       </c>
       <c r="M121" t="n">
-        <v>1.786860770250001</v>
+        <v>1.159495247249999</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Ti</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>tpy</t>
+          <t>phen</t>
         </is>
       </c>
       <c r="C122" t="n">
         <v>3.04</v>
       </c>
       <c r="D122" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E122" t="n">
-        <v>6.612</v>
+        <v>3.509</v>
       </c>
       <c r="F122" t="n">
         <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>1.54</v>
+        <v>0.57</v>
       </c>
       <c r="H122" t="n">
-        <v>0.605</v>
+        <v>0.57</v>
       </c>
       <c r="I122" t="n">
         <v>0</v>
       </c>
       <c r="J122" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K122" t="n">
-        <v>1.172127</v>
+        <v>0.754474</v>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>Ti-tpy</t>
+          <t>Cu-phen</t>
         </is>
       </c>
       <c r="M122" t="n">
-        <v>1.071022150833332</v>
+        <v>0.8155785140833319</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -6200,39 +6200,39 @@
         <v>2</v>
       </c>
       <c r="E123" t="n">
-        <v>3.509</v>
+        <v>3.077</v>
       </c>
       <c r="F123" t="n">
         <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>0.57</v>
+        <v>1.88</v>
       </c>
       <c r="H123" t="n">
-        <v>0.57</v>
+        <v>0.745</v>
       </c>
       <c r="I123" t="n">
         <v>0</v>
       </c>
       <c r="J123" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K123" t="n">
-        <v>0.754474</v>
+        <v>1.166227</v>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>Cu-phen</t>
+          <t>Co-phen</t>
         </is>
       </c>
       <c r="M123" t="n">
-        <v>0.8326255677738094</v>
+        <v>1.241783552166663</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>La</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -6247,39 +6247,39 @@
         <v>2</v>
       </c>
       <c r="E124" t="n">
-        <v>3.077</v>
+        <v>2.586</v>
       </c>
       <c r="F124" t="n">
         <v>1</v>
       </c>
       <c r="G124" t="n">
-        <v>1.88</v>
+        <v>1.16</v>
       </c>
       <c r="H124" t="n">
-        <v>0.745</v>
+        <v>1.16</v>
       </c>
       <c r="I124" t="n">
         <v>0</v>
       </c>
       <c r="J124" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K124" t="n">
-        <v>1.166227</v>
+        <v>1.502635</v>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>Co-phen</t>
+          <t>La-phen</t>
         </is>
       </c>
       <c r="M124" t="n">
-        <v>1.185689053749998</v>
+        <v>1.667973842333334</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>La</t>
+          <t>Pt</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -6294,227 +6294,227 @@
         <v>2</v>
       </c>
       <c r="E125" t="n">
-        <v>2.586</v>
+        <v>3.333</v>
       </c>
       <c r="F125" t="n">
         <v>1</v>
       </c>
       <c r="G125" t="n">
-        <v>1.16</v>
+        <v>0.6</v>
       </c>
       <c r="H125" t="n">
-        <v>1.16</v>
+        <v>0.6</v>
       </c>
       <c r="I125" t="n">
         <v>0</v>
       </c>
       <c r="J125" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K125" t="n">
-        <v>1.502635</v>
+        <v>0.704694</v>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>La-phen</t>
+          <t>Pt-phen</t>
         </is>
       </c>
       <c r="M125" t="n">
-        <v>1.678677425559523</v>
+        <v>0.9190281243928565</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Pt</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>phen</t>
+          <t>tpy</t>
         </is>
       </c>
       <c r="C126" t="n">
         <v>3.04</v>
       </c>
       <c r="D126" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E126" t="n">
-        <v>3.333</v>
+        <v>2.985</v>
       </c>
       <c r="F126" t="n">
         <v>1</v>
       </c>
       <c r="G126" t="n">
-        <v>0.6</v>
+        <v>1.55</v>
       </c>
       <c r="H126" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="I126" t="n">
         <v>0</v>
       </c>
       <c r="J126" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K126" t="n">
-        <v>0.704694</v>
+        <v>1.136419</v>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>Pt-phen</t>
+          <t>Mn-tpy</t>
         </is>
       </c>
       <c r="M126" t="n">
-        <v>0.8950157507857144</v>
+        <v>1.190443289999996</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Ir</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>tpy</t>
+          <t>phen</t>
         </is>
       </c>
       <c r="C127" t="n">
         <v>3.04</v>
       </c>
       <c r="D127" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E127" t="n">
-        <v>2.985</v>
+        <v>4.412</v>
       </c>
       <c r="F127" t="n">
         <v>1</v>
       </c>
       <c r="G127" t="n">
-        <v>1.55</v>
+        <v>0.68</v>
       </c>
       <c r="H127" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="I127" t="n">
         <v>0</v>
       </c>
       <c r="J127" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K127" t="n">
-        <v>1.136419</v>
+        <v>1.122922</v>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>Mn-tpy</t>
+          <t>Ir-phen</t>
         </is>
       </c>
       <c r="M127" t="n">
-        <v>1.281615376392857</v>
+        <v>1.481144786124999</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Ir</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>phen</t>
+          <t>tpy</t>
         </is>
       </c>
       <c r="C128" t="n">
         <v>3.04</v>
       </c>
       <c r="D128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E128" t="n">
-        <v>4.412</v>
+        <v>3.077</v>
       </c>
       <c r="F128" t="n">
         <v>1</v>
       </c>
       <c r="G128" t="n">
-        <v>0.68</v>
+        <v>1.9</v>
       </c>
       <c r="H128" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="I128" t="n">
         <v>0</v>
       </c>
       <c r="J128" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K128" t="n">
-        <v>1.122922</v>
+        <v>0.920467</v>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>Ir-phen</t>
+          <t>Cu-tpy</t>
         </is>
       </c>
       <c r="M128" t="n">
-        <v>1.335918219999998</v>
+        <v>1.022330834166667</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Ce</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>tpy</t>
+          <t>phen</t>
         </is>
       </c>
       <c r="C129" t="n">
         <v>3.04</v>
       </c>
       <c r="D129" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E129" t="n">
-        <v>3.077</v>
+        <v>2.625</v>
       </c>
       <c r="F129" t="n">
         <v>1</v>
       </c>
       <c r="G129" t="n">
-        <v>1.9</v>
+        <v>1.143</v>
       </c>
       <c r="H129" t="n">
-        <v>0.65</v>
+        <v>1.143</v>
       </c>
       <c r="I129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J129" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K129" t="n">
-        <v>0.920467</v>
+        <v>1.477847</v>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>Cu-tpy</t>
+          <t>Ce-phen</t>
         </is>
       </c>
       <c r="M129" t="n">
-        <v>1.014834800000001</v>
+        <v>1.663242690666665</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Ce</t>
+          <t>Dy</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -6529,39 +6529,39 @@
         <v>2</v>
       </c>
       <c r="E130" t="n">
-        <v>2.625</v>
+        <v>2.921</v>
       </c>
       <c r="F130" t="n">
         <v>1</v>
       </c>
       <c r="G130" t="n">
-        <v>1.143</v>
+        <v>1.027</v>
       </c>
       <c r="H130" t="n">
-        <v>1.143</v>
+        <v>1.027</v>
       </c>
       <c r="I130" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
       </c>
       <c r="K130" t="n">
-        <v>1.477847</v>
+        <v>1.495429</v>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>Ce-phen</t>
+          <t>Dy-phen</t>
         </is>
       </c>
       <c r="M130" t="n">
-        <v>1.642977390345236</v>
+        <v>1.607533569666666</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Dy</t>
+          <t>Er</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -6576,39 +6576,39 @@
         <v>2</v>
       </c>
       <c r="E131" t="n">
-        <v>2.921</v>
+        <v>2.988</v>
       </c>
       <c r="F131" t="n">
         <v>1</v>
       </c>
       <c r="G131" t="n">
-        <v>1.027</v>
+        <v>1.004</v>
       </c>
       <c r="H131" t="n">
-        <v>1.027</v>
+        <v>1.004</v>
       </c>
       <c r="I131" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>1.495429</v>
+        <v>1.505762</v>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>Dy-phen</t>
+          <t>Er-phen</t>
         </is>
       </c>
       <c r="M131" t="n">
-        <v>1.629279361361112</v>
+        <v>1.501769991666667</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Er</t>
+          <t>Rh</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -6623,39 +6623,39 @@
         <v>2</v>
       </c>
       <c r="E132" t="n">
-        <v>2.988</v>
+        <v>4.511</v>
       </c>
       <c r="F132" t="n">
         <v>1</v>
       </c>
       <c r="G132" t="n">
-        <v>1.004</v>
+        <v>0.665</v>
       </c>
       <c r="H132" t="n">
-        <v>1.004</v>
+        <v>0.665</v>
       </c>
       <c r="I132" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J132" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K132" t="n">
-        <v>1.505762</v>
+        <v>1.015029</v>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>Er-phen</t>
+          <t>Rh-phen</t>
         </is>
       </c>
       <c r="M132" t="n">
-        <v>1.553205430666668</v>
+        <v>1.228062739684523</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Rh</t>
+          <t>Yb</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -6670,39 +6670,39 @@
         <v>2</v>
       </c>
       <c r="E133" t="n">
-        <v>4.511</v>
+        <v>3.046</v>
       </c>
       <c r="F133" t="n">
         <v>1</v>
       </c>
       <c r="G133" t="n">
-        <v>0.665</v>
+        <v>0.985</v>
       </c>
       <c r="H133" t="n">
-        <v>0.665</v>
+        <v>0.985</v>
       </c>
       <c r="I133" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J133" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K133" t="n">
-        <v>1.015029</v>
+        <v>1.479314</v>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>Rh-phen</t>
+          <t>Yb-phen</t>
         </is>
       </c>
       <c r="M133" t="n">
-        <v>1.219000210416667</v>
+        <v>1.701775563833334</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Yb</t>
+          <t>Gd</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -6717,39 +6717,39 @@
         <v>2</v>
       </c>
       <c r="E134" t="n">
-        <v>3.046</v>
+        <v>2.849</v>
       </c>
       <c r="F134" t="n">
         <v>1</v>
       </c>
       <c r="G134" t="n">
-        <v>0.985</v>
+        <v>1.053</v>
       </c>
       <c r="H134" t="n">
-        <v>0.985</v>
+        <v>1.053</v>
       </c>
       <c r="I134" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
       </c>
       <c r="K134" t="n">
-        <v>1.479314</v>
+        <v>1.499809</v>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>Yb-phen</t>
+          <t>Gd-phen</t>
         </is>
       </c>
       <c r="M134" t="n">
-        <v>1.716601411333334</v>
+        <v>1.51335351</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Gd</t>
+          <t>Nd</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -6764,39 +6764,39 @@
         <v>2</v>
       </c>
       <c r="E135" t="n">
-        <v>2.849</v>
+        <v>2.705</v>
       </c>
       <c r="F135" t="n">
         <v>1</v>
       </c>
       <c r="G135" t="n">
-        <v>1.053</v>
+        <v>1.109</v>
       </c>
       <c r="H135" t="n">
-        <v>1.053</v>
+        <v>1.109</v>
       </c>
       <c r="I135" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
       </c>
       <c r="K135" t="n">
-        <v>1.499809</v>
+        <v>1.4841</v>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>Gd-phen</t>
+          <t>Nd-phen</t>
         </is>
       </c>
       <c r="M135" t="n">
-        <v>1.534397212194445</v>
+        <v>1.620709019083334</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Nd</t>
+          <t>Lu</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -6811,39 +6811,39 @@
         <v>2</v>
       </c>
       <c r="E136" t="n">
-        <v>2.705</v>
+        <v>3.071</v>
       </c>
       <c r="F136" t="n">
         <v>1</v>
       </c>
       <c r="G136" t="n">
-        <v>1.109</v>
+        <v>0.977</v>
       </c>
       <c r="H136" t="n">
-        <v>1.109</v>
+        <v>0.977</v>
       </c>
       <c r="I136" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
       </c>
       <c r="K136" t="n">
-        <v>1.4841</v>
+        <v>1.483216</v>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>Nd-phen</t>
+          <t>Lu-phen</t>
         </is>
       </c>
       <c r="M136" t="n">
-        <v>1.631257657488096</v>
+        <v>1.647205103250001</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6858,39 +6858,39 @@
         <v>2</v>
       </c>
       <c r="E137" t="n">
-        <v>3.071</v>
+        <v>2.532</v>
       </c>
       <c r="F137" t="n">
         <v>1</v>
       </c>
       <c r="G137" t="n">
-        <v>0.977</v>
+        <v>1.63</v>
       </c>
       <c r="H137" t="n">
-        <v>0.977</v>
+        <v>0.79</v>
       </c>
       <c r="I137" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J137" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K137" t="n">
-        <v>1.483216</v>
+        <v>1.064441</v>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>Lu-phen</t>
+          <t>V-phen</t>
         </is>
       </c>
       <c r="M137" t="n">
-        <v>1.635016916833334</v>
+        <v>1.296561909499998</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>Ho</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6905,39 +6905,39 @@
         <v>2</v>
       </c>
       <c r="E138" t="n">
-        <v>2.532</v>
+        <v>2.956</v>
       </c>
       <c r="F138" t="n">
         <v>1</v>
       </c>
       <c r="G138" t="n">
-        <v>1.63</v>
+        <v>1.015</v>
       </c>
       <c r="H138" t="n">
-        <v>0.79</v>
+        <v>1.015</v>
       </c>
       <c r="I138" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J138" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K138" t="n">
-        <v>1.064441</v>
+        <v>1.44145</v>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>V-phen</t>
+          <t>Ho-phen</t>
         </is>
       </c>
       <c r="M138" t="n">
-        <v>1.270439217809524</v>
+        <v>1.485425779166665</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Ho</t>
+          <t>Cr</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -6952,39 +6952,39 @@
         <v>2</v>
       </c>
       <c r="E139" t="n">
-        <v>2.956</v>
+        <v>4.878</v>
       </c>
       <c r="F139" t="n">
         <v>1</v>
       </c>
       <c r="G139" t="n">
-        <v>1.015</v>
+        <v>1.66</v>
       </c>
       <c r="H139" t="n">
-        <v>1.015</v>
+        <v>0.615</v>
       </c>
       <c r="I139" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J139" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K139" t="n">
-        <v>1.44145</v>
+        <v>1.029483</v>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>Ho-phen</t>
+          <t>Cr-phen</t>
         </is>
       </c>
       <c r="M139" t="n">
-        <v>1.600347259896824</v>
+        <v>1.148117904666666</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Cr</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -6999,16 +6999,16 @@
         <v>2</v>
       </c>
       <c r="E140" t="n">
-        <v>4.878</v>
+        <v>4.348</v>
       </c>
       <c r="F140" t="n">
         <v>1</v>
       </c>
       <c r="G140" t="n">
-        <v>1.66</v>
+        <v>2.16</v>
       </c>
       <c r="H140" t="n">
-        <v>0.615</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I140" t="n">
         <v>0</v>
@@ -7017,21 +7017,21 @@
         <v>3</v>
       </c>
       <c r="K140" t="n">
-        <v>1.029483</v>
+        <v>1.039938</v>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>Cr-phen</t>
+          <t>Mo-phen</t>
         </is>
       </c>
       <c r="M140" t="n">
-        <v>1.27054676972619</v>
+        <v>1.197547407500003</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>Sm</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -7046,39 +7046,39 @@
         <v>2</v>
       </c>
       <c r="E141" t="n">
-        <v>4.348</v>
+        <v>2.78</v>
       </c>
       <c r="F141" t="n">
         <v>1</v>
       </c>
       <c r="G141" t="n">
-        <v>2.16</v>
+        <v>1.079</v>
       </c>
       <c r="H141" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.079</v>
       </c>
       <c r="I141" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J141" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K141" t="n">
-        <v>1.039938</v>
+        <v>1.39301</v>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>Mo-phen</t>
+          <t>Sm-phen</t>
         </is>
       </c>
       <c r="M141" t="n">
-        <v>1.184956584750003</v>
+        <v>1.595577532999999</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Sm</t>
+          <t>Tm</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -7093,39 +7093,39 @@
         <v>2</v>
       </c>
       <c r="E142" t="n">
-        <v>2.78</v>
+        <v>2.852</v>
       </c>
       <c r="F142" t="n">
         <v>1</v>
       </c>
       <c r="G142" t="n">
-        <v>1.079</v>
+        <v>0.994</v>
       </c>
       <c r="H142" t="n">
-        <v>1.079</v>
+        <v>0.994</v>
       </c>
       <c r="I142" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
       </c>
       <c r="K142" t="n">
-        <v>1.39301</v>
+        <v>1.419205</v>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>Sm-phen</t>
+          <t>Tm-phen</t>
         </is>
       </c>
       <c r="M142" t="n">
-        <v>1.598126964416666</v>
+        <v>1.495328538416667</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Tm</t>
+          <t>Zr</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -7140,63 +7140,63 @@
         <v>2</v>
       </c>
       <c r="E143" t="n">
-        <v>2.852</v>
+        <v>5.556</v>
       </c>
       <c r="F143" t="n">
         <v>1</v>
       </c>
       <c r="G143" t="n">
-        <v>0.994</v>
+        <v>0.72</v>
       </c>
       <c r="H143" t="n">
-        <v>0.994</v>
+        <v>0.72</v>
       </c>
       <c r="I143" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
       </c>
       <c r="K143" t="n">
-        <v>1.419205</v>
+        <v>0.764731</v>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>Tm-phen</t>
+          <t>Zr-phen</t>
         </is>
       </c>
       <c r="M143" t="n">
-        <v>1.526551644833333</v>
+        <v>0.9721486894821445</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Zr</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>phen</t>
+          <t>tpy</t>
         </is>
       </c>
       <c r="C144" t="n">
         <v>3.04</v>
       </c>
       <c r="D144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E144" t="n">
-        <v>5.556</v>
+        <v>10</v>
       </c>
       <c r="F144" t="n">
         <v>1</v>
       </c>
       <c r="G144" t="n">
-        <v>0.72</v>
+        <v>2.36</v>
       </c>
       <c r="H144" t="n">
-        <v>0.72</v>
+        <v>0.6</v>
       </c>
       <c r="I144" t="n">
         <v>0</v>
@@ -7205,62 +7205,15 @@
         <v>0</v>
       </c>
       <c r="K144" t="n">
-        <v>0.764731</v>
+        <v>0.509731</v>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>Zr-phen</t>
+          <t>W-tpy</t>
         </is>
       </c>
       <c r="M144" t="n">
-        <v>0.982329727250002</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>tpy</t>
-        </is>
-      </c>
-      <c r="C145" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="D145" t="n">
-        <v>3</v>
-      </c>
-      <c r="E145" t="n">
-        <v>10</v>
-      </c>
-      <c r="F145" t="n">
-        <v>1</v>
-      </c>
-      <c r="G145" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="H145" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I145" t="n">
-        <v>0</v>
-      </c>
-      <c r="J145" t="n">
-        <v>0</v>
-      </c>
-      <c r="K145" t="n">
-        <v>0.509731</v>
-      </c>
-      <c r="L145" t="inlineStr">
-        <is>
-          <t>W-tpy</t>
-        </is>
-      </c>
-      <c r="M145" t="n">
-        <v>0.7373307800000002</v>
+        <v>0.7791516869166664</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/predicted_with_all_scores.xlsx
+++ b/outputs/predicted_with_all_scores.xlsx
@@ -962,7 +962,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>1.900514155000002</v>
+        <v>1.900514155000001</v>
       </c>
     </row>
     <row r="12">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>1.914118270000004</v>
+        <v>1.914118270000003</v>
       </c>
     </row>
     <row r="27">
@@ -1808,7 +1808,7 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>1.659590524940475</v>
+        <v>1.659590524940476</v>
       </c>
     </row>
     <row r="30">
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>2.533607095000005</v>
+        <v>2.533607095000006</v>
       </c>
     </row>
     <row r="31">
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>1.111443524583334</v>
+        <v>1.111443524583335</v>
       </c>
     </row>
     <row r="35">
@@ -2325,7 +2325,7 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>1.481144786124999</v>
+        <v>1.481144786125</v>
       </c>
     </row>
     <row r="41">
@@ -2372,7 +2372,7 @@
         </is>
       </c>
       <c r="M41" t="n">
-        <v>1.455697885833332</v>
+        <v>1.455697885833333</v>
       </c>
     </row>
     <row r="42">
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>0.9190281243928565</v>
+        <v>0.9190281243928566</v>
       </c>
     </row>
     <row r="45">
@@ -2748,7 +2748,7 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>1.228062739684523</v>
+        <v>1.228062739684524</v>
       </c>
     </row>
     <row r="50">
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>1.455697885833332</v>
+        <v>1.455697885833333</v>
       </c>
     </row>
     <row r="51">
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>1.393830866958332</v>
+        <v>1.393830866958331</v>
       </c>
     </row>
     <row r="53">
@@ -3030,7 +3030,7 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>1.610020932999998</v>
+        <v>1.610020932999999</v>
       </c>
     </row>
     <row r="56">
@@ -3594,7 +3594,7 @@
         </is>
       </c>
       <c r="M67" t="n">
-        <v>1.884624399999998</v>
+        <v>1.884624399999999</v>
       </c>
     </row>
     <row r="68">
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="M75" t="n">
-        <v>1.331069789166667</v>
+        <v>1.331069789166666</v>
       </c>
     </row>
     <row r="76">
@@ -4440,7 +4440,7 @@
         </is>
       </c>
       <c r="M85" t="n">
-        <v>1.620709019083334</v>
+        <v>1.620709019083335</v>
       </c>
     </row>
     <row r="86">
@@ -4722,7 +4722,7 @@
         </is>
       </c>
       <c r="M91" t="n">
-        <v>1.333173738750002</v>
+        <v>1.333173738750003</v>
       </c>
     </row>
     <row r="92">
@@ -5051,7 +5051,7 @@
         </is>
       </c>
       <c r="M98" t="n">
-        <v>1.821152890749996</v>
+        <v>1.821152890749997</v>
       </c>
     </row>
     <row r="99">
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="M105" t="n">
-        <v>1.277851859642858</v>
+        <v>1.277851859642857</v>
       </c>
     </row>
     <row r="106">
@@ -5521,7 +5521,7 @@
         </is>
       </c>
       <c r="M108" t="n">
-        <v>1.875882712999997</v>
+        <v>1.875882712999996</v>
       </c>
     </row>
     <row r="109">
@@ -5615,7 +5615,7 @@
         </is>
       </c>
       <c r="M110" t="n">
-        <v>0.9666736129761923</v>
+        <v>0.9666736129761924</v>
       </c>
     </row>
     <row r="111">
@@ -6320,7 +6320,7 @@
         </is>
       </c>
       <c r="M125" t="n">
-        <v>0.9190281243928565</v>
+        <v>0.9190281243928566</v>
       </c>
     </row>
     <row r="126">
@@ -6414,7 +6414,7 @@
         </is>
       </c>
       <c r="M127" t="n">
-        <v>1.481144786124999</v>
+        <v>1.481144786125</v>
       </c>
     </row>
     <row r="128">
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="M132" t="n">
-        <v>1.228062739684523</v>
+        <v>1.228062739684524</v>
       </c>
     </row>
     <row r="133">
@@ -6790,7 +6790,7 @@
         </is>
       </c>
       <c r="M135" t="n">
-        <v>1.620709019083334</v>
+        <v>1.620709019083335</v>
       </c>
     </row>
     <row r="136">
